--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,7 +31,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -52,7 +52,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -70,8 +75,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F5F9"/>
-        <bgColor rgb="00F2F5F9"/>
+        <fgColor rgb="00F9FAFC"/>
+        <bgColor rgb="00F9FAFC"/>
       </patternFill>
     </fill>
     <fill>
@@ -91,16 +96,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </bottom>
     </border>
     <border>
@@ -115,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +161,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -531,8 +537,8 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="57" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating Cycle: Sep 23 – Sep 29, 2026 | All 10 Team Members Standardized</t>
+          <t>Operating Cycle: Sep 23 – Sep 30, 2026 | All 10 Team Members Standardized + Sep 30 Standby</t>
         </is>
       </c>
     </row>
@@ -633,7 +639,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -683,7 +689,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Standard shift completed</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
@@ -728,7 +734,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Extended shift (+1h 40m overtime)</t>
+          <t>⚡ Extended shift (+1h 40m overtime)</t>
         </is>
       </c>
     </row>
@@ -773,7 +779,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Standard shift completed</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
@@ -818,7 +824,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Standard shift (4:00 PM return)</t>
+          <t>Standard daytime shift (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -863,7 +869,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Standard shift (4:00 PM return)</t>
+          <t>Standard daytime shift (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -908,14 +914,14 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Standard shift (4:00 PM return)</t>
+          <t>Standard daytime shift (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -925,12 +931,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -940,32 +946,32 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -975,42 +981,42 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>06:30 AM</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Standard 8.5h shift</t>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1043,19 +1049,19 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Standard 8.5h shift</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1088,19 +1094,19 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Standard 8.5h shift</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1110,42 +1116,42 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Morning shift (4:00 PM return)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1173,24 +1179,24 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Morning shift (4:00 PM return)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1218,34 +1224,34 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Morning shift (4:00 PM return)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1255,11 +1261,11 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1268,64 +1274,64 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Standard daytime shift (8.5 hrs)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1335,42 +1341,42 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>06:30 AM</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift (8.5 hrs)</t>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1403,19 +1409,19 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Standard daytime shift (8.5 hrs)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1425,42 +1431,42 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Morning departure processing (4:00 PM return)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -1470,42 +1476,42 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G24" s="7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Morning departure processing (4:00 PM return)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1515,7 +1521,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>03:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1525,37 +1531,37 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Early dawn flight departure handling (4:00 PM return)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Talal</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1565,42 +1571,42 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Morning 9.5h shift</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Talal</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1623,29 +1629,29 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Early dawn flight departure shift (4:00 PM return)</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Talal</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1668,34 +1674,34 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>Morning shift (4:00 PM return)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Talal</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>03:00 AM</t>
+          <t>06:30 AM</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -1705,42 +1711,42 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Early dawn flight departure shift (4:00 PM return)</t>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -1750,11 +1756,11 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -1763,24 +1769,24 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1790,16 +1796,16 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -1808,29 +1814,29 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Standard 8.5h shift</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -1840,87 +1846,87 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>13h 15m</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">
-        <v>8.5</v>
+        <v>13.25</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Standard 8.5h shift</t>
+          <t>✈️ Early dawn flight check-in &amp; boarding (13h 15m)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>03:40 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>12h 50m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>12.83</v>
+        <v>9</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Early dawn flight processing shift (12h 50m)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>03:40 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1930,42 +1936,42 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>12h 20m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G34" s="7" t="n">
-        <v>12.33</v>
+        <v>9</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Early dawn flight processing shift (4:00 PM return)</t>
+          <t>Morning departure processing</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>04:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1975,42 +1981,42 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>12h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Early morning flight departure shift (4:00 PM return)</t>
+          <t>Morning departure processing</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>04:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -2020,20 +2026,20 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>12h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G36" s="7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>Early morning flight departure shift (4:00 PM return)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2056,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2073,7 +2079,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -2095,26 +2101,26 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:10 AM</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>7h 50m</t>
         </is>
       </c>
       <c r="G38" s="7" t="n">
-        <v>8.5</v>
+        <v>7.83</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -2123,7 +2129,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>Standard 8.5h shift</t>
+          <t>Standard daytime shift (7h 50m)</t>
         </is>
       </c>
     </row>
@@ -2140,35 +2146,35 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>08:15 AM</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>7h 45m</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Scheduled weekly day off</t>
+          <t>Standard daytime shift (7h 45m)</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2191,12 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>03:30 AM</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -2200,20 +2206,20 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G40" s="7" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Morning 9.5h shift</t>
+          <t>✈️ Early dawn flight check-in &amp; departure (13.0 hrs)</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2236,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2253,12 +2259,12 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Morning flight shift (4:00 PM return)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2281,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -2298,12 +2304,12 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>Morning flight shift (4:00 PM return)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2326,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2343,19 +2349,19 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Morning flight shift (4:00 PM return)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -2365,12 +2371,12 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -2380,42 +2386,42 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>06:30 AM</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2425,37 +2431,37 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Standard shift (8.0 hrs)</t>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -2465,16 +2471,16 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G46" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
@@ -2483,119 +2489,119 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Standard shift (8.0 hrs)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Scheduled weekly day off</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>03:40 AM</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>12h 50m</t>
         </is>
       </c>
       <c r="G48" s="7" t="n">
-        <v>9</v>
+        <v>12.83</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Morning flight shift (9.0 hrs)</t>
+          <t>✈️ Dawn flight check-in &amp; boarding ops (12.83 hrs)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>03:40 AM</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -2605,42 +2611,42 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>12h 20m</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>9</v>
+        <v>12.33</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>Morning flight shift (9.0 hrs)</t>
+          <t>✈️ Dawn flight check-in &amp; boarding ops (12.33 hrs)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>04:00 AM</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -2650,42 +2656,42 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>12h 00m</t>
         </is>
       </c>
       <c r="G50" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Morning flight shift (4:00 PM return)</t>
+          <t>✈️ Early morning departure ops (12.0 hrs)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>04:00 AM</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -2695,42 +2701,42 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>12h 00m</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>✈️ Early morning departure ops (12.0 hrs)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -2740,42 +2746,42 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G52" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>Standard shift (8.0 hrs)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>06:30 AM</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -2785,177 +2791,177 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Standard shift (8.0 hrs)</t>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>08:20 AM</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>13h 15m</t>
+          <t>7h 40m</t>
         </is>
       </c>
       <c r="G54" s="7" t="n">
-        <v>13.25</v>
+        <v>7.67</v>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>Early dawn flight check-in &amp; boarding (13h 15m)</t>
+          <t>Standard daytime shift (7h 40m)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:15 AM</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:45 PM</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Morning departure processing (4:00 PM return)</t>
+          <t>Standard daytime shift (7h 30m)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:15 AM</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G56" s="7" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Morning shift (9.0 hrs)</t>
+          <t>Standard daytime shift (8h 15m)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -2965,42 +2971,42 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Morning flight shift (9.0 hrs)</t>
+          <t>Morning departure processing (8h 45m)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -3010,11 +3016,11 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>8h 40m</t>
         </is>
       </c>
       <c r="G58" s="7" t="n">
-        <v>9.5</v>
+        <v>8.67</v>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
@@ -3023,29 +3029,29 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>Morning departure processing (8h 40m)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>08:10 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3055,11 +3061,11 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>7h 50m</t>
+          <t>8h 40m</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>7.83</v>
+        <v>8.67</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
@@ -3068,29 +3074,29 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift (7h 50m)</t>
+          <t>Morning departure processing (8h 40m)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -3100,172 +3106,172 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G60" s="7" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>Standard daytime shift (7h 45m)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>03:30 AM</t>
+          <t>06:30 AM</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Dawn/Overtime</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Early dawn flight check-in &amp; departure (13.0 hrs)</t>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G62" s="7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Morning departure processing (4:00 PM return)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Day Off</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>Morning departure processing (4:00 PM return)</t>
+          <t>🌴 Scheduled weekly day off</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3275,47 +3281,47 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G64" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Morning departure processing (9.0 hrs)</t>
+          <t>Morning flight shift (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -3325,11 +3331,11 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
@@ -3338,29 +3344,29 @@
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>Morning flight shift (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>08:20 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -3370,11 +3376,11 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>7h 40m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G66" s="7" t="n">
-        <v>7.67</v>
+        <v>9</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -3383,43 +3389,43 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>Standard daytime shift (7h 40m)</t>
+          <t>Morning flight shift (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>03:45 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
@@ -3428,74 +3434,74 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift (7h 30m)</t>
+          <t>Morning flight shift (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G68" s="7" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>Standard daytime shift (8h 15m)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>06:30 AM</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -3505,42 +3511,42 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standardized</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Morning departure processing (8h 45m)</t>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -3550,42 +3556,42 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>8h 40m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G70" s="7" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>Morning departure processing (8h 40m)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -3595,32 +3601,32 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>8h 40m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Morning departure processing (8h 40m)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -3630,120 +3636,570 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>02:00 PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>6h 15m</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="G72" s="7" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Day Off</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>Saudia Airlines Training Session (6h 15m)</t>
+          <t>🌴 Scheduled weekly day off</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>02:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>6h 15m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Saudia Airlines Training Session (6h 15m)</t>
+          <t>Morning flight shift</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>Morning flight shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>Morning flight shift (4:00 PM return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Off / Not scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>07:45 AM</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>02:00 PM</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>6h 15m</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>Saudia Airlines Training Session (6h 15m)</t>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>🌴 Off / Not scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Off / Not scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>Morning flight shift (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>03:00 AM</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>Morning flight shift (4:00 PM return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>03:00 AM</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -3758,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3768,8 +4224,8 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3782,7 +4238,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating Cycle: Oct 01 – Ongoing | Saudia &amp; Etihad Operations</t>
+          <t>Operating Cycle: Oct 01 – Oct 06 | Saudia/Etihad Training &amp; Paid Administrative Standby</t>
         </is>
       </c>
     </row>
@@ -3847,35 +4303,35 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>02:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>6h 15m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Saudia Airlines Training Session (6h 15m)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -3892,35 +4348,35 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>02:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>6h 15m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Saudia Airlines Training Session (6h 15m)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -3965,322 +4421,322 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Saudia Airlines Training Session (6h 15m)</t>
+          <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Talal</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>02:00 PM</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>6h 15m</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Talal</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>02:00 PM</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>6h 15m</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4753,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -4325,7 +4781,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4798,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -4370,7 +4826,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4843,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -4415,52 +4871,2167 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Scheduled team day off (No shift)</t>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>🎓 Etihad IGS Training Session (MS Teams)</t>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>08:48 AM</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>7h 12m</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 08:48 AM (7h 12m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -4475,28 +7046,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Damascus Ground Operations — Team Hours Leaderboard</t>
+          <t>Damascus Ground Operations — Cumulative Hours Master Leaderboard</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated September 2026 Full Cycle Rankings</t>
+          <t>Consolidated September &amp; October 2026 Total Work &amp; Standby Output</t>
         </is>
       </c>
     </row>
@@ -4514,22 +7086,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Days Logged</t>
+          <t>September (8 Days)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Total Hours (hh:mm)</t>
+          <t>October (6 Days)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Cumulative Output</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>Decimal Hours</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Avg Daily Hours</t>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Status / Notes</t>
         </is>
       </c>
     </row>
@@ -4542,19 +7119,28 @@
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>75h 40m</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>75.67</v>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>84h 40m</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>42h 00m</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>126h 40m</t>
+        </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>10.81</v>
+        <v>126.66</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Core Team / Dawn Shift Lead</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4563,22 +7149,31 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>66h 00m</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>66</v>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>74h 45m</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>41h 15m</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>116h 00m</t>
+        </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>9.43</v>
+        <v>116</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Core Team / Station Operations</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4587,22 +7182,31 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>65h 45m</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>65.75</v>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>74h 05m</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>41h 15m</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>115h 20m</t>
+        </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>9.390000000000001</v>
+        <v>115.33</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Core Team / Station Operations</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4611,22 +7215,31 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>65h 05m</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>65.08</v>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>75h 00m</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>39h 15m</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>114h 15m</t>
+        </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>9.300000000000001</v>
+        <v>114.25</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Core Team / Saudia &amp; Etihad Ops</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -4638,19 +7251,28 @@
           <t>Khaled</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>62h 00m</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>62</v>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>71h 00m</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>41h 15m</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>112h 15m</t>
+        </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>8.859999999999999</v>
+        <v>112.25</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Core Team / Station Operations</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -4662,19 +7284,28 @@
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>59h 00m</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>59</v>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>68h 00m</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>41h 15m</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>109h 15m</t>
+        </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>8.43</v>
+        <v>109.25</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Core Team / Station Operations</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -4686,19 +7317,28 @@
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>57h 40m</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>57.67</v>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>66h 40m</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>41h 15m</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>107h 55m</t>
+        </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>8.24</v>
+        <v>107.92</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Core Team / Systems &amp; Ground Ops</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4710,19 +7350,28 @@
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>54h 30m</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>54.5</v>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>63h 30m</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>39h 15m</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>102h 45m</t>
+        </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>9.08</v>
+        <v>102.75</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Core Team / ID Delay - Paid</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -4734,19 +7383,28 @@
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>52h 30m</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>52.5</v>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>61h 30m</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>39h 15m</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>100h 45m</t>
+        </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>8.75</v>
+        <v>100.75</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Core Team / Saudia &amp; Etihad Ops</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4758,45 +7416,96 @@
           <t>Talal</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>44h 30m</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>44.5</v>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>53h 30m</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>42h 00m</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>95h 30m</t>
+        </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>11.12</v>
+        <v>95.5</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Core Team / ID Delay - Paid</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>7h 12m</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>7h 12m</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Onboarding Member (Joined Oct 04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>🏆</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Total Team Output</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>602h 40m</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>602.67</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>9.42</v>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>692h 40m</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>415h 27m</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>1,108h 07m</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>1108.12</v>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>Full Damascus Ground Station Roster</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -4214,18 +4214,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="104" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4238,7 +4238,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating Cycle: Oct 01 – Oct 06 | Saudia/Etihad Training &amp; Paid Administrative Standby</t>
+          <t>Operating Cycle: Oct 01 – Ongoing | Live Airport Duty &amp; Training</t>
         </is>
       </c>
     </row>
@@ -7032,6 +7032,96 @@
       <c r="I65" s="6" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>08:16 AM</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>7h 44m</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Damascus Int Airport - Check-in &amp; DCS Ops / Logged in 08:16 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>08:16 AM</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>7h 44m</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Damascus Int Airport - Check-in &amp; DCS Ops / Logged in 08:16 AM)</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7145,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7091,7 +7181,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>October (6 Days)</t>
+          <t>October (7 Days)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -7126,20 +7216,20 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>42h 00m</t>
+          <t>49h 44m</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>126h 40m</t>
+          <t>134h 24m</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>126.66</v>
+        <v>134.39</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Dawn Shift Lead</t>
+          <t>Core Team / Live Station Duty (08:16 AM)</t>
         </is>
       </c>
     </row>
@@ -7182,30 +7272,30 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>74h 05m</t>
+          <t>66h 40m</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>41h 15m</t>
+          <t>48h 59m</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>115h 20m</t>
+          <t>115h 39m</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>115.33</v>
+        <v>115.65</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Station Operations</t>
+          <t>Core Team / Live Station Duty (08:16 AM)</t>
         </is>
       </c>
     </row>
@@ -7215,30 +7305,30 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>75h 00m</t>
+          <t>74h 05m</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>39h 15m</t>
+          <t>41h 15m</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>114h 15m</t>
+          <t>115h 20m</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>114.25</v>
+        <v>115.33</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Core Team / Saudia &amp; Etihad Ops</t>
+          <t>Core Team / Station Operations</t>
         </is>
       </c>
     </row>
@@ -7248,30 +7338,30 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>71h 00m</t>
+          <t>75h 00m</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>41h 15m</t>
+          <t>39h 15m</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>112h 15m</t>
+          <t>114h 15m</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>112.25</v>
+        <v>114.25</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Station Operations</t>
+          <t>Core Team / Saudia &amp; Etihad Ops</t>
         </is>
       </c>
     </row>
@@ -7281,12 +7371,12 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>68h 00m</t>
+          <t>71h 00m</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -7296,11 +7386,11 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>109h 15m</t>
+          <t>112h 15m</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>109.25</v>
+        <v>112.25</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -7314,12 +7404,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>66h 40m</t>
+          <t>68h 00m</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -7329,15 +7419,15 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>107h 55m</t>
+          <t>109h 15m</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>107.92</v>
+        <v>109.25</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Systems &amp; Ground Ops</t>
+          <t>Core Team / Station Operations</t>
         </is>
       </c>
     </row>
@@ -7491,16 +7581,16 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>415h 27m</t>
+          <t>430h 55m</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>1,108h 07m</t>
+          <t>1,123h 35m</t>
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>1108.12</v>
+        <v>1123.58</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -4214,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4225,7 +4225,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="104" customWidth="1" min="9" max="9"/>
+    <col width="81" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>08:16 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -7063,20 +7063,20 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>7h 44m</t>
+          <t>12h 45m</t>
         </is>
       </c>
       <c r="G66" s="7" t="n">
-        <v>7.73</v>
+        <v>12.75</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Damascus Int Airport - Check-in &amp; DCS Ops / Logged in 08:16 AM)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / DAM Station)</t>
         </is>
       </c>
     </row>
@@ -7093,35 +7093,440 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>12h 45m</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / DAM Station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>12h 45m</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / DAM Station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>8h 45m</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:15 AM / DAM Station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>8h 45m</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:15 AM / DAM Station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>8h 45m</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:15 AM / DAM Station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>8h 45m</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:15 AM / DAM Station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>08:16 AM</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>7h 44m</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:16 AM / DAM Station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>08:16 AM</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>7h 44m</t>
         </is>
       </c>
-      <c r="G67" s="5" t="n">
+      <c r="G74" s="7" t="n">
         <v>7.73</v>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H74" s="7" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Airport Ground Station Duty (Damascus Int Airport - Check-in &amp; DCS Ops / Logged in 08:16 AM)</t>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:16 AM / DAM Station)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7550,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7229,7 +7634,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Live Station Duty (08:16 AM)</t>
+          <t>Core Team / Station Shift Lead (08:16 AM)</t>
         </is>
       </c>
     </row>
@@ -7249,20 +7654,20 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>41h 15m</t>
+          <t>54h 00m</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>116h 00m</t>
+          <t>128h 45m</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>116</v>
+        <v>128.75</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Core Team / Station Operations</t>
+          <t>Core Team / Dawn Flight Handling (03:15 AM)</t>
         </is>
       </c>
     </row>
@@ -7272,30 +7677,30 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>66h 40m</t>
+          <t>75h 00m</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>48h 59m</t>
+          <t>52h 00m</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>115h 39m</t>
+          <t>127h 00m</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>115.65</v>
+        <v>127</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Live Station Duty (08:16 AM)</t>
+          <t>Core Team / Dawn Flight Handling (03:15 AM)</t>
         </is>
       </c>
     </row>
@@ -7315,20 +7720,20 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>41h 15m</t>
+          <t>50h 00m</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>115h 20m</t>
+          <t>124h 05m</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>115.33</v>
+        <v>124.08</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Core Team / Station Operations</t>
+          <t>Core Team / Morning Station Duty (07:15 AM)</t>
         </is>
       </c>
     </row>
@@ -7338,30 +7743,30 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>75h 00m</t>
+          <t>71h 00m</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>39h 15m</t>
+          <t>50h 00m</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>114h 15m</t>
+          <t>121h 00m</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>114.25</v>
+        <v>121</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Saudia &amp; Etihad Ops</t>
+          <t>Core Team / Morning Station Duty (07:15 AM)</t>
         </is>
       </c>
     </row>
@@ -7371,30 +7776,30 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>71h 00m</t>
+          <t>68h 00m</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>41h 15m</t>
+          <t>50h 00m</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>112h 15m</t>
+          <t>118h 00m</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>112.25</v>
+        <v>118</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Core Team / Station Operations</t>
+          <t>Core Team / Morning Station Duty (07:15 AM)</t>
         </is>
       </c>
     </row>
@@ -7404,30 +7809,30 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>68h 00m</t>
+          <t>66h 40m</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>41h 15m</t>
+          <t>48h 59m</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>109h 15m</t>
+          <t>115h 39m</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>109.25</v>
+        <v>115.65</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Station Operations</t>
+          <t>Core Team / Station Systems &amp; Ops (08:16 AM)</t>
         </is>
       </c>
     </row>
@@ -7437,30 +7842,30 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>63h 30m</t>
+          <t>61h 30m</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>39h 15m</t>
+          <t>52h 00m</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>102h 45m</t>
+          <t>113h 30m</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>102.75</v>
+        <v>113.5</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Core Team / ID Delay - Paid</t>
+          <t>Core Team / Dawn Flight Handling (03:15 AM)</t>
         </is>
       </c>
     </row>
@@ -7470,30 +7875,30 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>61h 30m</t>
+          <t>63h 30m</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>39h 15m</t>
+          <t>48h 15m</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>100h 45m</t>
+          <t>111h 45m</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>100.75</v>
+        <v>111.75</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Core Team / Saudia &amp; Etihad Ops</t>
+          <t>Core Team / ID Delay - Paid Standby</t>
         </is>
       </c>
     </row>
@@ -7513,20 +7918,20 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>42h 00m</t>
+          <t>51h 00m</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>95h 30m</t>
+          <t>104h 30m</t>
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>95.5</v>
+        <v>104.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Core Team / ID Delay - Paid</t>
+          <t>Core Team / ID Delay - Paid Standby</t>
         </is>
       </c>
     </row>
@@ -7546,20 +7951,20 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>7h 12m</t>
+          <t>31h 57m</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>7h 12m</t>
+          <t>31h 57m</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7.2</v>
+        <v>31.95</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Onboarding Member (Joined Oct 04)</t>
+          <t>Onboarding / Morning Station Duty (07:15 AM)</t>
         </is>
       </c>
     </row>
@@ -7581,16 +7986,16 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>430h 55m</t>
+          <t>537h 11m</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>1,123h 35m</t>
+          <t>1,229h 51m</t>
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>1123.58</v>
+        <v>1229.85</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -555,7 +555,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4214,7 +4213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4242,7 +4241,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6608,16 +6606,16 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G56" s="7" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
@@ -6653,16 +6651,16 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
@@ -6698,16 +6696,16 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G58" s="7" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
@@ -6738,7 +6736,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -6748,20 +6746,20 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -6788,16 +6786,16 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G60" s="7" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
@@ -6828,7 +6826,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -6838,20 +6836,20 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -6878,16 +6876,16 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G62" s="7" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
@@ -6923,16 +6921,16 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
@@ -6968,16 +6966,16 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G64" s="7" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
@@ -7013,16 +7011,16 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
@@ -7527,6 +7525,96 @@
       <c r="I76" s="8" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>8</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7655,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7621,16 +7708,16 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>49h 44m</t>
+          <t>49h 49m</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>134h 24m</t>
+          <t>134h 29m</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>134.39</v>
+        <v>134.48</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -7654,16 +7741,16 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>54h 00m</t>
+          <t>54h 05m</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>128h 45m</t>
+          <t>128h 50m</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>128.75</v>
+        <v>128.83</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
@@ -7687,16 +7774,16 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>52h 00m</t>
+          <t>52h 05m</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>127h 00m</t>
+          <t>127h 05m</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>127</v>
+        <v>127.08</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -7720,16 +7807,16 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>50h 00m</t>
+          <t>50h 05m</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>124h 05m</t>
+          <t>124h 10m</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>124.08</v>
+        <v>124.17</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
@@ -7753,16 +7840,16 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>50h 00m</t>
+          <t>50h 05m</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>121h 00m</t>
+          <t>121h 05m</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>121</v>
+        <v>121.08</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -7786,16 +7873,16 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>50h 00m</t>
+          <t>50h 05m</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>118h 00m</t>
+          <t>118h 05m</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>118</v>
+        <v>118.08</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -7819,16 +7906,16 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>48h 59m</t>
+          <t>49h 04m</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>115h 39m</t>
+          <t>115h 44m</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>115.65</v>
+        <v>115.73</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -7852,16 +7939,16 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>52h 00m</t>
+          <t>52h 05m</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>113h 30m</t>
+          <t>113h 35m</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>113.5</v>
+        <v>113.58</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -7885,16 +7972,16 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>48h 15m</t>
+          <t>49h 15m</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>111h 45m</t>
+          <t>112h 45m</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>111.75</v>
+        <v>112.75</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -7918,16 +8005,16 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>51h 00m</t>
+          <t>52h 00m</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>104h 30m</t>
+          <t>105h 30m</t>
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>104.5</v>
+        <v>105.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -7951,16 +8038,16 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>31h 57m</t>
+          <t>32h 02m</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>31h 57m</t>
+          <t>32h 02m</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>31.95</v>
+        <v>32.03</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -7986,16 +8073,16 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>537h 11m</t>
+          <t>545h 15m</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>1,229h 51m</t>
+          <t>1,237h 55m</t>
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>1229.85</v>
+        <v>1237.92</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -7321,7 +7321,7 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G72" s="7" t="n">
-        <v>8.75</v>
+        <v>8.08</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:15 AM / DAM Station)</t>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / DAM Station)</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>08:16 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -7376,11 +7376,11 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>7h 44m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>7.73</v>
+        <v>8.08</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:16 AM / DAM Station)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / DAM Station)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -7051,21 +7051,21 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>12h 45m</t>
+          <t>7h 25m</t>
         </is>
       </c>
       <c r="G66" s="7" t="n">
-        <v>12.75</v>
+        <v>7.42</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / DAM Station)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7096,21 +7096,21 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>12h 45m</t>
+          <t>7h 25m</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>12.75</v>
+        <v>7.42</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / DAM Station)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7141,21 +7141,21 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>03:55 AM</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>12h 45m</t>
+          <t>11h 25m</t>
         </is>
       </c>
       <c r="G68" s="7" t="n">
-        <v>12.75</v>
+        <v>11.42</v>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / DAM Station)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7186,21 +7186,21 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>7h 25m</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>8.75</v>
+        <v>7.42</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:15 AM / DAM Station)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7231,21 +7231,21 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>03:55 AM</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>11h 25m</t>
         </is>
       </c>
       <c r="G70" s="7" t="n">
-        <v>8.75</v>
+        <v>11.42</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:15 AM / DAM Station)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7276,21 +7276,21 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>7h 25m</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>8.75</v>
+        <v>7.42</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:15 AM / DAM Station)</t>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7326,16 +7326,16 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>7h 25m</t>
         </is>
       </c>
       <c r="G72" s="7" t="n">
-        <v>8.08</v>
+        <v>7.42</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / DAM Station)</t>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7371,16 +7371,16 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>7h 25m</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>8.08</v>
+        <v>7.42</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / DAM Station)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7411,21 +7411,21 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>08:16 AM</t>
+          <t>03:55 AM</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>7h 44m</t>
+          <t>11h 25m</t>
         </is>
       </c>
       <c r="G74" s="7" t="n">
-        <v>7.73</v>
+        <v>11.42</v>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:16 AM / DAM Station)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 03:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7708,16 +7708,16 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>49h 49m</t>
+          <t>53h 30m</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>134h 29m</t>
+          <t>138h 10m</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>134.48</v>
+        <v>138.17</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -7741,16 +7741,16 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>54h 05m</t>
+          <t>48h 45m</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>128h 50m</t>
+          <t>123h 30m</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>128.83</v>
+        <v>123.5</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
@@ -7774,16 +7774,16 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>52h 05m</t>
+          <t>50h 45m</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>127h 05m</t>
+          <t>125h 45m</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>127.08</v>
+        <v>125.75</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -7807,16 +7807,16 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>50h 05m</t>
+          <t>52h 45m</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>124h 10m</t>
+          <t>126h 50m</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>124.17</v>
+        <v>126.83</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
@@ -7840,16 +7840,16 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>50h 05m</t>
+          <t>48h 45m</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>121h 05m</t>
+          <t>119h 45m</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>121.08</v>
+        <v>119.75</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -7873,16 +7873,16 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>50h 05m</t>
+          <t>48h 45m</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>118h 05m</t>
+          <t>116h 45m</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>118.08</v>
+        <v>116.75</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -7906,16 +7906,16 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>49h 04m</t>
+          <t>48h 45m</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>115h 44m</t>
+          <t>115h 25m</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>115.73</v>
+        <v>115.42</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -7939,16 +7939,16 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>52h 05m</t>
+          <t>46h 45m</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>113h 35m</t>
+          <t>108h 15m</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>113.58</v>
+        <v>108.25</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>32h 02m</t>
+          <t>30h 42m</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>32h 02m</t>
+          <t>30h 42m</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>32.03</v>
+        <v>30.7</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -4213,7 +4213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7615,6 +7615,501 @@
       <c r="I78" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>03:55 AM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>11h 25m</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>03:55 AM</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>11h 25m</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>03:55 AM</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>11h 25m</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>9</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>9</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -7546,30 +7546,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>7h 25m</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>8</v>
+        <v>7.42</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training / Paid Standby</t>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7591,30 +7591,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>03:20 PM</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>7h 25m</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>8.08</v>
+        <v>7.42</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training / Paid Standby</t>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>03:55 AM</t>
+          <t>04:45 AM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7736,11 +7736,11 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>11h 25m</t>
+          <t>10h 35m</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>11.42</v>
+        <v>10.58</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>03:55 AM</t>
+          <t>04:45 AM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7826,11 +7826,11 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>11h 25m</t>
+          <t>10h 35m</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>11.42</v>
+        <v>10.58</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>03:55 AM</t>
+          <t>04:45 AM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8006,11 +8006,11 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>11h 25m</t>
+          <t>10h 35m</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>11.42</v>
+        <v>10.58</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -7546,7 +7546,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:50 AM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:50 AM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>04:45 AM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7646,11 +7646,11 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>10h 35m</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>7.42</v>
+        <v>10.58</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:50 AM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7691,11 +7691,11 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>04:45 AM</t>
+          <t>07:50 AM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7736,11 +7736,11 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>10h 35m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>10.58</v>
+        <v>7.5</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:50 AM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7781,11 +7781,11 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:50 AM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7871,11 +7871,11 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:50 AM</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7916,11 +7916,11 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:50 AM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7961,11 +7961,11 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -4213,7 +4213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8110,6 +8110,456 @@
       <c r="I89" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>04:45 AM</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10h 35m</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>04:45 AM</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>10h 35m</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>04:45 AM</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>10h 35m</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>9</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>9</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -8131,25 +8131,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>04:45 AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10h 35m</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>10.58</v>
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+          <t>🌴 Scheduled Day Off</t>
         </is>
       </c>
     </row>
@@ -8653,16 +8658,16 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>53h 30m</t>
+          <t>74h 40m</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>138h 10m</t>
+          <t>159h 20m</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>138.17</v>
+        <v>159.33</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -8686,16 +8691,16 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>48h 45m</t>
+          <t>69h 55m</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>123h 30m</t>
+          <t>144h 40m</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>123.5</v>
+        <v>144.67</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
@@ -8719,16 +8724,16 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>50h 45m</t>
+          <t>65h 45m</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>125h 45m</t>
+          <t>140h 45m</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>125.75</v>
+        <v>140.75</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -8752,16 +8757,16 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>52h 45m</t>
+          <t>63h 20m</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>126h 50m</t>
+          <t>137h 25m</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>126.83</v>
+        <v>137.42</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
@@ -8785,16 +8790,16 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>48h 45m</t>
+          <t>63h 45m</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>119h 45m</t>
+          <t>134h 45m</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>119.75</v>
+        <v>134.75</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -8818,16 +8823,16 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>48h 45m</t>
+          <t>63h 45m</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>116h 45m</t>
+          <t>131h 45m</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>116.75</v>
+        <v>131.75</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -8841,26 +8846,26 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>66h 40m</t>
+          <t>63h 30m</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>48h 45m</t>
+          <t>67h 15m</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>115h 25m</t>
+          <t>130h 45m</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>115.42</v>
+        <v>130.75</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -8874,26 +8879,26 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>61h 30m</t>
+          <t>66h 40m</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>46h 45m</t>
+          <t>63h 45m</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>108h 15m</t>
+          <t>130h 25m</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>108.25</v>
+        <v>130.42</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -8907,26 +8912,26 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Talal</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>63h 30m</t>
+          <t>53h 30m</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>49h 15m</t>
+          <t>70h 00m</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>112h 45m</t>
+          <t>123h 30m</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>112.75</v>
+        <v>123.5</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -8940,26 +8945,26 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Talal</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>53h 30m</t>
+          <t>61h 30m</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>52h 00m</t>
+          <t>61h 45m</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>105h 30m</t>
+          <t>123h 15m</t>
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>105.5</v>
+        <v>123.25</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -8983,16 +8988,16 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>30h 42m</t>
+          <t>45h 42m</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>30h 42m</t>
+          <t>45h 42m</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>30.7</v>
+        <v>45.7</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -8154,7 +8154,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>🌴 Scheduled Day Off</t>
+          <t>🌴 Scheduled Day Off (⚠️ Second Day Off taken in October 2026 Cycle)</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Core Team / Morning Station Duty (07:15 AM)</t>
+          <t>Core Team / Morning Station Duty (07:15 AM) (⚠️ 2 Days Off Taken)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -8154,7 +8154,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>🌴 Scheduled Day Off (⚠️ Second Day Off taken in October 2026 Cycle)</t>
+          <t>🌴 Scheduled Day Off (Weekly Day Off)</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Core Team / Morning Station Duty (07:15 AM) (⚠️ 2 Days Off Taken)</t>
+          <t>Core Team / Morning Station Duty (07:15 AM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -666,7 +666,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -4353,7 +4352,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -8294,21 +8292,21 @@
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
         <is>
-          <t>10h 35m</t>
+          <t>10h 45m</t>
         </is>
       </c>
       <c r="G91" s="20" t="n">
-        <v>10.58</v>
+        <v>10.75</v>
       </c>
       <c r="H91" s="20" t="n"/>
       <c r="I91" s="21" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 04:45 AM / Logged out 03:30 PM)</t>
         </is>
       </c>
     </row>
@@ -8499,21 +8497,21 @@
       </c>
       <c r="E96" s="28" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F96" s="28" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>7h 40m</t>
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="H96" s="28" t="n"/>
       <c r="I96" s="29" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
         </is>
       </c>
     </row>
@@ -8540,21 +8538,21 @@
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>7h 40m</t>
         </is>
       </c>
       <c r="G97" s="20" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="H97" s="20" t="n"/>
       <c r="I97" s="21" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
         </is>
       </c>
     </row>
@@ -8671,21 +8669,21 @@
       </c>
       <c r="E100" s="28" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F100" s="28" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>7h 40m</t>
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="H100" s="28" t="n"/>
       <c r="I100" s="29" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8724,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -8333,21 +8333,21 @@
       </c>
       <c r="E92" s="28" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>05:13 PM</t>
         </is>
       </c>
       <c r="F92" s="28" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>9h 23m</t>
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>7.5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H92" s="28" t="n"/>
       <c r="I92" s="29" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
@@ -8374,21 +8374,21 @@
       </c>
       <c r="E93" s="20" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>05:13 PM</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
         <is>
-          <t>10h 35m</t>
+          <t>12h 28m</t>
         </is>
       </c>
       <c r="G93" s="20" t="n">
-        <v>10.58</v>
+        <v>12.47</v>
       </c>
       <c r="H93" s="20" t="n"/>
       <c r="I93" s="21" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 04:45 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
@@ -8415,21 +8415,21 @@
       </c>
       <c r="E94" s="28" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>05:13 PM</t>
         </is>
       </c>
       <c r="F94" s="28" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>9h 23m</t>
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>7.5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H94" s="28" t="n"/>
       <c r="I94" s="29" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
@@ -8456,21 +8456,21 @@
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>05:13 PM</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>9h 23m</t>
         </is>
       </c>
       <c r="G95" s="20" t="n">
-        <v>7.5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H95" s="20" t="n"/>
       <c r="I95" s="21" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -86,7 +86,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -141,6 +141,12 @@
         <bgColor rgb="00F2DCDB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -190,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -271,6 +277,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4324,14 +4336,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -4352,6 +4364,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -8684,6 +8697,501 @@
       <c r="I100" s="29" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B101" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C101" s="33" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D101" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E101" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F101" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G101" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="I101" s="33" t="inlineStr">
+        <is>
+          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C102" s="33" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D102" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E102" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F102" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G102" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="I102" s="33" t="inlineStr">
+        <is>
+          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B103" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C103" s="33" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D103" s="32" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E103" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F103" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G103" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="32" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I103" s="33" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B104" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C104" s="33" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D104" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E104" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F104" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G104" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="I104" s="33" t="inlineStr">
+        <is>
+          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B105" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C105" s="33" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D105" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E105" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F105" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G105" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="I105" s="33" t="inlineStr">
+        <is>
+          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B106" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C106" s="33" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D106" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E106" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F106" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G106" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="I106" s="33" t="inlineStr">
+        <is>
+          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B107" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C107" s="33" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D107" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E107" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F107" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G107" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="I107" s="33" t="inlineStr">
+        <is>
+          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B108" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C108" s="33" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D108" s="32" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E108" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F108" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G108" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="32" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I108" s="33" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B109" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C109" s="33" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D109" s="32" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E109" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F109" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G109" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="32" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I109" s="33" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C110" s="33" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D110" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E110" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F110" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G110" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="I110" s="33" t="inlineStr">
+        <is>
+          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B111" s="32" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C111" s="33" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D111" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E111" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F111" s="32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G111" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="32" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="I111" s="33" t="inlineStr">
+        <is>
+          <t>⏳ Awaiting Log-In / Log-Out Report</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -4364,7 +4364,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
@@ -8718,7 +8717,7 @@
       </c>
       <c r="D101" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>07:47 AM</t>
         </is>
       </c>
       <c r="E101" s="32" t="inlineStr">
@@ -8736,12 +8735,12 @@
       </c>
       <c r="H101" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I101" s="33" t="inlineStr">
         <is>
-          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8762,7 @@
       </c>
       <c r="D102" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>07:47 AM</t>
         </is>
       </c>
       <c r="E102" s="32" t="inlineStr">
@@ -8781,12 +8780,12 @@
       </c>
       <c r="H102" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I102" s="33" t="inlineStr">
         <is>
-          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8897,7 @@
       </c>
       <c r="D105" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>07:47 AM</t>
         </is>
       </c>
       <c r="E105" s="32" t="inlineStr">
@@ -8916,12 +8915,12 @@
       </c>
       <c r="H105" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I105" s="33" t="inlineStr">
         <is>
-          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8987,7 @@
       </c>
       <c r="D107" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>07:47 AM</t>
         </is>
       </c>
       <c r="E107" s="32" t="inlineStr">
@@ -9006,12 +9005,12 @@
       </c>
       <c r="H107" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I107" s="33" t="inlineStr">
         <is>
-          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9122,7 @@
       </c>
       <c r="D110" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>07:47 AM</t>
         </is>
       </c>
       <c r="E110" s="32" t="inlineStr">
@@ -9141,12 +9140,12 @@
       </c>
       <c r="H110" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I110" s="33" t="inlineStr">
         <is>
-          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9167,7 @@
       </c>
       <c r="D111" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>07:47 AM</t>
         </is>
       </c>
       <c r="E111" s="32" t="inlineStr">
@@ -9186,12 +9185,12 @@
       </c>
       <c r="H111" s="32" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -8509,21 +8509,21 @@
       </c>
       <c r="E96" s="28" t="inlineStr">
         <is>
-          <t>03:30 PM</t>
+          <t>08:00 PM</t>
         </is>
       </c>
       <c r="F96" s="28" t="inlineStr">
         <is>
-          <t>7h 40m</t>
+          <t>12h 10m</t>
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>7.67</v>
+        <v>12.17</v>
       </c>
       <c r="H96" s="28" t="n"/>
       <c r="I96" s="29" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 08:00 PM)</t>
         </is>
       </c>
     </row>
@@ -9284,16 +9284,16 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>74h 40m</t>
+          <t>76h 33m</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>159h 20m</t>
+          <t>161h 13m</t>
         </is>
       </c>
       <c r="F5" s="20" t="n">
-        <v>159.33</v>
+        <v>161.22</v>
       </c>
       <c r="G5" s="21" t="inlineStr">
         <is>
@@ -9317,16 +9317,16 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>69h 55m</t>
+          <t>70h 05m</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>144h 40m</t>
+          <t>144h 50m</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>144.67</v>
+        <v>144.83</v>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
@@ -9350,16 +9350,16 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>65h 45m</t>
+          <t>65h 55m</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>140h 45m</t>
+          <t>140h 55m</t>
         </is>
       </c>
       <c r="F7" s="20" t="n">
-        <v>140.75</v>
+        <v>140.92</v>
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
@@ -9416,16 +9416,16 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>63h 45m</t>
+          <t>65h 38m</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>134h 45m</t>
+          <t>136h 38m</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>134.75</v>
+        <v>136.63</v>
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
@@ -9449,16 +9449,16 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>63h 45m</t>
+          <t>68h 25m</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>131h 45m</t>
+          <t>136h 25m</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>131.75</v>
+        <v>136.42</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
@@ -9472,26 +9472,26 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>63h 30m</t>
+          <t>66h 40m</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>67h 15m</t>
+          <t>65h 38m</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>130h 45m</t>
+          <t>132h 18m</t>
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>130.75</v>
+        <v>132.3</v>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
@@ -9505,26 +9505,26 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>66h 40m</t>
+          <t>63h 30m</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>63h 45m</t>
+          <t>67h 15m</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>130h 25m</t>
+          <t>130h 45m</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>130.42</v>
+        <v>130.75</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
@@ -9581,16 +9581,16 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>61h 45m</t>
+          <t>61h 55m</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>123h 15m</t>
+          <t>123h 25m</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>123.25</v>
+        <v>123.42</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
@@ -9614,16 +9614,16 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>45h 42m</t>
+          <t>47h 35m</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>45h 42m</t>
+          <t>47h 35m</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>45.7</v>
+        <v>47.58</v>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -8523,7 +8523,7 @@
       <c r="H96" s="28" t="n"/>
       <c r="I96" s="29" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 08:00 PM)</t>
+          <t>✈️ Extended Duty (07:50 AM – 08:00 PM / 12h 05m) — ⚠️ Aircraft Technical Hazard: Fuel Leak Incident</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -8700,497 +8700,497 @@
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="32" t="inlineStr">
+      <c r="A101" s="20" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B101" s="32" t="inlineStr">
+      <c r="B101" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C101" s="33" t="inlineStr">
+      <c r="C101" s="21" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D101" s="32" t="inlineStr">
+      <c r="D101" s="20" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E101" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F101" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G101" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="32" t="inlineStr">
+      <c r="E101" s="20" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F101" s="20" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G101" s="20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H101" s="20" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I101" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
+      <c r="I101" s="21" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="32" t="inlineStr">
+      <c r="A102" s="28" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B102" s="32" t="inlineStr">
+      <c r="B102" s="28" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C102" s="33" t="inlineStr">
+      <c r="C102" s="29" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D102" s="32" t="inlineStr">
+      <c r="D102" s="28" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E102" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F102" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G102" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="32" t="inlineStr">
+      <c r="E102" s="28" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F102" s="28" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G102" s="28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H102" s="28" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I102" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
+      <c r="I102" s="29" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="32" t="inlineStr">
+      <c r="A103" s="20" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B103" s="32" t="inlineStr">
+      <c r="B103" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C103" s="33" t="inlineStr">
+      <c r="C103" s="21" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D103" s="32" t="inlineStr">
+      <c r="D103" s="20" t="inlineStr">
         <is>
           <t>03:30 AM</t>
         </is>
       </c>
-      <c r="E103" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F103" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G103" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="32" t="inlineStr">
+      <c r="E103" s="20" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F103" s="20" t="inlineStr">
+        <is>
+          <t>12h 05m</t>
+        </is>
+      </c>
+      <c r="G103" s="20" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H103" s="20" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I103" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Awaiting Checkout)</t>
+      <c r="I103" s="21" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="32" t="inlineStr">
+      <c r="A104" s="26" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B104" s="32" t="inlineStr">
+      <c r="B104" s="26" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C104" s="33" t="inlineStr">
+      <c r="C104" s="27" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D104" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E104" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F104" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G104" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="I104" s="33" t="inlineStr">
-        <is>
-          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+      <c r="D104" s="26" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E104" s="26" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F104" s="26" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G104" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="H104" s="26" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I104" s="27" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="32" t="inlineStr">
+      <c r="A105" s="20" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B105" s="32" t="inlineStr">
+      <c r="B105" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C105" s="33" t="inlineStr">
+      <c r="C105" s="21" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D105" s="32" t="inlineStr">
+      <c r="D105" s="20" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E105" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F105" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G105" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="32" t="inlineStr">
+      <c r="E105" s="20" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F105" s="20" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G105" s="20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H105" s="20" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I105" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
+      <c r="I105" s="21" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="32" t="inlineStr">
+      <c r="A106" s="26" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B106" s="32" t="inlineStr">
+      <c r="B106" s="26" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C106" s="33" t="inlineStr">
+      <c r="C106" s="27" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D106" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E106" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F106" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G106" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="I106" s="33" t="inlineStr">
-        <is>
-          <t>⏳ Awaiting Log-In / Log-Out Report</t>
+      <c r="D106" s="26" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E106" s="26" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F106" s="26" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G106" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="H106" s="26" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I106" s="27" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="32" t="inlineStr">
+      <c r="A107" s="20" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B107" s="32" t="inlineStr">
+      <c r="B107" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C107" s="33" t="inlineStr">
+      <c r="C107" s="21" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D107" s="32" t="inlineStr">
+      <c r="D107" s="20" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E107" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F107" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G107" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="32" t="inlineStr">
+      <c r="E107" s="20" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F107" s="20" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G107" s="20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H107" s="20" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I107" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
+      <c r="I107" s="21" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="32" t="inlineStr">
+      <c r="A108" s="28" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B108" s="32" t="inlineStr">
+      <c r="B108" s="28" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C108" s="33" t="inlineStr">
+      <c r="C108" s="29" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D108" s="32" t="inlineStr">
+      <c r="D108" s="28" t="inlineStr">
         <is>
           <t>03:30 AM</t>
         </is>
       </c>
-      <c r="E108" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F108" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G108" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="32" t="inlineStr">
+      <c r="E108" s="28" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F108" s="28" t="inlineStr">
+        <is>
+          <t>12h 05m</t>
+        </is>
+      </c>
+      <c r="G108" s="28" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H108" s="28" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I108" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Awaiting Checkout)</t>
+      <c r="I108" s="29" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="32" t="inlineStr">
+      <c r="A109" s="20" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B109" s="32" t="inlineStr">
+      <c r="B109" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C109" s="33" t="inlineStr">
+      <c r="C109" s="21" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D109" s="32" t="inlineStr">
+      <c r="D109" s="20" t="inlineStr">
         <is>
           <t>03:30 AM</t>
         </is>
       </c>
-      <c r="E109" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F109" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G109" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="32" t="inlineStr">
+      <c r="E109" s="20" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F109" s="20" t="inlineStr">
+        <is>
+          <t>12h 05m</t>
+        </is>
+      </c>
+      <c r="G109" s="20" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H109" s="20" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I109" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Awaiting Checkout)</t>
+      <c r="I109" s="21" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="32" t="inlineStr">
+      <c r="A110" s="28" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B110" s="32" t="inlineStr">
+      <c r="B110" s="28" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C110" s="33" t="inlineStr">
+      <c r="C110" s="29" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D110" s="32" t="inlineStr">
+      <c r="D110" s="28" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E110" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F110" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G110" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="32" t="inlineStr">
+      <c r="E110" s="28" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F110" s="28" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G110" s="28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H110" s="28" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I110" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
+      <c r="I110" s="29" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="32" t="inlineStr">
+      <c r="A111" s="20" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B111" s="32" t="inlineStr">
+      <c r="B111" s="20" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C111" s="33" t="inlineStr">
+      <c r="C111" s="21" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D111" s="32" t="inlineStr">
+      <c r="D111" s="20" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E111" s="32" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="F111" s="32" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G111" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="32" t="inlineStr">
+      <c r="E111" s="20" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F111" s="20" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G111" s="20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H111" s="20" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I111" s="33" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Awaiting Checkout)</t>
+      <c r="I111" s="21" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
@@ -9284,16 +9284,16 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>76h 33m</t>
+          <t>84h 21m</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>161h 13m</t>
+          <t>169h 01m</t>
         </is>
       </c>
       <c r="F5" s="20" t="n">
-        <v>161.22</v>
+        <v>169.02</v>
       </c>
       <c r="G5" s="21" t="inlineStr">
         <is>
@@ -9317,16 +9317,16 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>70h 05m</t>
+          <t>82h 10m</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>144h 50m</t>
+          <t>156h 55m</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>144.83</v>
+        <v>156.92</v>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
@@ -9350,16 +9350,16 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>65h 55m</t>
+          <t>78h 00m</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>140h 55m</t>
+          <t>153h 00m</t>
         </is>
       </c>
       <c r="F7" s="20" t="n">
-        <v>140.92</v>
+        <v>153</v>
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
@@ -9383,16 +9383,16 @@
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>63h 20m</t>
+          <t>75h 25m</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>137h 25m</t>
+          <t>149h 30m</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>137.42</v>
+        <v>149.5</v>
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
@@ -9416,16 +9416,16 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>65h 38m</t>
+          <t>73h 26m</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>136h 38m</t>
+          <t>144h 26m</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>136.63</v>
+        <v>144.43</v>
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
@@ -9449,16 +9449,16 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>68h 25m</t>
+          <t>76h 13m</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>136h 25m</t>
+          <t>144h 13m</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>136.42</v>
+        <v>144.22</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
@@ -9482,16 +9482,16 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>65h 38m</t>
+          <t>73h 26m</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>132h 18m</t>
+          <t>140h 06m</t>
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>132.3</v>
+        <v>140.1</v>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
@@ -9515,16 +9515,16 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>67h 15m</t>
+          <t>76h 15m</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>130h 45m</t>
+          <t>139h 45m</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>130.75</v>
+        <v>139.75</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
@@ -9548,16 +9548,16 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>70h 00m</t>
+          <t>79h 00m</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>123h 30m</t>
+          <t>132h 30m</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>123.5</v>
+        <v>132.5</v>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
@@ -9581,16 +9581,16 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>61h 55m</t>
+          <t>69h 43m</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>123h 25m</t>
+          <t>131h 13m</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>123.42</v>
+        <v>131.22</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
@@ -9614,16 +9614,16 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>47h 35m</t>
+          <t>55h 23m</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>47h 35m</t>
+          <t>55h 23m</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>47.58</v>
+        <v>55.38</v>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -3578,30 +3578,30 @@
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="E68" s="22" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="G68" s="22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="I68" s="23" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -4298,30 +4298,30 @@
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="E84" s="22" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="G84" s="22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H84" s="22" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="I84" s="23" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -4547,47 +4547,47 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E8" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F8" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I8" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -4637,47 +4637,47 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>07:45 AM</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>02:00 PM</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>6h 15m</t>
-        </is>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="H18" s="24" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="I18" s="25" t="inlineStr">
         <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -5122,12 +5122,12 @@
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -5447,47 +5447,47 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>8h 00m</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="I28" s="23" t="inlineStr">
-        <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I28" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -5537,47 +5537,47 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
-        <is>
-          <t>8h 00m</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="H30" s="22" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I30" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -5897,47 +5897,47 @@
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F38" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G38" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H38" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I38" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I38" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -5987,47 +5987,47 @@
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C40" s="27" t="inlineStr">
+      <c r="C40" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F40" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H40" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I40" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I40" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -6392,47 +6392,47 @@
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B49" s="24" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C49" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>8h 00m</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H49" s="20" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="I49" s="21" t="inlineStr">
-        <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I49" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -6482,47 +6482,47 @@
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="24" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B51" s="24" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C51" s="21" t="inlineStr">
+      <c r="C51" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E51" s="20" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F51" s="20" t="inlineStr">
-        <is>
-          <t>8h 00m</t>
-        </is>
-      </c>
-      <c r="G51" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H51" s="20" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="I51" s="21" t="inlineStr">
-        <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I51" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -6842,47 +6842,47 @@
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="26" t="inlineStr">
+      <c r="A59" s="24" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B59" s="26" t="inlineStr">
+      <c r="B59" s="24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C59" s="27" t="inlineStr">
+      <c r="C59" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D59" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E59" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F59" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G59" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H59" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I59" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I59" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -6932,47 +6932,47 @@
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="26" t="inlineStr">
+      <c r="A61" s="24" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B61" s="26" t="inlineStr">
+      <c r="B61" s="24" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C61" s="27" t="inlineStr">
+      <c r="C61" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D61" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E61" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F61" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G61" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H61" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I61" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I61" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -7562,92 +7562,92 @@
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="26" t="inlineStr">
+      <c r="A75" s="24" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B75" s="26" t="inlineStr">
+      <c r="B75" s="24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C75" s="27" t="inlineStr">
+      <c r="C75" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D75" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E75" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F75" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G75" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H75" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I75" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I75" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B76" s="26" t="inlineStr">
+      <c r="B76" s="24" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C76" s="27" t="inlineStr">
+      <c r="C76" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D76" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E76" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F76" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G76" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H76" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I76" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I76" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -8147,92 +8147,92 @@
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="26" t="inlineStr">
+      <c r="A88" s="24" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B88" s="26" t="inlineStr">
+      <c r="B88" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C88" s="27" t="inlineStr">
+      <c r="C88" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D88" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E88" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F88" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G88" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H88" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I88" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I88" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="26" t="inlineStr">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B89" s="26" t="inlineStr">
+      <c r="B89" s="24" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C89" s="27" t="inlineStr">
+      <c r="C89" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D89" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E89" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F89" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G89" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H89" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I89" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I89" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -8569,92 +8569,92 @@
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="26" t="inlineStr">
+      <c r="A98" s="24" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B98" s="26" t="inlineStr">
+      <c r="B98" s="24" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C98" s="27" t="inlineStr">
+      <c r="C98" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D98" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E98" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F98" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G98" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H98" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I98" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D98" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E98" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F98" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G98" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I98" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="A99" s="24" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B99" s="26" t="inlineStr">
+      <c r="B99" s="24" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C99" s="27" t="inlineStr">
+      <c r="C99" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D99" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E99" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F99" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G99" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H99" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I99" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D99" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E99" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F99" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G99" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I99" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -8835,47 +8835,47 @@
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="26" t="inlineStr">
+      <c r="A104" s="24" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B104" s="26" t="inlineStr">
+      <c r="B104" s="24" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C104" s="27" t="inlineStr">
+      <c r="C104" s="25" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D104" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E104" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F104" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G104" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H104" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I104" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D104" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E104" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F104" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G104" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I104" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -8925,47 +8925,47 @@
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="26" t="inlineStr">
+      <c r="A106" s="24" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B106" s="26" t="inlineStr">
+      <c r="B106" s="24" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C106" s="27" t="inlineStr">
+      <c r="C106" s="25" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D106" s="26" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E106" s="26" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F106" s="26" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G106" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H106" s="26" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="I106" s="27" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport ID Pass Delay - Company Paid)</t>
+      <c r="D106" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E106" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F106" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G106" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I106" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="G5" s="21" t="inlineStr">
         <is>
-          <t>Core Team / Station Shift Lead (08:16 AM)</t>
+          <t>Core Team / Station Duty</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Core Team / Dawn Flight Handling (03:15 AM)</t>
+          <t>Core Team / Station Duty</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>Core Team / Dawn Flight Handling (03:15 AM)</t>
+          <t>Core Team / Station Duty</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>Core Team / Morning Station Duty (07:15 AM)</t>
+          <t>Core Team / Station Duty</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>Core Team / Morning Station Duty (07:15 AM)</t>
+          <t>Core Team / Station Duty</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Core Team / Morning Station Duty (07:15 AM)</t>
+          <t>Core Team / Station Duty</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Core Team / Station Systems &amp; Ops (08:16 AM)</t>
+          <t>Core Team / Station Duty</t>
         </is>
       </c>
     </row>
@@ -9505,30 +9505,30 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Tarek Orfhly</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>63h 30m</t>
+          <t>61h 30m</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>76h 15m</t>
+          <t>69h 43m</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>139h 45m</t>
+          <t>131h 13m</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>139.75</v>
+        <v>131.22</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Core Team / Dawn Flight Handling (03:15 AM)</t>
+          <t>Core Team / Station Duty</t>
         </is>
       </c>
     </row>
@@ -9538,30 +9538,30 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>Talal</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>53h 30m</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>79h 00m</t>
+          <t>55h 23m</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>132h 30m</t>
+          <t>55h 23m</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>132.5</v>
+        <v>55.38</v>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Core Team / ID Delay - Paid Standby</t>
+          <t>Onboarding / Morning Duty</t>
         </is>
       </c>
     </row>
@@ -9571,30 +9571,30 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Tarek Orfhly</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>61h 30m</t>
+          <t>54h 30m</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>69h 43m</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>131h 13m</t>
+          <t>54h 30m</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>131.22</v>
+        <v>54.5</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Core Team / ID Delay - Paid Standby</t>
+          <t>Inactive / Terminated (Last Duty: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -9604,30 +9604,30 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Talal</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
+          <t>44h 30m</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>55h 23m</t>
-        </is>
-      </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>55h 23m</t>
+          <t>44h 30m</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>55.38</v>
+        <v>44.5</v>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Onboarding / Morning Station Duty (07:15 AM)</t>
+          <t>Inactive / Terminated (Last Duty: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
@@ -9639,30 +9639,30 @@
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>Total Team Output</t>
+          <t>Team Total Output</t>
         </is>
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>692h 40m</t>
+          <t>674h 40m</t>
         </is>
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>545h 15m</t>
+          <t>668h 07m</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>1,237h 55m</t>
+          <t>1342h 47m</t>
         </is>
       </c>
       <c r="F16" s="30" t="n">
-        <v>1237.92</v>
+        <v>1342.78</v>
       </c>
       <c r="G16" s="30" t="inlineStr">
         <is>
-          <t>Full Damascus Ground Station Roster</t>
+          <t>Full Damascus Ground Station Roster (Active &amp; Departed)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -4336,7 +4336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -9191,6 +9191,501 @@
       <c r="I111" s="21" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C112" s="25" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D112" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G112" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I112" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C113" s="25" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I113" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C114" s="25" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I114" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C115" s="25" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D115" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E115" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F115" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I115" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B116" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C116" s="25" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D116" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E116" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F116" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G116" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I116" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C117" s="25" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G117" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="24" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I117" s="25" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B118" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C118" s="25" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D118" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E118" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F118" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G118" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I118" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B119" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C119" s="25" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D119" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E119" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F119" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G119" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I119" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B120" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C120" s="25" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D120" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E120" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F120" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G120" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I120" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B121" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C121" s="25" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D121" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E121" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F121" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G121" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I121" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C122" s="25" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D122" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E122" s="24" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F122" s="24" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G122" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="24" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I122" s="25" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="September 2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="October 2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard &amp; Stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="00-STATION-PULSE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="September 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="October 2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard &amp; Stats" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +86,67 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00E0E6ED"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFC000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B365D"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00777777"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B365D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -147,6 +207,36 @@
         <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C4D75"/>
+        <bgColor rgb="002C4D75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4F8"/>
+        <bgColor rgb="00F0F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FBFD"/>
+        <bgColor rgb="00F9FBFD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -196,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -285,6 +375,111 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -650,6 +845,687 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>DAMASCUS INTERNATIONAL AIRPORT (DAM / OSDI) — STATION GROUND OPERATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Executive Shift Ledger, Attendance Pulse &amp; Duty Analytics (October 2026 Cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>Station Systems Admin: Omar Elnemr | Active Roster: 9 Staff | Audit Status: 100% VERIFIED | Data Engine: Hermes LLM Vault</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>1,180.3 HRS</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="n"/>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>511.9 HRS</t>
+        </is>
+      </c>
+      <c r="D5" s="38" t="n"/>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>9 ACTIVE</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>55.4 HRS</t>
+        </is>
+      </c>
+      <c r="G5" s="38" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>CUMULATIVE TEAM OUTPUT</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="n"/>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>OCTOBER ACTIVE CYCLE</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="39" t="inlineStr">
+        <is>
+          <t>STATION ROSTER</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="inlineStr">
+        <is>
+          <t>ONBOARDING TRACKER</t>
+        </is>
+      </c>
+      <c r="G6" s="38" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>Sep + Oct Total Delivered</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="n"/>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>7 Active Shifts Tracked</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="n"/>
+      <c r="E7" s="40" t="inlineStr">
+        <is>
+          <t>2 Departed / Inactive</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani Output</t>
+        </is>
+      </c>
+      <c r="G7" s="38" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>🏆 Executive Cumulative Hours Leaderboard (September &amp; October Cycles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Employee / Team Member</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="E10" s="42" t="inlineStr">
+        <is>
+          <t>Cumulative Output</t>
+        </is>
+      </c>
+      <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>Combined Decimal</t>
+        </is>
+      </c>
+      <c r="G10" s="43" t="inlineStr">
+        <is>
+          <t>Operating Duty Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>🥇 1</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>84h 40m</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>84h 21m</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>169h 01m</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="n">
+        <v>169.02</v>
+      </c>
+      <c r="G11" s="47" t="inlineStr">
+        <is>
+          <t>Core Team / Station Duty Lead (Dawn/Morning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t>🥈 2</t>
+        </is>
+      </c>
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>74h 45m</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>82h 10m</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="inlineStr">
+        <is>
+          <t>156h 55m</t>
+        </is>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>156.92</v>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>Core Team / Dawn Flight Handling (03:30 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t>🥉 3</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>75h 00m</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>78h 00m</t>
+        </is>
+      </c>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>153h 00m</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="n">
+        <v>153</v>
+      </c>
+      <c r="G13" s="55" t="inlineStr">
+        <is>
+          <t>Core Team / Dawn Flight Handling (03:30 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>74h 05m</t>
+        </is>
+      </c>
+      <c r="D14" s="58" t="inlineStr">
+        <is>
+          <t>75h 25m</t>
+        </is>
+      </c>
+      <c r="E14" s="56" t="inlineStr">
+        <is>
+          <t>149h 30m</t>
+        </is>
+      </c>
+      <c r="F14" s="56" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="G14" s="59" t="inlineStr">
+        <is>
+          <t>Core Team / Dawn Flight Handling (03:30 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" s="61" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>71h 00m</t>
+        </is>
+      </c>
+      <c r="D15" s="62" t="inlineStr">
+        <is>
+          <t>73h 26m</t>
+        </is>
+      </c>
+      <c r="E15" s="60" t="inlineStr">
+        <is>
+          <t>144h 26m</t>
+        </is>
+      </c>
+      <c r="F15" s="60" t="n">
+        <v>144.43</v>
+      </c>
+      <c r="G15" s="63" t="inlineStr">
+        <is>
+          <t>Core Team / Morning Station Duty (07:47 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="C16" s="58" t="inlineStr">
+        <is>
+          <t>68h 00m</t>
+        </is>
+      </c>
+      <c r="D16" s="58" t="inlineStr">
+        <is>
+          <t>76h 13m</t>
+        </is>
+      </c>
+      <c r="E16" s="56" t="inlineStr">
+        <is>
+          <t>144h 13m</t>
+        </is>
+      </c>
+      <c r="F16" s="56" t="n">
+        <v>144.22</v>
+      </c>
+      <c r="G16" s="59" t="inlineStr">
+        <is>
+          <t>Core Team / Morning Station Duty + Incident OT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="61" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="C17" s="62" t="inlineStr">
+        <is>
+          <t>66h 40m</t>
+        </is>
+      </c>
+      <c r="D17" s="62" t="inlineStr">
+        <is>
+          <t>73h 26m</t>
+        </is>
+      </c>
+      <c r="E17" s="60" t="inlineStr">
+        <is>
+          <t>140h 06m</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="G17" s="63" t="inlineStr">
+        <is>
+          <t>Core Team / Station Systems &amp; Ops (07:47 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="C18" s="58" t="inlineStr">
+        <is>
+          <t>61h 30m</t>
+        </is>
+      </c>
+      <c r="D18" s="58" t="inlineStr">
+        <is>
+          <t>69h 43m</t>
+        </is>
+      </c>
+      <c r="E18" s="56" t="inlineStr">
+        <is>
+          <t>131h 13m</t>
+        </is>
+      </c>
+      <c r="F18" s="56" t="n">
+        <v>131.22</v>
+      </c>
+      <c r="G18" s="59" t="inlineStr">
+        <is>
+          <t>Core Team / Daytime Station Duty (07:47 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="60" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="61" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="C19" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="62" t="inlineStr">
+        <is>
+          <t>55h 23m</t>
+        </is>
+      </c>
+      <c r="E19" s="60" t="inlineStr">
+        <is>
+          <t>55h 23m</t>
+        </is>
+      </c>
+      <c r="F19" s="60" t="n">
+        <v>55.38</v>
+      </c>
+      <c r="G19" s="63" t="inlineStr">
+        <is>
+          <t>Onboarding Staff / Morning Duty (07:47 AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="C20" s="64" t="inlineStr">
+        <is>
+          <t>54h 30m</t>
+        </is>
+      </c>
+      <c r="D20" s="64" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="E20" s="64" t="inlineStr">
+        <is>
+          <t>54h 30m</t>
+        </is>
+      </c>
+      <c r="F20" s="64" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="G20" s="65" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Departed (Last Duty: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="66" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="C21" s="66" t="inlineStr">
+        <is>
+          <t>44h 30m</t>
+        </is>
+      </c>
+      <c r="D21" s="66" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="E21" s="66" t="inlineStr">
+        <is>
+          <t>44h 30m</t>
+        </is>
+      </c>
+      <c r="F21" s="66" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G21" s="67" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Departed (Last Duty: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="68" t="inlineStr">
+        <is>
+          <t>🏆</t>
+        </is>
+      </c>
+      <c r="B22" s="69" t="inlineStr">
+        <is>
+          <t>Team Total Output</t>
+        </is>
+      </c>
+      <c r="C22" s="68" t="inlineStr">
+        <is>
+          <t>692h 40m</t>
+        </is>
+      </c>
+      <c r="D22" s="68" t="inlineStr">
+        <is>
+          <t>520h 30m</t>
+        </is>
+      </c>
+      <c r="E22" s="68" t="inlineStr">
+        <is>
+          <t>1,213h 10m</t>
+        </is>
+      </c>
+      <c r="F22" s="68" t="n">
+        <v>1213.17</v>
+      </c>
+      <c r="G22" s="69" t="inlineStr">
+        <is>
+          <t>Full Damascus Ground Operations Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>⚠️ Operational Incident &amp; Technical Hazard Log (October 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>Shift Type</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
+        <is>
+          <t>Extended Time</t>
+        </is>
+      </c>
+      <c r="E25" s="42" t="inlineStr">
+        <is>
+          <t>Incident Category</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="inlineStr">
+        <is>
+          <t>Operational Event &amp; Resolution</t>
+        </is>
+      </c>
+      <c r="G25" s="38" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>Daily Duty</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>07:50 AM → 08:00 PM (12h 05m)</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>Aircraft Hazard</t>
+        </is>
+      </c>
+      <c r="F26" s="70" t="inlineStr">
+        <is>
+          <t>Stayed on station due to aircraft technical malfunction (Fuel Leak Incident). Extended duty resolved safely.</t>
+        </is>
+      </c>
+      <c r="G26" s="38" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="F7:G7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F11:F21">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="170"/>
+        <color rgb="002C4D75"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4330,7 +5206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9694,7 +10570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,8 +145,84 @@
       <color rgb="00888888"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0094A3B8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="0094A3B8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="0094A3B8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00334155"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
@@ -237,8 +313,68 @@
         <bgColor rgb="00F9FBFD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000284C7"/>
+        <bgColor rgb="000284C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+        <bgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE4E6"/>
+        <bgColor rgb="00FFE4E6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -282,11 +418,72 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,6 +677,118 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -848,655 +1157,659 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>DAMASCUS INTERNATIONAL AIRPORT (DAM / OSDI) — STATION GROUND OPERATIONS</t>
+      <c r="A1" s="71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DAMASCUS INTERNATIONAL AIRPORT — STATION GROUND OPERATIONS</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
-        <is>
-          <t>Executive Shift Ledger, Attendance Pulse &amp; Duty Analytics (October 2026 Cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
-        <is>
-          <t>Station Systems Admin: Omar Elnemr | Active Roster: 9 Staff | Audit Status: 100% VERIFIED | Data Engine: Hermes LLM Vault</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
-        <is>
-          <t>1,180.3 HRS</t>
-        </is>
-      </c>
-      <c r="B5" s="38" t="n"/>
-      <c r="C5" s="37" t="inlineStr">
-        <is>
-          <t>511.9 HRS</t>
-        </is>
-      </c>
-      <c r="D5" s="38" t="n"/>
-      <c r="E5" s="37" t="inlineStr">
-        <is>
-          <t>9 ACTIVE</t>
-        </is>
-      </c>
-      <c r="F5" s="37" t="inlineStr">
-        <is>
-          <t>55.4 HRS</t>
-        </is>
-      </c>
-      <c r="G5" s="38" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>CUMULATIVE TEAM OUTPUT</t>
-        </is>
-      </c>
-      <c r="B6" s="38" t="n"/>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OPERATIONAL PULSE DASHBOARD  •  OCTOBER 2026 CYCLE  •  ADMIN: OMAR ELNEMR  •  SYSTEM: HERMES LLM VAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="3" customHeight="1">
+      <c r="A3" s="73" t="n"/>
+      <c r="B3" s="73" t="n"/>
+      <c r="C3" s="73" t="n"/>
+      <c r="D3" s="73" t="n"/>
+      <c r="E3" s="73" t="n"/>
+      <c r="F3" s="73" t="n"/>
+      <c r="G3" s="73" t="n"/>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="74" t="inlineStr">
+        <is>
+          <t>1,213.2h</t>
+        </is>
+      </c>
+      <c r="B5" s="75" t="n"/>
+      <c r="C5" s="74" t="inlineStr">
+        <is>
+          <t>520.5h</t>
+        </is>
+      </c>
+      <c r="D5" s="75" t="n"/>
+      <c r="E5" s="74" t="inlineStr">
+        <is>
+          <t>9 Active</t>
+        </is>
+      </c>
+      <c r="F5" s="74" t="inlineStr">
+        <is>
+          <t>55.4h</t>
+        </is>
+      </c>
+      <c r="G5" s="75" t="n"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="76" t="inlineStr">
+        <is>
+          <t>CUMULATIVE OUTPUT</t>
+        </is>
+      </c>
+      <c r="B6" s="75" t="n"/>
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>OCTOBER ACTIVE CYCLE</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="39" t="inlineStr">
+      <c r="D6" s="75" t="n"/>
+      <c r="E6" s="76" t="inlineStr">
         <is>
           <t>STATION ROSTER</t>
         </is>
       </c>
-      <c r="F6" s="39" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>ONBOARDING TRACKER</t>
         </is>
       </c>
-      <c r="G6" s="38" t="n"/>
+      <c r="G6" s="75" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>Sep + Oct Total Delivered</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n"/>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="B7" s="75" t="n"/>
+      <c r="C7" s="77" t="inlineStr">
         <is>
           <t>7 Active Shifts Tracked</t>
         </is>
       </c>
-      <c r="D7" s="38" t="n"/>
-      <c r="E7" s="40" t="inlineStr">
-        <is>
-          <t>2 Departed / Inactive</t>
-        </is>
-      </c>
-      <c r="F7" s="40" t="inlineStr">
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="77" t="inlineStr">
+        <is>
+          <t>● 100% Operational</t>
+        </is>
+      </c>
+      <c r="F7" s="77" t="inlineStr">
         <is>
           <t>Osama Alkabbani Output</t>
         </is>
       </c>
-      <c r="G7" s="38" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="41" t="inlineStr">
-        <is>
-          <t>🏆 Executive Cumulative Hours Leaderboard (September &amp; October Cycles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>Employee / Team Member</t>
-        </is>
-      </c>
-      <c r="C10" s="42" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="E10" s="42" t="inlineStr">
-        <is>
-          <t>Cumulative Output</t>
-        </is>
-      </c>
-      <c r="F10" s="42" t="inlineStr">
-        <is>
-          <t>Combined Decimal</t>
-        </is>
-      </c>
-      <c r="G10" s="43" t="inlineStr">
-        <is>
-          <t>Operating Duty Status</t>
+      <c r="G7" s="75" t="n"/>
+    </row>
+    <row r="8" ht="12" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="78" t="inlineStr">
+        <is>
+          <t>LEADERBOARD &amp; PERFORMANCE METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="79" t="inlineStr">
+        <is>
+          <t>RANK</t>
+        </is>
+      </c>
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>TEAM MEMBER</t>
+        </is>
+      </c>
+      <c r="C10" s="79" t="inlineStr">
+        <is>
+          <t>SEPTEMBER</t>
+        </is>
+      </c>
+      <c r="D10" s="79" t="inlineStr">
+        <is>
+          <t>OCTOBER</t>
+        </is>
+      </c>
+      <c r="E10" s="79" t="inlineStr">
+        <is>
+          <t>CUMULATIVE</t>
+        </is>
+      </c>
+      <c r="F10" s="79" t="inlineStr">
+        <is>
+          <t>DECIMAL HRS</t>
+        </is>
+      </c>
+      <c r="G10" s="80" t="inlineStr">
+        <is>
+          <t>STATUS / OPERATIONAL ROLE</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>🥇 1</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B11" s="82" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="83" t="inlineStr">
         <is>
           <t>84h 40m</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="83" t="inlineStr">
         <is>
           <t>84h 21m</t>
         </is>
       </c>
-      <c r="E11" s="44" t="inlineStr">
+      <c r="E11" s="81" t="inlineStr">
         <is>
           <t>169h 01m</t>
         </is>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="81" t="n">
         <v>169.02</v>
       </c>
-      <c r="G11" s="47" t="inlineStr">
-        <is>
-          <t>Core Team / Station Duty Lead (Dawn/Morning)</t>
+      <c r="G11" s="84" t="inlineStr">
+        <is>
+          <t>Core Team / Station Shift Lead (Dawn/Morning)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="48" t="inlineStr">
-        <is>
-          <t>🥈 2</t>
-        </is>
-      </c>
-      <c r="B12" s="49" t="inlineStr">
+      <c r="A12" s="85" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B12" s="86" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="C12" s="50" t="inlineStr">
+      <c r="C12" s="87" t="inlineStr">
         <is>
           <t>74h 45m</t>
         </is>
       </c>
-      <c r="D12" s="50" t="inlineStr">
+      <c r="D12" s="87" t="inlineStr">
         <is>
           <t>82h 10m</t>
         </is>
       </c>
-      <c r="E12" s="48" t="inlineStr">
+      <c r="E12" s="85" t="inlineStr">
         <is>
           <t>156h 55m</t>
         </is>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F12" s="85" t="n">
         <v>156.92</v>
       </c>
-      <c r="G12" s="51" t="inlineStr">
-        <is>
-          <t>Core Team / Dawn Flight Handling (03:30 AM)</t>
+      <c r="G12" s="88" t="inlineStr">
+        <is>
+          <t>Core Team / Dawn Departure Lead (03:30 AM)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="52" t="inlineStr">
-        <is>
-          <t>🥉 3</t>
-        </is>
-      </c>
-      <c r="B13" s="53" t="inlineStr">
+      <c r="A13" s="89" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B13" s="90" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="C13" s="54" t="inlineStr">
+      <c r="C13" s="91" t="inlineStr">
         <is>
           <t>75h 00m</t>
         </is>
       </c>
-      <c r="D13" s="54" t="inlineStr">
+      <c r="D13" s="91" t="inlineStr">
         <is>
           <t>78h 00m</t>
         </is>
       </c>
-      <c r="E13" s="52" t="inlineStr">
+      <c r="E13" s="89" t="inlineStr">
         <is>
           <t>153h 00m</t>
         </is>
       </c>
-      <c r="F13" s="52" t="n">
+      <c r="F13" s="89" t="n">
         <v>153</v>
       </c>
-      <c r="G13" s="55" t="inlineStr">
-        <is>
-          <t>Core Team / Dawn Flight Handling (03:30 AM)</t>
+      <c r="G13" s="92" t="inlineStr">
+        <is>
+          <t>Core Team / Dawn Departure Lead (03:30 AM)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B14" s="57" t="inlineStr">
+      <c r="A14" s="93" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="C14" s="58" t="inlineStr">
+      <c r="C14" s="95" t="inlineStr">
         <is>
           <t>74h 05m</t>
         </is>
       </c>
-      <c r="D14" s="58" t="inlineStr">
+      <c r="D14" s="95" t="inlineStr">
         <is>
           <t>75h 25m</t>
         </is>
       </c>
-      <c r="E14" s="56" t="inlineStr">
+      <c r="E14" s="93" t="inlineStr">
         <is>
           <t>149h 30m</t>
         </is>
       </c>
-      <c r="F14" s="56" t="n">
+      <c r="F14" s="93" t="n">
         <v>149.5</v>
       </c>
-      <c r="G14" s="59" t="inlineStr">
-        <is>
-          <t>Core Team / Dawn Flight Handling (03:30 AM)</t>
+      <c r="G14" s="96" t="inlineStr">
+        <is>
+          <t>Core Team / Dawn Departure Lead (03:30 AM)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="A15" s="97" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B15" s="98" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="99" t="inlineStr">
         <is>
           <t>71h 00m</t>
         </is>
       </c>
-      <c r="D15" s="62" t="inlineStr">
+      <c r="D15" s="99" t="inlineStr">
         <is>
           <t>73h 26m</t>
         </is>
       </c>
-      <c r="E15" s="60" t="inlineStr">
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>144h 26m</t>
         </is>
       </c>
-      <c r="F15" s="60" t="n">
+      <c r="F15" s="97" t="n">
         <v>144.43</v>
       </c>
-      <c r="G15" s="63" t="inlineStr">
+      <c r="G15" s="100" t="inlineStr">
         <is>
           <t>Core Team / Morning Station Duty (07:47 AM)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B16" s="57" t="inlineStr">
+      <c r="A16" s="93" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="C16" s="58" t="inlineStr">
+      <c r="C16" s="95" t="inlineStr">
         <is>
           <t>68h 00m</t>
         </is>
       </c>
-      <c r="D16" s="58" t="inlineStr">
+      <c r="D16" s="95" t="inlineStr">
         <is>
           <t>76h 13m</t>
         </is>
       </c>
-      <c r="E16" s="56" t="inlineStr">
+      <c r="E16" s="93" t="inlineStr">
         <is>
           <t>144h 13m</t>
         </is>
       </c>
-      <c r="F16" s="56" t="n">
+      <c r="F16" s="93" t="n">
         <v>144.22</v>
       </c>
-      <c r="G16" s="59" t="inlineStr">
+      <c r="G16" s="96" t="inlineStr">
         <is>
           <t>Core Team / Morning Station Duty + Incident OT</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="A17" s="97" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B17" s="98" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C17" s="99" t="inlineStr">
         <is>
           <t>66h 40m</t>
         </is>
       </c>
-      <c r="D17" s="62" t="inlineStr">
+      <c r="D17" s="99" t="inlineStr">
         <is>
           <t>73h 26m</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>140h 06m</t>
         </is>
       </c>
-      <c r="F17" s="60" t="n">
+      <c r="F17" s="97" t="n">
         <v>140.1</v>
       </c>
-      <c r="G17" s="63" t="inlineStr">
+      <c r="G17" s="100" t="inlineStr">
         <is>
           <t>Core Team / Station Systems &amp; Ops (07:47 AM)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B18" s="57" t="inlineStr">
+      <c r="A18" s="93" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="C18" s="58" t="inlineStr">
+      <c r="C18" s="95" t="inlineStr">
         <is>
           <t>61h 30m</t>
         </is>
       </c>
-      <c r="D18" s="58" t="inlineStr">
+      <c r="D18" s="95" t="inlineStr">
         <is>
           <t>69h 43m</t>
         </is>
       </c>
-      <c r="E18" s="56" t="inlineStr">
+      <c r="E18" s="93" t="inlineStr">
         <is>
           <t>131h 13m</t>
         </is>
       </c>
-      <c r="F18" s="56" t="n">
+      <c r="F18" s="93" t="n">
         <v>131.22</v>
       </c>
-      <c r="G18" s="59" t="inlineStr">
-        <is>
-          <t>Core Team / Daytime Station Duty (07:47 AM)</t>
+      <c r="G18" s="96" t="inlineStr">
+        <is>
+          <t>Core Team / Morning Station Duty (07:47 AM)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="A19" s="97" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B19" s="98" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C19" s="99" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="62" t="inlineStr">
+      <c r="D19" s="99" t="inlineStr">
         <is>
           <t>55h 23m</t>
         </is>
       </c>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>55h 23m</t>
         </is>
       </c>
-      <c r="F19" s="60" t="n">
+      <c r="F19" s="97" t="n">
         <v>55.38</v>
       </c>
-      <c r="G19" s="63" t="inlineStr">
+      <c r="G19" s="100" t="inlineStr">
         <is>
           <t>Onboarding Staff / Morning Duty (07:47 AM)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="64" t="inlineStr">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B20" s="65" t="inlineStr">
+      <c r="B20" s="102" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="C20" s="64" t="inlineStr">
+      <c r="C20" s="101" t="inlineStr">
         <is>
           <t>54h 30m</t>
         </is>
       </c>
-      <c r="D20" s="64" t="inlineStr">
+      <c r="D20" s="101" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="E20" s="64" t="inlineStr">
+      <c r="E20" s="101" t="inlineStr">
         <is>
           <t>54h 30m</t>
         </is>
       </c>
-      <c r="F20" s="64" t="n">
+      <c r="F20" s="101" t="n">
         <v>54.5</v>
       </c>
-      <c r="G20" s="65" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Departed (Last Duty: Sep 29, 2026)</t>
+      <c r="G20" s="102" t="inlineStr">
+        <is>
+          <t>● Inactive / Departed (Last Duty: Sep 29)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="66" t="inlineStr">
+      <c r="A21" s="103" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="67" t="inlineStr">
+      <c r="B21" s="104" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="C21" s="66" t="inlineStr">
+      <c r="C21" s="103" t="inlineStr">
         <is>
           <t>44h 30m</t>
         </is>
       </c>
-      <c r="D21" s="66" t="inlineStr">
+      <c r="D21" s="103" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="E21" s="66" t="inlineStr">
+      <c r="E21" s="103" t="inlineStr">
         <is>
           <t>44h 30m</t>
         </is>
       </c>
-      <c r="F21" s="66" t="n">
+      <c r="F21" s="103" t="n">
         <v>44.5</v>
       </c>
-      <c r="G21" s="67" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Departed (Last Duty: Sep 29, 2026)</t>
+      <c r="G21" s="104" t="inlineStr">
+        <is>
+          <t>● Inactive / Departed (Last Duty: Sep 29)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="68" t="inlineStr">
-        <is>
-          <t>🏆</t>
-        </is>
-      </c>
-      <c r="B22" s="69" t="inlineStr">
-        <is>
-          <t>Team Total Output</t>
-        </is>
-      </c>
-      <c r="C22" s="68" t="inlineStr">
+      <c r="A22" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B22" s="106" t="inlineStr">
+        <is>
+          <t>TOTAL TEAM OUTPUT</t>
+        </is>
+      </c>
+      <c r="C22" s="105" t="inlineStr">
         <is>
           <t>692h 40m</t>
         </is>
       </c>
-      <c r="D22" s="68" t="inlineStr">
+      <c r="D22" s="105" t="inlineStr">
         <is>
           <t>520h 30m</t>
         </is>
       </c>
-      <c r="E22" s="68" t="inlineStr">
+      <c r="E22" s="105" t="inlineStr">
         <is>
           <t>1,213h 10m</t>
         </is>
       </c>
-      <c r="F22" s="68" t="n">
+      <c r="F22" s="105" t="n">
         <v>1213.17</v>
       </c>
-      <c r="G22" s="69" t="inlineStr">
-        <is>
-          <t>Full Damascus Ground Operations Ledger</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="41" t="inlineStr">
-        <is>
-          <t>⚠️ Operational Incident &amp; Technical Hazard Log (October 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="inlineStr">
-        <is>
-          <t>Employee</t>
-        </is>
-      </c>
-      <c r="C25" s="42" t="inlineStr">
-        <is>
-          <t>Shift Type</t>
-        </is>
-      </c>
-      <c r="D25" s="42" t="inlineStr">
-        <is>
-          <t>Extended Time</t>
-        </is>
-      </c>
-      <c r="E25" s="42" t="inlineStr">
-        <is>
-          <t>Incident Category</t>
-        </is>
-      </c>
-      <c r="F25" s="43" t="inlineStr">
-        <is>
-          <t>Operational Event &amp; Resolution</t>
-        </is>
-      </c>
-      <c r="G25" s="38" t="n"/>
+      <c r="G22" s="106" t="inlineStr">
+        <is>
+          <t>Full Station Ground Operations Ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="78" t="inlineStr">
+        <is>
+          <t>INCIDENT &amp; OVERTIME EVENT LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="79" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="B25" s="80" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C25" s="79" t="inlineStr">
+        <is>
+          <t>SHIFT TYPE</t>
+        </is>
+      </c>
+      <c r="D25" s="79" t="inlineStr">
+        <is>
+          <t>EXTENDED TIME</t>
+        </is>
+      </c>
+      <c r="E25" s="79" t="inlineStr">
+        <is>
+          <t>INCIDENT CATEGORY</t>
+        </is>
+      </c>
+      <c r="F25" s="80" t="inlineStr">
+        <is>
+          <t>EVENT DESCRIPTION &amp; RESOLUTION</t>
+        </is>
+      </c>
+      <c r="G25" s="107" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="46" t="inlineStr">
+      <c r="A26" s="83" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B26" s="45" t="inlineStr">
+      <c r="B26" s="82" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="C26" s="83" t="inlineStr">
         <is>
           <t>Daily Duty</t>
         </is>
       </c>
-      <c r="D26" s="46" t="inlineStr">
+      <c r="D26" s="83" t="inlineStr">
         <is>
           <t>07:50 AM → 08:00 PM (12h 05m)</t>
         </is>
       </c>
-      <c r="E26" s="46" t="inlineStr">
+      <c r="E26" s="83" t="inlineStr">
         <is>
           <t>Aircraft Hazard</t>
         </is>
       </c>
-      <c r="F26" s="70" t="inlineStr">
-        <is>
-          <t>Stayed on station due to aircraft technical malfunction (Fuel Leak Incident). Extended duty resolved safely.</t>
-        </is>
-      </c>
-      <c r="G26" s="38" t="n"/>
+      <c r="F26" s="108" t="inlineStr">
+        <is>
+          <t>Remained on station due to aircraft fuel leak hazard. Overtime logged &amp; resolved.</t>
+        </is>
+      </c>
+      <c r="G26" s="107" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A3:G3"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
@@ -1512,7 +1825,7 @@
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="170"/>
-        <color rgb="002C4D75"/>
+        <color rgb="000284C7"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>
@@ -5227,5339 +5540,5339 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>Damascus Station — Airport Ground Operations Timesheet (October 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>Operating Cycle: Oct 01 – Ongoing | Live Airport Duty &amp; Training</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="79" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="79" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="79" t="inlineStr">
         <is>
           <t>Employee</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="79" t="inlineStr">
         <is>
           <t>Log_In</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="79" t="inlineStr">
         <is>
           <t>Log_Out</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="79" t="inlineStr">
         <is>
           <t>Duration_Formatted</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="79" t="inlineStr">
         <is>
           <t>Decimal_Hours</t>
         </is>
       </c>
-      <c r="H4" s="19" t="inlineStr">
+      <c r="H4" s="79" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="I4" s="79" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="99" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="100" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="99" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="99" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="99" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="100" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="95" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="95" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="96" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="95" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="95" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="95" t="n">
         <v>9</v>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="H6" s="95" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="I6" s="96" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="99" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="100" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="99" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="99" t="inlineStr">
         <is>
           <t>02:00 PM</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="99" t="inlineStr">
         <is>
           <t>6h 15m</t>
         </is>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="99" t="n">
         <v>6.25</v>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="99" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="100" t="inlineStr">
         <is>
           <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="99" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="100" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="99" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="99" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="H9" s="99" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="I9" s="100" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="111" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="111" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F10" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="24" t="inlineStr">
+      <c r="H10" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="99" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="100" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="99" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="99" t="inlineStr">
         <is>
           <t>02:00 PM</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="99" t="inlineStr">
         <is>
           <t>6h 15m</t>
         </is>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="99" t="n">
         <v>6.25</v>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="99" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="100" t="inlineStr">
         <is>
           <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="95" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="95" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="96" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="95" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="95" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="95" t="n">
         <v>9</v>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H12" s="95" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="I12" s="96" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="99" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="100" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="99" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="99" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="99" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="I13" s="100" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="95" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="95" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="96" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="95" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="95" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="95" t="n">
         <v>9</v>
       </c>
-      <c r="H14" s="26" t="inlineStr">
+      <c r="H14" s="95" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="96" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="112" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F15" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="24" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="I15" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="112" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="F16" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="24" t="inlineStr">
+      <c r="H16" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="112" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="24" t="inlineStr">
+      <c r="H17" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F18" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="24" t="inlineStr">
+      <c r="H18" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="I18" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="112" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="24" t="inlineStr">
+      <c r="H19" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I19" s="25" t="inlineStr">
+      <c r="I19" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F20" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="24" t="inlineStr">
+      <c r="H20" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I20" s="25" t="inlineStr">
+      <c r="I20" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="C21" s="112" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr">
+      <c r="F21" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G21" s="24" t="n">
+      <c r="G21" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="24" t="inlineStr">
+      <c r="H21" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I21" s="25" t="inlineStr">
+      <c r="I21" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="112" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F22" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G22" s="24" t="n">
+      <c r="G22" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="24" t="inlineStr">
+      <c r="H22" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I22" s="25" t="inlineStr">
+      <c r="I22" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C23" s="112" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="F23" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G23" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="111" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="112" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F24" s="24" t="inlineStr">
+      <c r="F24" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="24" t="inlineStr">
+      <c r="H24" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I24" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="99" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="100" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="99" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="H25" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="95" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="95" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="96" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="95" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G26" s="22" t="n">
+      <c r="G26" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I26" s="23" t="inlineStr">
+      <c r="I26" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="99" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="100" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="99" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G27" s="20" t="n">
+      <c r="G27" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="H27" s="20" t="inlineStr">
+      <c r="H27" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="111" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="111" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F28" s="24" t="inlineStr">
+      <c r="F28" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G28" s="24" t="n">
+      <c r="G28" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="24" t="inlineStr">
+      <c r="H28" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I28" s="25" t="inlineStr">
+      <c r="I28" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="99" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="100" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="99" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G29" s="20" t="n">
+      <c r="G29" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="H29" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I29" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="111" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="111" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="F30" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G30" s="24" t="n">
+      <c r="G30" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="24" t="inlineStr">
+      <c r="H30" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I30" s="25" t="inlineStr">
+      <c r="I30" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="99" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="100" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="99" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G31" s="20" t="n">
+      <c r="G31" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="H31" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="95" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="95" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="96" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="95" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G32" s="22" t="n">
+      <c r="G32" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="I32" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="99" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="100" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="99" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G33" s="20" t="n">
+      <c r="G33" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="H33" s="20" t="inlineStr">
+      <c r="H33" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
+      <c r="I33" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="95" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="95" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="96" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="95" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G34" s="22" t="n">
+      <c r="G34" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I34" s="23" t="inlineStr">
+      <c r="I34" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="99" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="99" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="100" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D35" s="99" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="F35" s="99" t="inlineStr">
         <is>
           <t>8h 15m</t>
         </is>
       </c>
-      <c r="G35" s="20" t="n">
+      <c r="G35" s="99" t="n">
         <v>8.25</v>
       </c>
-      <c r="H35" s="20" t="inlineStr">
+      <c r="H35" s="99" t="inlineStr">
         <is>
           <t>Paid Shift</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="I35" s="100" t="inlineStr">
         <is>
           <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="95" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="95" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="96" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="95" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="95" t="inlineStr">
         <is>
           <t>8h 15m</t>
         </is>
       </c>
-      <c r="G36" s="22" t="n">
+      <c r="G36" s="95" t="n">
         <v>8.25</v>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="95" t="inlineStr">
         <is>
           <t>Paid Shift</t>
         </is>
       </c>
-      <c r="I36" s="23" t="inlineStr">
+      <c r="I36" s="96" t="inlineStr">
         <is>
           <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="26" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="99" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B37" s="99" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C37" s="27" t="inlineStr">
+      <c r="C37" s="100" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D37" s="99" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E37" s="26" t="inlineStr">
+      <c r="E37" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
+      <c r="F37" s="99" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G37" s="26" t="n">
+      <c r="G37" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="H37" s="26" t="inlineStr">
+      <c r="H37" s="99" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I37" s="27" t="inlineStr">
+      <c r="I37" s="100" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="111" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C38" s="25" t="inlineStr">
+      <c r="C38" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F38" s="24" t="inlineStr">
+      <c r="F38" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G38" s="24" t="n">
+      <c r="G38" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="24" t="inlineStr">
+      <c r="H38" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I38" s="25" t="inlineStr">
+      <c r="I38" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="26" t="inlineStr">
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="99" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
+      <c r="B39" s="99" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C39" s="27" t="inlineStr">
+      <c r="C39" s="100" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D39" s="99" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
+      <c r="E39" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="F39" s="99" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G39" s="26" t="n">
+      <c r="G39" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="H39" s="26" t="inlineStr">
+      <c r="H39" s="99" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I39" s="27" t="inlineStr">
+      <c r="I39" s="100" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="111" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B40" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C40" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D40" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E40" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F40" s="24" t="inlineStr">
+      <c r="F40" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G40" s="24" t="n">
+      <c r="G40" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="24" t="inlineStr">
+      <c r="H40" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I40" s="25" t="inlineStr">
+      <c r="I40" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="26" t="inlineStr">
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="99" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B41" s="99" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C41" s="27" t="inlineStr">
+      <c r="C41" s="100" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="D41" s="99" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E41" s="26" t="inlineStr">
+      <c r="E41" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="F41" s="99" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G41" s="26" t="n">
+      <c r="G41" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="H41" s="26" t="inlineStr">
+      <c r="H41" s="99" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="I41" s="27" t="inlineStr">
+      <c r="I41" s="100" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="95" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B42" s="95" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="96" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="95" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E42" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="95" t="inlineStr">
         <is>
           <t>8h 15m</t>
         </is>
       </c>
-      <c r="G42" s="22" t="n">
+      <c r="G42" s="95" t="n">
         <v>8.25</v>
       </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="H42" s="95" t="inlineStr">
         <is>
           <t>Paid Shift</t>
         </is>
       </c>
-      <c r="I42" s="23" t="inlineStr">
+      <c r="I42" s="96" t="inlineStr">
         <is>
           <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="99" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="99" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="C43" s="100" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="D43" s="99" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E43" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="F43" s="99" t="inlineStr">
         <is>
           <t>8h 15m</t>
         </is>
       </c>
-      <c r="G43" s="20" t="n">
+      <c r="G43" s="99" t="n">
         <v>8.25</v>
       </c>
-      <c r="H43" s="20" t="inlineStr">
+      <c r="H43" s="99" t="inlineStr">
         <is>
           <t>Paid Shift</t>
         </is>
       </c>
-      <c r="I43" s="21" t="inlineStr">
+      <c r="I43" s="100" t="inlineStr">
         <is>
           <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="22" t="inlineStr">
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="95" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B44" s="22" t="inlineStr">
+      <c r="B44" s="95" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="96" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D44" s="22" t="inlineStr">
+      <c r="D44" s="95" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E44" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F44" s="22" t="inlineStr">
+      <c r="F44" s="95" t="inlineStr">
         <is>
           <t>8h 15m</t>
         </is>
       </c>
-      <c r="G44" s="22" t="n">
+      <c r="G44" s="95" t="n">
         <v>8.25</v>
       </c>
-      <c r="H44" s="22" t="inlineStr">
+      <c r="H44" s="95" t="inlineStr">
         <is>
           <t>Paid Shift</t>
         </is>
       </c>
-      <c r="I44" s="23" t="inlineStr">
+      <c r="I44" s="96" t="inlineStr">
         <is>
           <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="99" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="99" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C45" s="100" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D45" s="99" t="inlineStr">
         <is>
           <t>08:48 AM</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E45" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="F45" s="99" t="inlineStr">
         <is>
           <t>7h 12m</t>
         </is>
       </c>
-      <c r="G45" s="20" t="n">
+      <c r="G45" s="99" t="n">
         <v>7.2</v>
       </c>
-      <c r="H45" s="20" t="inlineStr">
+      <c r="H45" s="99" t="inlineStr">
         <is>
           <t>Paid Shift</t>
         </is>
       </c>
-      <c r="I45" s="21" t="inlineStr">
+      <c r="I45" s="100" t="inlineStr">
         <is>
           <t>🏢 Airport Onboarding Shift / Logged in 08:48 AM (7h 12m)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="95" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B46" s="95" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="96" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D46" s="22" t="inlineStr">
+      <c r="D46" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E46" s="22" t="inlineStr">
+      <c r="E46" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F46" s="22" t="inlineStr">
+      <c r="F46" s="95" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G46" s="22" t="n">
+      <c r="G46" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="H46" s="22" t="inlineStr">
+      <c r="H46" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I46" s="23" t="inlineStr">
+      <c r="I46" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="99" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="99" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C47" s="21" t="inlineStr">
+      <c r="C47" s="100" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D47" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E47" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F47" s="99" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G47" s="20" t="n">
+      <c r="G47" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="H47" s="20" t="inlineStr">
+      <c r="H47" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I47" s="21" t="inlineStr">
+      <c r="I47" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="95" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="95" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
+      <c r="C48" s="96" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D48" s="22" t="inlineStr">
+      <c r="D48" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E48" s="22" t="inlineStr">
+      <c r="E48" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F48" s="95" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G48" s="22" t="n">
+      <c r="G48" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="H48" s="22" t="inlineStr">
+      <c r="H48" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I48" s="23" t="inlineStr">
+      <c r="I48" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="111" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B49" s="111" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C49" s="25" t="inlineStr">
+      <c r="C49" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D49" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E49" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F49" s="24" t="inlineStr">
+      <c r="F49" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G49" s="24" t="n">
+      <c r="G49" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="24" t="inlineStr">
+      <c r="H49" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I49" s="25" t="inlineStr">
+      <c r="I49" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="22" t="inlineStr">
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="95" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
+      <c r="B50" s="95" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="96" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D50" s="22" t="inlineStr">
+      <c r="D50" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E50" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F50" s="22" t="inlineStr">
+      <c r="F50" s="95" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G50" s="22" t="n">
+      <c r="G50" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="H50" s="22" t="inlineStr">
+      <c r="H50" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I50" s="23" t="inlineStr">
+      <c r="I50" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="24" t="inlineStr">
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="111" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B51" s="24" t="inlineStr">
+      <c r="B51" s="111" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C51" s="25" t="inlineStr">
+      <c r="C51" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="D51" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F51" s="24" t="inlineStr">
+      <c r="F51" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G51" s="24" t="n">
+      <c r="G51" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="24" t="inlineStr">
+      <c r="H51" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I51" s="25" t="inlineStr">
+      <c r="I51" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="95" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B52" s="95" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="96" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D52" s="22" t="inlineStr">
+      <c r="D52" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E52" s="22" t="inlineStr">
+      <c r="E52" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F52" s="22" t="inlineStr">
+      <c r="F52" s="95" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G52" s="22" t="n">
+      <c r="G52" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="H52" s="22" t="inlineStr">
+      <c r="H52" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I52" s="23" t="inlineStr">
+      <c r="I52" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="99" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B53" s="99" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
+      <c r="C53" s="100" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="D53" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E53" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="F53" s="99" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G53" s="20" t="n">
+      <c r="G53" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="H53" s="20" t="inlineStr">
+      <c r="H53" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I53" s="21" t="inlineStr">
+      <c r="I53" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="95" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B54" s="22" t="inlineStr">
+      <c r="B54" s="95" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C54" s="96" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D54" s="22" t="inlineStr">
+      <c r="D54" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E54" s="22" t="inlineStr">
+      <c r="E54" s="95" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F54" s="22" t="inlineStr">
+      <c r="F54" s="95" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G54" s="22" t="n">
+      <c r="G54" s="95" t="n">
         <v>8</v>
       </c>
-      <c r="H54" s="22" t="inlineStr">
+      <c r="H54" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I54" s="23" t="inlineStr">
+      <c r="I54" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="99" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B55" s="99" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C55" s="21" t="inlineStr">
+      <c r="C55" s="100" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr">
+      <c r="D55" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="E55" s="99" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="F55" s="99" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="G55" s="20" t="n">
+      <c r="G55" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="H55" s="20" t="inlineStr">
+      <c r="H55" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I55" s="21" t="inlineStr">
+      <c r="I55" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="22" t="inlineStr">
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="95" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B56" s="22" t="inlineStr">
+      <c r="B56" s="95" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="96" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D56" s="22" t="inlineStr">
+      <c r="D56" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E56" s="22" t="inlineStr">
+      <c r="E56" s="95" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="F56" s="22" t="inlineStr">
+      <c r="F56" s="95" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="G56" s="22" t="n">
+      <c r="G56" s="95" t="n">
         <v>8.08</v>
       </c>
-      <c r="H56" s="22" t="inlineStr">
+      <c r="H56" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I56" s="23" t="inlineStr">
+      <c r="I56" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="99" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B57" s="99" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C57" s="21" t="inlineStr">
+      <c r="C57" s="100" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="D57" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="E57" s="99" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="F57" s="99" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="G57" s="20" t="n">
+      <c r="G57" s="99" t="n">
         <v>8.08</v>
       </c>
-      <c r="H57" s="20" t="inlineStr">
+      <c r="H57" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I57" s="21" t="inlineStr">
+      <c r="I57" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="22" t="inlineStr">
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="95" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B58" s="22" t="inlineStr">
+      <c r="B58" s="95" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
+      <c r="C58" s="96" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D58" s="22" t="inlineStr">
+      <c r="D58" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E58" s="22" t="inlineStr">
+      <c r="E58" s="95" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="F58" s="95" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="G58" s="22" t="n">
+      <c r="G58" s="95" t="n">
         <v>8.08</v>
       </c>
-      <c r="H58" s="22" t="inlineStr">
+      <c r="H58" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I58" s="23" t="inlineStr">
+      <c r="I58" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="111" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B59" s="24" t="inlineStr">
+      <c r="B59" s="111" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C59" s="25" t="inlineStr">
+      <c r="C59" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="D59" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="E59" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F59" s="24" t="inlineStr">
+      <c r="F59" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G59" s="24" t="n">
+      <c r="G59" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="24" t="inlineStr">
+      <c r="H59" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I59" s="25" t="inlineStr">
+      <c r="I59" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="22" t="inlineStr">
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="95" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B60" s="22" t="inlineStr">
+      <c r="B60" s="95" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C60" s="23" t="inlineStr">
+      <c r="C60" s="96" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D60" s="22" t="inlineStr">
+      <c r="D60" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E60" s="22" t="inlineStr">
+      <c r="E60" s="95" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="F60" s="22" t="inlineStr">
+      <c r="F60" s="95" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="G60" s="22" t="n">
+      <c r="G60" s="95" t="n">
         <v>8.08</v>
       </c>
-      <c r="H60" s="22" t="inlineStr">
+      <c r="H60" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I60" s="23" t="inlineStr">
+      <c r="I60" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="111" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="B61" s="111" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C61" s="25" t="inlineStr">
+      <c r="C61" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D61" s="24" t="inlineStr">
+      <c r="D61" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E61" s="24" t="inlineStr">
+      <c r="E61" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F61" s="24" t="inlineStr">
+      <c r="F61" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G61" s="24" t="n">
+      <c r="G61" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="24" t="inlineStr">
+      <c r="H61" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I61" s="25" t="inlineStr">
+      <c r="I61" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="22" t="inlineStr">
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="95" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B62" s="22" t="inlineStr">
+      <c r="B62" s="95" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C62" s="23" t="inlineStr">
+      <c r="C62" s="96" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D62" s="22" t="inlineStr">
+      <c r="D62" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E62" s="22" t="inlineStr">
+      <c r="E62" s="95" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="F62" s="22" t="inlineStr">
+      <c r="F62" s="95" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="G62" s="22" t="n">
+      <c r="G62" s="95" t="n">
         <v>8.08</v>
       </c>
-      <c r="H62" s="22" t="inlineStr">
+      <c r="H62" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I62" s="23" t="inlineStr">
+      <c r="I62" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="20" t="inlineStr">
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="99" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B63" s="20" t="inlineStr">
+      <c r="B63" s="99" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C63" s="21" t="inlineStr">
+      <c r="C63" s="100" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D63" s="20" t="inlineStr">
+      <c r="D63" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E63" s="20" t="inlineStr">
+      <c r="E63" s="99" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="F63" s="99" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="G63" s="20" t="n">
+      <c r="G63" s="99" t="n">
         <v>8.08</v>
       </c>
-      <c r="H63" s="20" t="inlineStr">
+      <c r="H63" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I63" s="21" t="inlineStr">
+      <c r="I63" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="22" t="inlineStr">
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="95" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B64" s="22" t="inlineStr">
+      <c r="B64" s="95" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C64" s="23" t="inlineStr">
+      <c r="C64" s="96" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D64" s="22" t="inlineStr">
+      <c r="D64" s="95" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E64" s="22" t="inlineStr">
+      <c r="E64" s="95" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="F64" s="22" t="inlineStr">
+      <c r="F64" s="95" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="G64" s="22" t="n">
+      <c r="G64" s="95" t="n">
         <v>8.08</v>
       </c>
-      <c r="H64" s="22" t="inlineStr">
+      <c r="H64" s="95" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I64" s="23" t="inlineStr">
+      <c r="I64" s="96" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="20" t="inlineStr">
+    <row r="65" ht="19" customHeight="1">
+      <c r="A65" s="99" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B65" s="20" t="inlineStr">
+      <c r="B65" s="99" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C65" s="21" t="inlineStr">
+      <c r="C65" s="100" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D65" s="20" t="inlineStr">
+      <c r="D65" s="99" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E65" s="20" t="inlineStr">
+      <c r="E65" s="99" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="F65" s="20" t="inlineStr">
+      <c r="F65" s="99" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="G65" s="20" t="n">
+      <c r="G65" s="99" t="n">
         <v>8.08</v>
       </c>
-      <c r="H65" s="20" t="inlineStr">
+      <c r="H65" s="99" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="I65" s="21" t="inlineStr">
+      <c r="I65" s="100" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="22" t="inlineStr">
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="95" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B66" s="22" t="inlineStr">
+      <c r="B66" s="95" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C66" s="23" t="inlineStr">
+      <c r="C66" s="96" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D66" s="22" t="inlineStr">
+      <c r="D66" s="95" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="E66" s="22" t="inlineStr">
+      <c r="E66" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F66" s="22" t="inlineStr">
+      <c r="F66" s="95" t="inlineStr">
         <is>
           <t>7h 25m</t>
         </is>
       </c>
-      <c r="G66" s="22" t="n">
+      <c r="G66" s="95" t="n">
         <v>7.42</v>
       </c>
-      <c r="H66" s="22" t="inlineStr">
+      <c r="H66" s="95" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I66" s="23" t="inlineStr">
+      <c r="I66" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="20" t="inlineStr">
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="99" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B67" s="99" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C67" s="21" t="inlineStr">
+      <c r="C67" s="100" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="D67" s="99" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="E67" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F67" s="20" t="inlineStr">
+      <c r="F67" s="99" t="inlineStr">
         <is>
           <t>7h 25m</t>
         </is>
       </c>
-      <c r="G67" s="20" t="n">
+      <c r="G67" s="99" t="n">
         <v>7.42</v>
       </c>
-      <c r="H67" s="20" t="inlineStr">
+      <c r="H67" s="99" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I67" s="21" t="inlineStr">
+      <c r="I67" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="22" t="inlineStr">
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="95" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B68" s="22" t="inlineStr">
+      <c r="B68" s="95" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C68" s="23" t="inlineStr">
+      <c r="C68" s="96" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D68" s="22" t="inlineStr">
+      <c r="D68" s="95" t="inlineStr">
         <is>
           <t>03:55 AM</t>
         </is>
       </c>
-      <c r="E68" s="22" t="inlineStr">
+      <c r="E68" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F68" s="22" t="inlineStr">
+      <c r="F68" s="95" t="inlineStr">
         <is>
           <t>11h 25m</t>
         </is>
       </c>
-      <c r="G68" s="22" t="n">
+      <c r="G68" s="95" t="n">
         <v>11.42</v>
       </c>
-      <c r="H68" s="22" t="inlineStr">
+      <c r="H68" s="95" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I68" s="23" t="inlineStr">
+      <c r="I68" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="20" t="inlineStr">
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="99" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B69" s="20" t="inlineStr">
+      <c r="B69" s="99" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C69" s="21" t="inlineStr">
+      <c r="C69" s="100" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D69" s="20" t="inlineStr">
+      <c r="D69" s="99" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="E69" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="F69" s="99" t="inlineStr">
         <is>
           <t>7h 25m</t>
         </is>
       </c>
-      <c r="G69" s="20" t="n">
+      <c r="G69" s="99" t="n">
         <v>7.42</v>
       </c>
-      <c r="H69" s="20" t="inlineStr">
+      <c r="H69" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I69" s="21" t="inlineStr">
+      <c r="I69" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="22" t="inlineStr">
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="95" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B70" s="22" t="inlineStr">
+      <c r="B70" s="95" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C70" s="23" t="inlineStr">
+      <c r="C70" s="96" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D70" s="22" t="inlineStr">
+      <c r="D70" s="95" t="inlineStr">
         <is>
           <t>03:55 AM</t>
         </is>
       </c>
-      <c r="E70" s="22" t="inlineStr">
+      <c r="E70" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F70" s="22" t="inlineStr">
+      <c r="F70" s="95" t="inlineStr">
         <is>
           <t>11h 25m</t>
         </is>
       </c>
-      <c r="G70" s="22" t="n">
+      <c r="G70" s="95" t="n">
         <v>11.42</v>
       </c>
-      <c r="H70" s="22" t="inlineStr">
+      <c r="H70" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I70" s="23" t="inlineStr">
+      <c r="I70" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
+    <row r="71" ht="19" customHeight="1">
+      <c r="A71" s="99" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B71" s="20" t="inlineStr">
+      <c r="B71" s="99" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C71" s="21" t="inlineStr">
+      <c r="C71" s="100" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D71" s="20" t="inlineStr">
+      <c r="D71" s="99" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="E71" s="20" t="inlineStr">
+      <c r="E71" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F71" s="20" t="inlineStr">
+      <c r="F71" s="99" t="inlineStr">
         <is>
           <t>7h 25m</t>
         </is>
       </c>
-      <c r="G71" s="20" t="n">
+      <c r="G71" s="99" t="n">
         <v>7.42</v>
       </c>
-      <c r="H71" s="20" t="inlineStr">
+      <c r="H71" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I71" s="21" t="inlineStr">
+      <c r="I71" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="22" t="inlineStr">
+    <row r="72" ht="19" customHeight="1">
+      <c r="A72" s="95" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B72" s="22" t="inlineStr">
+      <c r="B72" s="95" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C72" s="23" t="inlineStr">
+      <c r="C72" s="96" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D72" s="22" t="inlineStr">
+      <c r="D72" s="95" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="E72" s="22" t="inlineStr">
+      <c r="E72" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F72" s="22" t="inlineStr">
+      <c r="F72" s="95" t="inlineStr">
         <is>
           <t>7h 25m</t>
         </is>
       </c>
-      <c r="G72" s="22" t="n">
+      <c r="G72" s="95" t="n">
         <v>7.42</v>
       </c>
-      <c r="H72" s="22" t="inlineStr">
+      <c r="H72" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I72" s="23" t="inlineStr">
+      <c r="I72" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
+    <row r="73" ht="19" customHeight="1">
+      <c r="A73" s="99" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B73" s="20" t="inlineStr">
+      <c r="B73" s="99" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C73" s="21" t="inlineStr">
+      <c r="C73" s="100" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D73" s="20" t="inlineStr">
+      <c r="D73" s="99" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="E73" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
+      <c r="F73" s="99" t="inlineStr">
         <is>
           <t>7h 25m</t>
         </is>
       </c>
-      <c r="G73" s="20" t="n">
+      <c r="G73" s="99" t="n">
         <v>7.42</v>
       </c>
-      <c r="H73" s="20" t="inlineStr">
+      <c r="H73" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I73" s="21" t="inlineStr">
+      <c r="I73" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="22" t="inlineStr">
+    <row r="74" ht="19" customHeight="1">
+      <c r="A74" s="95" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B74" s="22" t="inlineStr">
+      <c r="B74" s="95" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C74" s="23" t="inlineStr">
+      <c r="C74" s="96" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D74" s="22" t="inlineStr">
+      <c r="D74" s="95" t="inlineStr">
         <is>
           <t>03:55 AM</t>
         </is>
       </c>
-      <c r="E74" s="22" t="inlineStr">
+      <c r="E74" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F74" s="22" t="inlineStr">
+      <c r="F74" s="95" t="inlineStr">
         <is>
           <t>11h 25m</t>
         </is>
       </c>
-      <c r="G74" s="22" t="n">
+      <c r="G74" s="95" t="n">
         <v>11.42</v>
       </c>
-      <c r="H74" s="22" t="inlineStr">
+      <c r="H74" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I74" s="23" t="inlineStr">
+      <c r="I74" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Airport Ground Station Duty (Logged in 03:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="24" t="inlineStr">
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="111" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B75" s="24" t="inlineStr">
+      <c r="B75" s="111" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C75" s="25" t="inlineStr">
+      <c r="C75" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D75" s="24" t="inlineStr">
+      <c r="D75" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E75" s="24" t="inlineStr">
+      <c r="E75" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F75" s="24" t="inlineStr">
+      <c r="F75" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G75" s="24" t="n">
+      <c r="G75" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="24" t="inlineStr">
+      <c r="H75" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I75" s="25" t="inlineStr">
+      <c r="I75" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="24" t="inlineStr">
+    <row r="76" ht="19" customHeight="1">
+      <c r="A76" s="111" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B76" s="24" t="inlineStr">
+      <c r="B76" s="111" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C76" s="25" t="inlineStr">
+      <c r="C76" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D76" s="24" t="inlineStr">
+      <c r="D76" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E76" s="24" t="inlineStr">
+      <c r="E76" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F76" s="24" t="inlineStr">
+      <c r="F76" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G76" s="24" t="n">
+      <c r="G76" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="24" t="inlineStr">
+      <c r="H76" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I76" s="25" t="inlineStr">
+      <c r="I76" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="20" t="inlineStr">
+    <row r="77" ht="19" customHeight="1">
+      <c r="A77" s="99" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B77" s="99" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C77" s="21" t="inlineStr">
+      <c r="C77" s="100" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D77" s="20" t="inlineStr">
+      <c r="D77" s="99" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E77" s="20" t="inlineStr">
+      <c r="E77" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="F77" s="99" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="G77" s="20" t="n">
+      <c r="G77" s="99" t="n">
         <v>7.5</v>
       </c>
-      <c r="H77" s="20" t="inlineStr">
+      <c r="H77" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I77" s="21" t="inlineStr">
+      <c r="I77" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="28" t="inlineStr">
+    <row r="78" ht="19" customHeight="1">
+      <c r="A78" s="95" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B78" s="28" t="inlineStr">
+      <c r="B78" s="95" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
+      <c r="C78" s="96" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D78" s="28" t="inlineStr">
+      <c r="D78" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E78" s="28" t="inlineStr">
+      <c r="E78" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F78" s="28" t="inlineStr">
+      <c r="F78" s="95" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="G78" s="28" t="n">
+      <c r="G78" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="H78" s="28" t="inlineStr">
+      <c r="H78" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I78" s="29" t="inlineStr">
+      <c r="I78" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="20" t="inlineStr">
+    <row r="79" ht="19" customHeight="1">
+      <c r="A79" s="99" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B79" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C79" s="21" t="inlineStr">
+      <c r="C79" s="100" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D79" s="20" t="inlineStr">
+      <c r="D79" s="99" t="inlineStr">
         <is>
           <t>04:45 AM</t>
         </is>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E79" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F79" s="20" t="inlineStr">
+      <c r="F79" s="99" t="inlineStr">
         <is>
           <t>10h 35m</t>
         </is>
       </c>
-      <c r="G79" s="20" t="n">
+      <c r="G79" s="99" t="n">
         <v>10.58</v>
       </c>
-      <c r="H79" s="20" t="inlineStr">
+      <c r="H79" s="99" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I79" s="21" t="inlineStr">
+      <c r="I79" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="28" t="inlineStr">
+    <row r="80" ht="19" customHeight="1">
+      <c r="A80" s="95" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B80" s="28" t="inlineStr">
+      <c r="B80" s="95" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C80" s="29" t="inlineStr">
+      <c r="C80" s="96" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D80" s="28" t="inlineStr">
+      <c r="D80" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E80" s="28" t="inlineStr">
+      <c r="E80" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F80" s="28" t="inlineStr">
+      <c r="F80" s="95" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="G80" s="28" t="n">
+      <c r="G80" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="H80" s="28" t="inlineStr">
+      <c r="H80" s="95" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I80" s="29" t="inlineStr">
+      <c r="I80" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="20" t="inlineStr">
+    <row r="81" ht="19" customHeight="1">
+      <c r="A81" s="99" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B81" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C81" s="21" t="inlineStr">
+      <c r="C81" s="100" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr">
+      <c r="D81" s="99" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E81" s="20" t="inlineStr">
+      <c r="E81" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F81" s="99" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="G81" s="20" t="n">
+      <c r="G81" s="99" t="n">
         <v>7.5</v>
       </c>
-      <c r="H81" s="20" t="inlineStr">
+      <c r="H81" s="99" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I81" s="21" t="inlineStr">
+      <c r="I81" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="28" t="inlineStr">
+    <row r="82" ht="19" customHeight="1">
+      <c r="A82" s="95" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B82" s="28" t="inlineStr">
+      <c r="B82" s="95" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C82" s="29" t="inlineStr">
+      <c r="C82" s="96" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D82" s="28" t="inlineStr">
+      <c r="D82" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E82" s="28" t="inlineStr">
+      <c r="E82" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F82" s="28" t="inlineStr">
+      <c r="F82" s="95" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="G82" s="28" t="n">
+      <c r="G82" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="H82" s="28" t="inlineStr">
+      <c r="H82" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I82" s="29" t="inlineStr">
+      <c r="I82" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="20" t="inlineStr">
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="99" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B83" s="20" t="inlineStr">
+      <c r="B83" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C83" s="21" t="inlineStr">
+      <c r="C83" s="100" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D83" s="20" t="inlineStr">
+      <c r="D83" s="99" t="inlineStr">
         <is>
           <t>04:45 AM</t>
         </is>
       </c>
-      <c r="E83" s="20" t="inlineStr">
+      <c r="E83" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F83" s="20" t="inlineStr">
+      <c r="F83" s="99" t="inlineStr">
         <is>
           <t>10h 35m</t>
         </is>
       </c>
-      <c r="G83" s="20" t="n">
+      <c r="G83" s="99" t="n">
         <v>10.58</v>
       </c>
-      <c r="H83" s="20" t="inlineStr">
+      <c r="H83" s="99" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I83" s="21" t="inlineStr">
+      <c r="I83" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="28" t="inlineStr">
+    <row r="84" ht="19" customHeight="1">
+      <c r="A84" s="95" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B84" s="28" t="inlineStr">
+      <c r="B84" s="95" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C84" s="29" t="inlineStr">
+      <c r="C84" s="96" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D84" s="28" t="inlineStr">
+      <c r="D84" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E84" s="28" t="inlineStr">
+      <c r="E84" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F84" s="28" t="inlineStr">
+      <c r="F84" s="95" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="G84" s="28" t="n">
+      <c r="G84" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="H84" s="28" t="inlineStr">
+      <c r="H84" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I84" s="29" t="inlineStr">
+      <c r="I84" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="20" t="inlineStr">
+    <row r="85" ht="19" customHeight="1">
+      <c r="A85" s="99" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B85" s="20" t="inlineStr">
+      <c r="B85" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C85" s="21" t="inlineStr">
+      <c r="C85" s="100" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr">
+      <c r="D85" s="99" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E85" s="20" t="inlineStr">
+      <c r="E85" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F85" s="20" t="inlineStr">
+      <c r="F85" s="99" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="G85" s="20" t="n">
+      <c r="G85" s="99" t="n">
         <v>7.5</v>
       </c>
-      <c r="H85" s="20" t="inlineStr">
+      <c r="H85" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I85" s="21" t="inlineStr">
+      <c r="I85" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="28" t="inlineStr">
+    <row r="86" ht="19" customHeight="1">
+      <c r="A86" s="95" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B86" s="28" t="inlineStr">
+      <c r="B86" s="95" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C86" s="29" t="inlineStr">
+      <c r="C86" s="96" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D86" s="28" t="inlineStr">
+      <c r="D86" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E86" s="28" t="inlineStr">
+      <c r="E86" s="95" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F86" s="28" t="inlineStr">
+      <c r="F86" s="95" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="G86" s="28" t="n">
+      <c r="G86" s="95" t="n">
         <v>7.5</v>
       </c>
-      <c r="H86" s="28" t="inlineStr">
+      <c r="H86" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I86" s="29" t="inlineStr">
+      <c r="I86" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="20" t="inlineStr">
+    <row r="87" ht="19" customHeight="1">
+      <c r="A87" s="99" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B87" s="20" t="inlineStr">
+      <c r="B87" s="99" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C87" s="21" t="inlineStr">
+      <c r="C87" s="100" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D87" s="20" t="inlineStr">
+      <c r="D87" s="99" t="inlineStr">
         <is>
           <t>04:45 AM</t>
         </is>
       </c>
-      <c r="E87" s="20" t="inlineStr">
+      <c r="E87" s="99" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="F87" s="20" t="inlineStr">
+      <c r="F87" s="99" t="inlineStr">
         <is>
           <t>10h 35m</t>
         </is>
       </c>
-      <c r="G87" s="20" t="n">
+      <c r="G87" s="99" t="n">
         <v>10.58</v>
       </c>
-      <c r="H87" s="20" t="inlineStr">
+      <c r="H87" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I87" s="21" t="inlineStr">
+      <c r="I87" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="24" t="inlineStr">
+    <row r="88" ht="19" customHeight="1">
+      <c r="A88" s="111" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B88" s="24" t="inlineStr">
+      <c r="B88" s="111" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C88" s="25" t="inlineStr">
+      <c r="C88" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D88" s="24" t="inlineStr">
+      <c r="D88" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E88" s="24" t="inlineStr">
+      <c r="E88" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F88" s="24" t="inlineStr">
+      <c r="F88" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G88" s="24" t="n">
+      <c r="G88" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="24" t="inlineStr">
+      <c r="H88" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I88" s="25" t="inlineStr">
+      <c r="I88" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="24" t="inlineStr">
+    <row r="89" ht="19" customHeight="1">
+      <c r="A89" s="111" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B89" s="24" t="inlineStr">
+      <c r="B89" s="111" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C89" s="25" t="inlineStr">
+      <c r="C89" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D89" s="24" t="inlineStr">
+      <c r="D89" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E89" s="24" t="inlineStr">
+      <c r="E89" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F89" s="24" t="inlineStr">
+      <c r="F89" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G89" s="24" t="n">
+      <c r="G89" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="24" t="inlineStr">
+      <c r="H89" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I89" s="25" t="inlineStr">
+      <c r="I89" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="24" t="inlineStr">
+    <row r="90" ht="19" customHeight="1">
+      <c r="A90" s="111" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B90" s="24" t="inlineStr">
+      <c r="B90" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C90" s="25" t="inlineStr">
+      <c r="C90" s="112" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D90" s="24" t="inlineStr">
+      <c r="D90" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E90" s="24" t="inlineStr">
+      <c r="E90" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F90" s="24" t="inlineStr">
+      <c r="F90" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G90" s="24" t="n">
+      <c r="G90" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H90" s="24" t="inlineStr">
+      <c r="H90" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I90" s="25" t="inlineStr">
+      <c r="I90" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Day Off (Weekly Day Off)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="20" t="inlineStr">
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="99" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B91" s="20" t="inlineStr">
+      <c r="B91" s="99" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C91" s="21" t="inlineStr">
+      <c r="C91" s="100" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D91" s="20" t="inlineStr">
+      <c r="D91" s="99" t="inlineStr">
         <is>
           <t>04:45 AM</t>
         </is>
       </c>
-      <c r="E91" s="20" t="inlineStr">
+      <c r="E91" s="99" t="inlineStr">
         <is>
           <t>03:30 PM</t>
         </is>
       </c>
-      <c r="F91" s="20" t="inlineStr">
+      <c r="F91" s="99" t="inlineStr">
         <is>
           <t>10h 45m</t>
         </is>
       </c>
-      <c r="G91" s="20" t="n">
+      <c r="G91" s="99" t="n">
         <v>10.75</v>
       </c>
-      <c r="H91" s="20" t="n"/>
-      <c r="I91" s="21" t="inlineStr">
+      <c r="H91" s="99" t="n"/>
+      <c r="I91" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 04:45 AM / Logged out 03:30 PM)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="28" t="inlineStr">
+    <row r="92" ht="19" customHeight="1">
+      <c r="A92" s="95" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B92" s="28" t="inlineStr">
+      <c r="B92" s="95" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C92" s="29" t="inlineStr">
+      <c r="C92" s="96" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D92" s="28" t="inlineStr">
+      <c r="D92" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E92" s="28" t="inlineStr">
+      <c r="E92" s="95" t="inlineStr">
         <is>
           <t>05:13 PM</t>
         </is>
       </c>
-      <c r="F92" s="28" t="inlineStr">
+      <c r="F92" s="95" t="inlineStr">
         <is>
           <t>9h 23m</t>
         </is>
       </c>
-      <c r="G92" s="28" t="n">
+      <c r="G92" s="95" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="H92" s="28" t="n"/>
-      <c r="I92" s="29" t="inlineStr">
+      <c r="H92" s="95" t="n"/>
+      <c r="I92" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="20" t="inlineStr">
+    <row r="93" ht="19" customHeight="1">
+      <c r="A93" s="99" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B93" s="20" t="inlineStr">
+      <c r="B93" s="99" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C93" s="21" t="inlineStr">
+      <c r="C93" s="100" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D93" s="20" t="inlineStr">
+      <c r="D93" s="99" t="inlineStr">
         <is>
           <t>04:45 AM</t>
         </is>
       </c>
-      <c r="E93" s="20" t="inlineStr">
+      <c r="E93" s="99" t="inlineStr">
         <is>
           <t>05:13 PM</t>
         </is>
       </c>
-      <c r="F93" s="20" t="inlineStr">
+      <c r="F93" s="99" t="inlineStr">
         <is>
           <t>12h 28m</t>
         </is>
       </c>
-      <c r="G93" s="20" t="n">
+      <c r="G93" s="99" t="n">
         <v>12.47</v>
       </c>
-      <c r="H93" s="20" t="n"/>
-      <c r="I93" s="21" t="inlineStr">
+      <c r="H93" s="99" t="n"/>
+      <c r="I93" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 04:45 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="28" t="inlineStr">
+    <row r="94" ht="19" customHeight="1">
+      <c r="A94" s="95" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B94" s="28" t="inlineStr">
+      <c r="B94" s="95" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C94" s="29" t="inlineStr">
+      <c r="C94" s="96" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D94" s="28" t="inlineStr">
+      <c r="D94" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E94" s="28" t="inlineStr">
+      <c r="E94" s="95" t="inlineStr">
         <is>
           <t>05:13 PM</t>
         </is>
       </c>
-      <c r="F94" s="28" t="inlineStr">
+      <c r="F94" s="95" t="inlineStr">
         <is>
           <t>9h 23m</t>
         </is>
       </c>
-      <c r="G94" s="28" t="n">
+      <c r="G94" s="95" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="H94" s="28" t="n"/>
-      <c r="I94" s="29" t="inlineStr">
+      <c r="H94" s="95" t="n"/>
+      <c r="I94" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="20" t="inlineStr">
+    <row r="95" ht="19" customHeight="1">
+      <c r="A95" s="99" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B95" s="20" t="inlineStr">
+      <c r="B95" s="99" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C95" s="21" t="inlineStr">
+      <c r="C95" s="100" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D95" s="20" t="inlineStr">
+      <c r="D95" s="99" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E95" s="20" t="inlineStr">
+      <c r="E95" s="99" t="inlineStr">
         <is>
           <t>05:13 PM</t>
         </is>
       </c>
-      <c r="F95" s="20" t="inlineStr">
+      <c r="F95" s="99" t="inlineStr">
         <is>
           <t>9h 23m</t>
         </is>
       </c>
-      <c r="G95" s="20" t="n">
+      <c r="G95" s="99" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="H95" s="20" t="n"/>
-      <c r="I95" s="21" t="inlineStr">
+      <c r="H95" s="99" t="n"/>
+      <c r="I95" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="28" t="inlineStr">
+    <row r="96" ht="19" customHeight="1">
+      <c r="A96" s="95" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B96" s="28" t="inlineStr">
+      <c r="B96" s="95" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C96" s="29" t="inlineStr">
+      <c r="C96" s="96" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D96" s="28" t="inlineStr">
+      <c r="D96" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E96" s="28" t="inlineStr">
+      <c r="E96" s="95" t="inlineStr">
         <is>
           <t>08:00 PM</t>
         </is>
       </c>
-      <c r="F96" s="28" t="inlineStr">
+      <c r="F96" s="95" t="inlineStr">
         <is>
           <t>12h 10m</t>
         </is>
       </c>
-      <c r="G96" s="28" t="n">
+      <c r="G96" s="95" t="n">
         <v>12.17</v>
       </c>
-      <c r="H96" s="28" t="n"/>
-      <c r="I96" s="29" t="inlineStr">
+      <c r="H96" s="95" t="n"/>
+      <c r="I96" s="96" t="inlineStr">
         <is>
           <t>✈️ Extended Duty (07:50 AM – 08:00 PM / 12h 05m) — ⚠️ Aircraft Technical Hazard: Fuel Leak Incident</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="20" t="inlineStr">
+    <row r="97" ht="19" customHeight="1">
+      <c r="A97" s="99" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B97" s="20" t="inlineStr">
+      <c r="B97" s="99" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C97" s="21" t="inlineStr">
+      <c r="C97" s="100" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D97" s="20" t="inlineStr">
+      <c r="D97" s="99" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E97" s="20" t="inlineStr">
+      <c r="E97" s="99" t="inlineStr">
         <is>
           <t>03:30 PM</t>
         </is>
       </c>
-      <c r="F97" s="20" t="inlineStr">
+      <c r="F97" s="99" t="inlineStr">
         <is>
           <t>7h 40m</t>
         </is>
       </c>
-      <c r="G97" s="20" t="n">
+      <c r="G97" s="99" t="n">
         <v>7.67</v>
       </c>
-      <c r="H97" s="20" t="n"/>
-      <c r="I97" s="21" t="inlineStr">
+      <c r="H97" s="99" t="n"/>
+      <c r="I97" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="24" t="inlineStr">
+    <row r="98" ht="19" customHeight="1">
+      <c r="A98" s="111" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B98" s="24" t="inlineStr">
+      <c r="B98" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C98" s="25" t="inlineStr">
+      <c r="C98" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D98" s="24" t="inlineStr">
+      <c r="D98" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E98" s="24" t="inlineStr">
+      <c r="E98" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F98" s="24" t="inlineStr">
+      <c r="F98" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G98" s="24" t="n">
+      <c r="G98" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H98" s="24" t="inlineStr">
+      <c r="H98" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I98" s="25" t="inlineStr">
+      <c r="I98" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="24" t="inlineStr">
+    <row r="99" ht="19" customHeight="1">
+      <c r="A99" s="111" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B99" s="24" t="inlineStr">
+      <c r="B99" s="111" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C99" s="25" t="inlineStr">
+      <c r="C99" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D99" s="24" t="inlineStr">
+      <c r="D99" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E99" s="24" t="inlineStr">
+      <c r="E99" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F99" s="24" t="inlineStr">
+      <c r="F99" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G99" s="24" t="n">
+      <c r="G99" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H99" s="24" t="inlineStr">
+      <c r="H99" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I99" s="25" t="inlineStr">
+      <c r="I99" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="28" t="inlineStr">
+    <row r="100" ht="19" customHeight="1">
+      <c r="A100" s="95" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B100" s="28" t="inlineStr">
+      <c r="B100" s="95" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C100" s="29" t="inlineStr">
+      <c r="C100" s="96" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D100" s="28" t="inlineStr">
+      <c r="D100" s="95" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="E100" s="28" t="inlineStr">
+      <c r="E100" s="95" t="inlineStr">
         <is>
           <t>03:30 PM</t>
         </is>
       </c>
-      <c r="F100" s="28" t="inlineStr">
+      <c r="F100" s="95" t="inlineStr">
         <is>
           <t>7h 40m</t>
         </is>
       </c>
-      <c r="G100" s="28" t="n">
+      <c r="G100" s="95" t="n">
         <v>7.67</v>
       </c>
-      <c r="H100" s="28" t="n"/>
-      <c r="I100" s="29" t="inlineStr">
+      <c r="H100" s="95" t="n"/>
+      <c r="I100" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="20" t="inlineStr">
+    <row r="101" ht="19" customHeight="1">
+      <c r="A101" s="99" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B101" s="20" t="inlineStr">
+      <c r="B101" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C101" s="21" t="inlineStr">
+      <c r="C101" s="100" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D101" s="20" t="inlineStr">
+      <c r="D101" s="99" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E101" s="20" t="inlineStr">
+      <c r="E101" s="99" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F101" s="20" t="inlineStr">
+      <c r="F101" s="99" t="inlineStr">
         <is>
           <t>7h 48m</t>
         </is>
       </c>
-      <c r="G101" s="20" t="n">
+      <c r="G101" s="99" t="n">
         <v>7.8</v>
       </c>
-      <c r="H101" s="20" t="inlineStr">
+      <c r="H101" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I101" s="21" t="inlineStr">
+      <c r="I101" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="28" t="inlineStr">
+    <row r="102" ht="19" customHeight="1">
+      <c r="A102" s="95" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B102" s="28" t="inlineStr">
+      <c r="B102" s="95" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C102" s="29" t="inlineStr">
+      <c r="C102" s="96" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D102" s="28" t="inlineStr">
+      <c r="D102" s="95" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E102" s="28" t="inlineStr">
+      <c r="E102" s="95" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F102" s="28" t="inlineStr">
+      <c r="F102" s="95" t="inlineStr">
         <is>
           <t>7h 48m</t>
         </is>
       </c>
-      <c r="G102" s="28" t="n">
+      <c r="G102" s="95" t="n">
         <v>7.8</v>
       </c>
-      <c r="H102" s="28" t="inlineStr">
+      <c r="H102" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I102" s="29" t="inlineStr">
+      <c r="I102" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="20" t="inlineStr">
+    <row r="103" ht="19" customHeight="1">
+      <c r="A103" s="99" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B103" s="20" t="inlineStr">
+      <c r="B103" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C103" s="21" t="inlineStr">
+      <c r="C103" s="100" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D103" s="20" t="inlineStr">
+      <c r="D103" s="99" t="inlineStr">
         <is>
           <t>03:30 AM</t>
         </is>
       </c>
-      <c r="E103" s="20" t="inlineStr">
+      <c r="E103" s="99" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F103" s="20" t="inlineStr">
+      <c r="F103" s="99" t="inlineStr">
         <is>
           <t>12h 05m</t>
         </is>
       </c>
-      <c r="G103" s="20" t="n">
+      <c r="G103" s="99" t="n">
         <v>12.08</v>
       </c>
-      <c r="H103" s="20" t="inlineStr">
+      <c r="H103" s="99" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I103" s="21" t="inlineStr">
+      <c r="I103" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="24" t="inlineStr">
+    <row r="104" ht="19" customHeight="1">
+      <c r="A104" s="111" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B104" s="24" t="inlineStr">
+      <c r="B104" s="111" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C104" s="25" t="inlineStr">
+      <c r="C104" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D104" s="24" t="inlineStr">
+      <c r="D104" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E104" s="24" t="inlineStr">
+      <c r="E104" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F104" s="24" t="inlineStr">
+      <c r="F104" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G104" s="24" t="n">
+      <c r="G104" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H104" s="24" t="inlineStr">
+      <c r="H104" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I104" s="25" t="inlineStr">
+      <c r="I104" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="20" t="inlineStr">
+    <row r="105" ht="19" customHeight="1">
+      <c r="A105" s="99" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B105" s="20" t="inlineStr">
+      <c r="B105" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C105" s="21" t="inlineStr">
+      <c r="C105" s="100" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D105" s="20" t="inlineStr">
+      <c r="D105" s="99" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E105" s="20" t="inlineStr">
+      <c r="E105" s="99" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F105" s="20" t="inlineStr">
+      <c r="F105" s="99" t="inlineStr">
         <is>
           <t>7h 48m</t>
         </is>
       </c>
-      <c r="G105" s="20" t="n">
+      <c r="G105" s="99" t="n">
         <v>7.8</v>
       </c>
-      <c r="H105" s="20" t="inlineStr">
+      <c r="H105" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I105" s="21" t="inlineStr">
+      <c r="I105" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="24" t="inlineStr">
+    <row r="106" ht="19" customHeight="1">
+      <c r="A106" s="111" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B106" s="24" t="inlineStr">
+      <c r="B106" s="111" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C106" s="25" t="inlineStr">
+      <c r="C106" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D106" s="24" t="inlineStr">
+      <c r="D106" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E106" s="24" t="inlineStr">
+      <c r="E106" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F106" s="24" t="inlineStr">
+      <c r="F106" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G106" s="24" t="n">
+      <c r="G106" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H106" s="24" t="inlineStr">
+      <c r="H106" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I106" s="25" t="inlineStr">
+      <c r="I106" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="20" t="inlineStr">
+    <row r="107" ht="19" customHeight="1">
+      <c r="A107" s="99" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B107" s="20" t="inlineStr">
+      <c r="B107" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C107" s="21" t="inlineStr">
+      <c r="C107" s="100" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D107" s="20" t="inlineStr">
+      <c r="D107" s="99" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E107" s="20" t="inlineStr">
+      <c r="E107" s="99" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F107" s="20" t="inlineStr">
+      <c r="F107" s="99" t="inlineStr">
         <is>
           <t>7h 48m</t>
         </is>
       </c>
-      <c r="G107" s="20" t="n">
+      <c r="G107" s="99" t="n">
         <v>7.8</v>
       </c>
-      <c r="H107" s="20" t="inlineStr">
+      <c r="H107" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I107" s="21" t="inlineStr">
+      <c r="I107" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="28" t="inlineStr">
+    <row r="108" ht="19" customHeight="1">
+      <c r="A108" s="95" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B108" s="28" t="inlineStr">
+      <c r="B108" s="95" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C108" s="29" t="inlineStr">
+      <c r="C108" s="96" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D108" s="28" t="inlineStr">
+      <c r="D108" s="95" t="inlineStr">
         <is>
           <t>03:30 AM</t>
         </is>
       </c>
-      <c r="E108" s="28" t="inlineStr">
+      <c r="E108" s="95" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F108" s="28" t="inlineStr">
+      <c r="F108" s="95" t="inlineStr">
         <is>
           <t>12h 05m</t>
         </is>
       </c>
-      <c r="G108" s="28" t="n">
+      <c r="G108" s="95" t="n">
         <v>12.08</v>
       </c>
-      <c r="H108" s="28" t="inlineStr">
+      <c r="H108" s="95" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I108" s="29" t="inlineStr">
+      <c r="I108" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="20" t="inlineStr">
+    <row r="109" ht="19" customHeight="1">
+      <c r="A109" s="99" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B109" s="20" t="inlineStr">
+      <c r="B109" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C109" s="21" t="inlineStr">
+      <c r="C109" s="100" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D109" s="20" t="inlineStr">
+      <c r="D109" s="99" t="inlineStr">
         <is>
           <t>03:30 AM</t>
         </is>
       </c>
-      <c r="E109" s="20" t="inlineStr">
+      <c r="E109" s="99" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F109" s="20" t="inlineStr">
+      <c r="F109" s="99" t="inlineStr">
         <is>
           <t>12h 05m</t>
         </is>
       </c>
-      <c r="G109" s="20" t="n">
+      <c r="G109" s="99" t="n">
         <v>12.08</v>
       </c>
-      <c r="H109" s="20" t="inlineStr">
+      <c r="H109" s="99" t="inlineStr">
         <is>
           <t>Dawn Shift</t>
         </is>
       </c>
-      <c r="I109" s="21" t="inlineStr">
+      <c r="I109" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="28" t="inlineStr">
+    <row r="110" ht="19" customHeight="1">
+      <c r="A110" s="95" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B110" s="28" t="inlineStr">
+      <c r="B110" s="95" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C110" s="29" t="inlineStr">
+      <c r="C110" s="96" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D110" s="28" t="inlineStr">
+      <c r="D110" s="95" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E110" s="28" t="inlineStr">
+      <c r="E110" s="95" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F110" s="28" t="inlineStr">
+      <c r="F110" s="95" t="inlineStr">
         <is>
           <t>7h 48m</t>
         </is>
       </c>
-      <c r="G110" s="28" t="n">
+      <c r="G110" s="95" t="n">
         <v>7.8</v>
       </c>
-      <c r="H110" s="28" t="inlineStr">
+      <c r="H110" s="95" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I110" s="29" t="inlineStr">
+      <c r="I110" s="96" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="20" t="inlineStr">
+    <row r="111" ht="19" customHeight="1">
+      <c r="A111" s="99" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B111" s="20" t="inlineStr">
+      <c r="B111" s="99" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C111" s="21" t="inlineStr">
+      <c r="C111" s="100" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D111" s="20" t="inlineStr">
+      <c r="D111" s="99" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="E111" s="20" t="inlineStr">
+      <c r="E111" s="99" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="F111" s="20" t="inlineStr">
+      <c r="F111" s="99" t="inlineStr">
         <is>
           <t>7h 48m</t>
         </is>
       </c>
-      <c r="G111" s="20" t="n">
+      <c r="G111" s="99" t="n">
         <v>7.8</v>
       </c>
-      <c r="H111" s="20" t="inlineStr">
+      <c r="H111" s="99" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I111" s="21" t="inlineStr">
+      <c r="I111" s="100" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="24" t="inlineStr">
+    <row r="112" ht="19" customHeight="1">
+      <c r="A112" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B112" s="24" t="inlineStr">
+      <c r="B112" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C112" s="25" t="inlineStr">
+      <c r="C112" s="112" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D112" s="24" t="inlineStr">
+      <c r="D112" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E112" s="24" t="inlineStr">
+      <c r="E112" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F112" s="24" t="inlineStr">
+      <c r="F112" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G112" s="24" t="n">
+      <c r="G112" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H112" s="24" t="inlineStr">
+      <c r="H112" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I112" s="25" t="inlineStr">
+      <c r="I112" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="24" t="inlineStr">
+    <row r="113" ht="19" customHeight="1">
+      <c r="A113" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B113" s="24" t="inlineStr">
+      <c r="B113" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C113" s="25" t="inlineStr">
+      <c r="C113" s="112" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D113" s="24" t="inlineStr">
+      <c r="D113" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E113" s="24" t="inlineStr">
+      <c r="E113" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F113" s="24" t="inlineStr">
+      <c r="F113" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G113" s="24" t="n">
+      <c r="G113" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="24" t="inlineStr">
+      <c r="H113" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I113" s="25" t="inlineStr">
+      <c r="I113" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="24" t="inlineStr">
+    <row r="114" ht="19" customHeight="1">
+      <c r="A114" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B114" s="24" t="inlineStr">
+      <c r="B114" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C114" s="25" t="inlineStr">
+      <c r="C114" s="112" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D114" s="24" t="inlineStr">
+      <c r="D114" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E114" s="24" t="inlineStr">
+      <c r="E114" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F114" s="24" t="inlineStr">
+      <c r="F114" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G114" s="24" t="n">
+      <c r="G114" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="24" t="inlineStr">
+      <c r="H114" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I114" s="25" t="inlineStr">
+      <c r="I114" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="24" t="inlineStr">
+    <row r="115" ht="19" customHeight="1">
+      <c r="A115" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B115" s="24" t="inlineStr">
+      <c r="B115" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C115" s="25" t="inlineStr">
+      <c r="C115" s="112" t="inlineStr">
         <is>
           <t>Talal</t>
         </is>
       </c>
-      <c r="D115" s="24" t="inlineStr">
+      <c r="D115" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E115" s="24" t="inlineStr">
+      <c r="E115" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F115" s="24" t="inlineStr">
+      <c r="F115" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G115" s="24" t="n">
+      <c r="G115" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="24" t="inlineStr">
+      <c r="H115" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I115" s="25" t="inlineStr">
+      <c r="I115" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="24" t="inlineStr">
+    <row r="116" ht="19" customHeight="1">
+      <c r="A116" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B116" s="24" t="inlineStr">
+      <c r="B116" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C116" s="25" t="inlineStr">
+      <c r="C116" s="112" t="inlineStr">
         <is>
           <t>Mohamed Adnan</t>
         </is>
       </c>
-      <c r="D116" s="24" t="inlineStr">
+      <c r="D116" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E116" s="24" t="inlineStr">
+      <c r="E116" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F116" s="24" t="inlineStr">
+      <c r="F116" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G116" s="24" t="n">
+      <c r="G116" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="24" t="inlineStr">
+      <c r="H116" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I116" s="25" t="inlineStr">
+      <c r="I116" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="24" t="inlineStr">
+    <row r="117" ht="19" customHeight="1">
+      <c r="A117" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B117" s="24" t="inlineStr">
+      <c r="B117" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C117" s="25" t="inlineStr">
+      <c r="C117" s="112" t="inlineStr">
         <is>
           <t>Tarek Orfhly</t>
         </is>
       </c>
-      <c r="D117" s="24" t="inlineStr">
+      <c r="D117" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E117" s="24" t="inlineStr">
+      <c r="E117" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F117" s="24" t="inlineStr">
+      <c r="F117" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G117" s="24" t="n">
+      <c r="G117" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="24" t="inlineStr">
+      <c r="H117" s="111" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="I117" s="25" t="inlineStr">
+      <c r="I117" s="112" t="inlineStr">
         <is>
           <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="24" t="inlineStr">
+    <row r="118" ht="19" customHeight="1">
+      <c r="A118" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B118" s="24" t="inlineStr">
+      <c r="B118" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C118" s="25" t="inlineStr">
+      <c r="C118" s="112" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D118" s="24" t="inlineStr">
+      <c r="D118" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E118" s="24" t="inlineStr">
+      <c r="E118" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F118" s="24" t="inlineStr">
+      <c r="F118" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G118" s="24" t="n">
+      <c r="G118" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H118" s="24" t="inlineStr">
+      <c r="H118" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I118" s="25" t="inlineStr">
+      <c r="I118" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="24" t="inlineStr">
+    <row r="119" ht="19" customHeight="1">
+      <c r="A119" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B119" s="24" t="inlineStr">
+      <c r="B119" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C119" s="25" t="inlineStr">
+      <c r="C119" s="112" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D119" s="24" t="inlineStr">
+      <c r="D119" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E119" s="24" t="inlineStr">
+      <c r="E119" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F119" s="24" t="inlineStr">
+      <c r="F119" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G119" s="24" t="n">
+      <c r="G119" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H119" s="24" t="inlineStr">
+      <c r="H119" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I119" s="25" t="inlineStr">
+      <c r="I119" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="24" t="inlineStr">
+    <row r="120" ht="19" customHeight="1">
+      <c r="A120" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B120" s="24" t="inlineStr">
+      <c r="B120" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C120" s="25" t="inlineStr">
+      <c r="C120" s="112" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D120" s="24" t="inlineStr">
+      <c r="D120" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E120" s="24" t="inlineStr">
+      <c r="E120" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F120" s="24" t="inlineStr">
+      <c r="F120" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G120" s="24" t="n">
+      <c r="G120" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H120" s="24" t="inlineStr">
+      <c r="H120" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I120" s="25" t="inlineStr">
+      <c r="I120" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="24" t="inlineStr">
+    <row r="121" ht="19" customHeight="1">
+      <c r="A121" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B121" s="24" t="inlineStr">
+      <c r="B121" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C121" s="25" t="inlineStr">
+      <c r="C121" s="112" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D121" s="24" t="inlineStr">
+      <c r="D121" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E121" s="24" t="inlineStr">
+      <c r="E121" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F121" s="24" t="inlineStr">
+      <c r="F121" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G121" s="24" t="n">
+      <c r="G121" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H121" s="24" t="inlineStr">
+      <c r="H121" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I121" s="25" t="inlineStr">
+      <c r="I121" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="24" t="inlineStr">
+    <row r="122" ht="19" customHeight="1">
+      <c r="A122" s="111" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B122" s="24" t="inlineStr">
+      <c r="B122" s="111" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C122" s="25" t="inlineStr">
+      <c r="C122" s="112" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D122" s="24" t="inlineStr">
+      <c r="D122" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E122" s="24" t="inlineStr">
+      <c r="E122" s="111" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F122" s="24" t="inlineStr">
+      <c r="F122" s="111" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G122" s="24" t="n">
+      <c r="G122" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="24" t="inlineStr">
+      <c r="H122" s="111" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I122" s="25" t="inlineStr">
+      <c r="I122" s="112" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -374,7 +374,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -479,11 +479,77 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -789,6 +855,8 @@
     <xf numFmtId="0" fontId="30" fillId="25" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1193,16 +1261,16 @@
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="74" t="inlineStr">
         <is>
-          <t>1,213.2h</t>
-        </is>
-      </c>
-      <c r="B5" s="75" t="n"/>
+          <t>1347,44h</t>
+        </is>
+      </c>
+      <c r="B5" s="113" t="n"/>
       <c r="C5" s="74" t="inlineStr">
         <is>
-          <t>520.5h</t>
-        </is>
-      </c>
-      <c r="D5" s="75" t="n"/>
+          <t>673.1h</t>
+        </is>
+      </c>
+      <c r="D5" s="113" t="n"/>
       <c r="E5" s="74" t="inlineStr">
         <is>
           <t>9 Active</t>
@@ -1213,7 +1281,7 @@
           <t>55.4h</t>
         </is>
       </c>
-      <c r="G5" s="75" t="n"/>
+      <c r="G5" s="113" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="76" t="inlineStr">
@@ -1221,13 +1289,13 @@
           <t>CUMULATIVE OUTPUT</t>
         </is>
       </c>
-      <c r="B6" s="75" t="n"/>
+      <c r="B6" s="113" t="n"/>
       <c r="C6" s="76" t="inlineStr">
         <is>
           <t>OCTOBER ACTIVE CYCLE</t>
         </is>
       </c>
-      <c r="D6" s="75" t="n"/>
+      <c r="D6" s="113" t="n"/>
       <c r="E6" s="76" t="inlineStr">
         <is>
           <t>STATION ROSTER</t>
@@ -1238,7 +1306,7 @@
           <t>ONBOARDING TRACKER</t>
         </is>
       </c>
-      <c r="G6" s="75" t="n"/>
+      <c r="G6" s="113" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="77" t="inlineStr">
@@ -1246,13 +1314,13 @@
           <t>Sep + Oct Total Delivered</t>
         </is>
       </c>
-      <c r="B7" s="75" t="n"/>
+      <c r="B7" s="113" t="n"/>
       <c r="C7" s="77" t="inlineStr">
         <is>
           <t>7 Active Shifts Tracked</t>
         </is>
       </c>
-      <c r="D7" s="75" t="n"/>
+      <c r="D7" s="113" t="n"/>
       <c r="E7" s="77" t="inlineStr">
         <is>
           <t>● 100% Operational</t>
@@ -1263,7 +1331,7 @@
           <t>Osama Alkabbani Output</t>
         </is>
       </c>
-      <c r="G7" s="75" t="n"/>
+      <c r="G7" s="113" t="n"/>
     </row>
     <row r="8" ht="12" customHeight="1"/>
     <row r="9" ht="20" customHeight="1">
@@ -1458,26 +1526,26 @@
       </c>
       <c r="B15" s="98" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C15" s="99" t="inlineStr">
         <is>
-          <t>71h 00m</t>
+          <t>68h 00m</t>
         </is>
       </c>
       <c r="D15" s="99" t="inlineStr">
         <is>
-          <t>73h 26m</t>
+          <t>81h 10m</t>
         </is>
       </c>
       <c r="E15" s="97" t="inlineStr">
         <is>
-          <t>144h 26m</t>
+          <t>149h 10m</t>
         </is>
       </c>
       <c r="F15" s="97" t="n">
-        <v>144.43</v>
+        <v>149.17</v>
       </c>
       <c r="G15" s="100" t="inlineStr">
         <is>
@@ -1493,26 +1561,26 @@
       </c>
       <c r="B16" s="94" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C16" s="95" t="inlineStr">
         <is>
-          <t>68h 00m</t>
+          <t>71h 00m</t>
         </is>
       </c>
       <c r="D16" s="95" t="inlineStr">
         <is>
-          <t>76h 13m</t>
+          <t>73h 26m</t>
         </is>
       </c>
       <c r="E16" s="93" t="inlineStr">
         <is>
-          <t>144h 13m</t>
+          <t>144h 26m</t>
         </is>
       </c>
       <c r="F16" s="93" t="n">
-        <v>144.22</v>
+        <v>144.43</v>
       </c>
       <c r="G16" s="96" t="inlineStr">
         <is>
@@ -1603,7 +1671,7 @@
       </c>
       <c r="C19" s="99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0h 00m</t>
         </is>
       </c>
       <c r="D19" s="99" t="inlineStr">
@@ -1708,21 +1776,21 @@
       </c>
       <c r="C22" s="105" t="inlineStr">
         <is>
-          <t>692h 40m</t>
+          <t>674h 40m</t>
         </is>
       </c>
       <c r="D22" s="105" t="inlineStr">
         <is>
-          <t>520h 30m</t>
+          <t>673h 04m</t>
         </is>
       </c>
       <c r="E22" s="105" t="inlineStr">
         <is>
-          <t>1,213h 10m</t>
+          <t>1347h 44m</t>
         </is>
       </c>
       <c r="F22" s="105" t="n">
-        <v>1213.17</v>
+        <v>1347.73</v>
       </c>
       <c r="G22" s="106" t="inlineStr">
         <is>
@@ -1769,7 +1837,7 @@
           <t>EVENT DESCRIPTION &amp; RESOLUTION</t>
         </is>
       </c>
-      <c r="G25" s="107" t="n"/>
+      <c r="G25" s="114" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="83" t="inlineStr">
@@ -1802,14 +1870,14 @@
           <t>Remained on station due to aircraft fuel leak hazard. Overtime logged &amp; resolved.</t>
         </is>
       </c>
-      <c r="G26" s="107" t="n"/>
+      <c r="G26" s="114" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
@@ -10311,30 +10379,30 @@
       </c>
       <c r="D110" s="95" t="inlineStr">
         <is>
-          <t>07:47 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="E110" s="95" t="inlineStr">
         <is>
-          <t>03:35 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F110" s="95" t="inlineStr">
         <is>
-          <t>7h 48m</t>
+          <t>12h 45m</t>
         </is>
       </c>
       <c r="G110" s="95" t="n">
-        <v>7.8</v>
+        <v>12.75</v>
       </c>
       <c r="H110" s="95" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I110" s="96" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -11090,26 +11158,26 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>71h 00m</t>
+          <t>68h 00m</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>73h 26m</t>
+          <t>81h 10m</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>144h 26m</t>
+          <t>149h 10m</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>144.43</v>
+        <v>149.17</v>
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
@@ -11123,26 +11191,26 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>68h 00m</t>
+          <t>71h 00m</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>76h 13m</t>
+          <t>73h 26m</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>144h 13m</t>
+          <t>144h 26m</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>144.22</v>
+        <v>144.43</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
@@ -11245,7 +11313,7 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Onboarding / Morning Duty</t>
+          <t>Onboarding Staff / Morning Duty (07:47 AM)</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11346,7 @@
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Inactive / Terminated (Last Duty: Sep 29, 2026)</t>
+          <t>🛑 Inactive / Departed (Last Duty: Sep 29)</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11379,7 @@
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Inactive / Terminated (Last Duty: Sep 29, 2026)</t>
+          <t>🛑 Inactive / Departed (Last Duty: Sep 29)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -810,12 +810,12 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Paid Mission</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -1225,47 +1225,47 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Paid Mission</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1702,20 +1702,20 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G27" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Mission</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Paid Shift</t>
+          <t>Paid Mission</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -3182,16 +3182,16 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -3672,21 +3672,21 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G71" s="7" t="n">
-        <v>7.42</v>
+        <v>9.5</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
@@ -4167,21 +4167,21 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -4672,20 +4672,20 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>12h 10m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G93" s="7" t="n">
-        <v>12.17</v>
+        <v>13</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>✈️ Extended Duty (07:50 AM – 08:00 PM / 12h 05m) — ⚠️ Aircraft Technical Hazard: Fuel Leak Incident</t>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 08:00 PM / 13h 00m)</t>
         </is>
       </c>
     </row>
@@ -5157,30 +5157,30 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>12h 45m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G104" s="4" t="n">
-        <v>12.75</v>
+        <v>9.5</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / Logged out 04:00 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
@@ -5952,17 +5952,17 @@
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5972,16 +5972,16 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G122" s="4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -6017,42 +6017,42 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G123" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -6062,42 +6062,42 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>04:15 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G124" s="4" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
         </is>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -6120,24 +6120,24 @@
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -6152,16 +6152,16 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6177,12 +6177,12 @@
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -6202,11 +6202,11 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G127" s="7" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
@@ -6215,24 +6215,24 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -6242,16 +6242,16 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G128" s="4" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -6267,12 +6267,12 @@
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -6292,56 +6292,56 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G129" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>03:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
-        <v>8.5</v>
+        <v>8.08</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6350,64 +6350,64 @@
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D131" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F131" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G131" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -6417,75 +6417,525 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>13h 15m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>13.25</v>
+        <v>5.5</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>01:30 PM</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>5h 30m</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>03:30 PM</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>13h 15m</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G133" s="7" t="n">
+      <c r="G142" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>✈️ Live Daily Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
@@ -8784,7 +9234,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>08:20 AM</t>
+          <t>08:10 AM</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -8794,11 +9244,11 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>7h 40m</t>
+          <t>7h 50m</t>
         </is>
       </c>
       <c r="G51" s="7" t="n">
-        <v>7.67</v>
+        <v>7.83</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -8807,7 +9257,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift (7h 40m)</t>
+          <t>Standard daytime shift (7h 50m)</t>
         </is>
       </c>
     </row>
@@ -8834,16 +9284,16 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>03:45 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>7h 45m</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8852,7 +9302,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Standard daytime shift (7h 30m)</t>
+          <t>Standard daytime shift (7h 45m)</t>
         </is>
       </c>
     </row>
@@ -8919,7 +9369,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8929,11 +9379,11 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8942,7 +9392,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Morning departure processing (8h 45m)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -8964,7 +9414,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -8974,11 +9424,11 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>8h 40m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G55" s="7" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
@@ -8987,7 +9437,7 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Morning departure processing (8h 40m)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9459,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -9019,11 +9469,11 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>8h 40m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -9032,7 +9482,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Morning departure processing (8h 40m)</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -9072,12 +9522,12 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Paid Mission</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -10243,20 +10693,20 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>66.67</v>
+        <v>69.33</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>107.09</v>
+        <v>169.67</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>173.76</v>
+        <v>239</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -10265,20 +10715,20 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>84.66</v>
+        <v>66.67</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>84.34999999999999</v>
+        <v>107.09</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>169.01</v>
+        <v>173.76</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -10287,17 +10737,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>74.75</v>
+        <v>84.66</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>82.16</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>156.91</v>
+        <v>169.01</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>17</v>
@@ -10309,17 +10759,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>75</v>
+        <v>74.75</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>78</v>
+        <v>82.16</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>153</v>
+        <v>156.91</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>17</v>
@@ -10331,17 +10781,17 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>68.01000000000001</v>
+        <v>75</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>81.17</v>
+        <v>78</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>149.18</v>
+        <v>153</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>17</v>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -837,30 +837,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>02:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6h 15m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -1270,47 +1270,47 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1747,20 +1747,20 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+          <t>✈️ Live Daily Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2232,30 +2232,30 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2737,20 +2737,20 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>✈️ Live Daily Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3222,30 +3222,30 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>03:00 AM</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G61" s="7" t="n">
-        <v>8.08</v>
+        <v>13</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
@@ -3717,21 +3717,21 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>03:55 AM</t>
+          <t>03:00 AM</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>11h 25m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>11.42</v>
+        <v>13</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
@@ -4212,21 +4212,21 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>03:00 AM</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G83" s="7" t="n">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
@@ -4707,30 +4707,30 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>03:00 AM</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>03:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>7h 40m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G94" s="4" t="n">
-        <v>7.67</v>
+        <v>13</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
@@ -5202,21 +5202,21 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>03:30 AM</t>
+          <t>03:00 AM</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>03:35 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>12h 05m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G105" s="7" t="n">
-        <v>12.08</v>
+        <v>13</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
@@ -5680,47 +5680,47 @@
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G116" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -5997,45 +5997,45 @@
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G123" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -6062,25 +6062,25 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G124" s="4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -6107,42 +6107,42 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G125" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
         </is>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -6152,16 +6152,16 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>04:15 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -6177,45 +6177,45 @@
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G127" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -6242,16 +6242,16 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G128" s="4" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -6267,17 +6267,17 @@
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -6300,34 +6300,34 @@
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6337,77 +6337,77 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G131" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -6422,16 +6422,16 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6447,67 +6447,67 @@
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G133" s="7" t="n">
-        <v>5.5</v>
+        <v>8.08</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6517,77 +6517,77 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G135" s="7" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -6597,137 +6597,137 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>01:30 PM</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>5h 30m</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>01:30 PM</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>5h 30m</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>03:30 PM</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>8h 30m</t>
-        </is>
-      </c>
-      <c r="G136" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>Raboushee</t>
-        </is>
-      </c>
-      <c r="D137" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E137" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G137" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C138" s="9" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F138" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G138" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -6737,16 +6737,16 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G139" s="7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
@@ -6755,29 +6755,29 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6787,155 +6787,605 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>13h 15m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>13.25</v>
+        <v>9.5</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>03:00 AM</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G141" s="7" t="n">
-        <v>9.67</v>
+        <v>13</v>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>03:30 PM</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>10h 30m</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>5h 30m</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>Afternoon Duty</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>13h 15m</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>10h 40m</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B151" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E151" s="5" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F151" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H151" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I142" s="3" t="inlineStr">
+      <c r="I151" s="6" t="inlineStr">
         <is>
           <t>✈️ Live Daily Ground Duty</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>07:30 AM</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>9h 30m</t>
         </is>
       </c>
-      <c r="G143" s="7" t="n">
+      <c r="G152" s="4" t="n">
         <v>9.5</v>
       </c>
-      <c r="H143" s="5" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I143" s="6" t="inlineStr">
+      <c r="I152" s="3" t="inlineStr">
         <is>
           <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>10h 00m</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:00 PM / 10h 00m)</t>
         </is>
       </c>
     </row>
@@ -7749,30 +8199,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Standardized</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>Standard daytime shift (8h 30m)</t>
         </is>
       </c>
     </row>
@@ -7817,7 +8267,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard daytime shift (8h 30m)</t>
         </is>
       </c>
     </row>
@@ -7844,16 +8294,16 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7862,7 +8312,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard daytime shift (8h 00m)</t>
         </is>
       </c>
     </row>
@@ -7889,16 +8339,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -7907,7 +8357,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard daytime shift (8h 00m)</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8514,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>03:00 AM</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -8074,20 +8524,20 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
@@ -10671,20 +11121,20 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>75.08</v>
+        <v>77</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>177</v>
+        <v>196.17</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>252.08</v>
+        <v>273.17</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -10693,17 +11143,17 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>69.33</v>
+        <v>75.08</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>169.67</v>
+        <v>177</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>239</v>
+        <v>252.08</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>27</v>
@@ -10715,20 +11165,20 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>66.67</v>
+        <v>69.33</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>107.09</v>
+        <v>169.67</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>173.76</v>
+        <v>239</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -10737,20 +11187,20 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>84.66</v>
+        <v>66.67</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>84.34999999999999</v>
+        <v>107.09</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>169.01</v>
+        <v>173.76</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -10759,17 +11209,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>74.75</v>
+        <v>84.66</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>82.16</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>156.91</v>
+        <v>169.01</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>17</v>
@@ -10781,17 +11231,17 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>75</v>
+        <v>74.75</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>78</v>
+        <v>82.16</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>153</v>
+        <v>156.91</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>17</v>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I166"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1090,47 +1090,47 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1612,20 +1612,20 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2097,30 +2097,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Paid Shift</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2597,16 +2597,16 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G47" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -3092,16 +3092,16 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>8.08</v>
+        <v>8.5</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -3582,30 +3582,30 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G69" s="7" t="n">
-        <v>7.42</v>
+        <v>8</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Ground Duty (08:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4077,30 +4077,30 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>04:45 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>10h 35m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>10.58</v>
+        <v>8</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Ground Duty (08:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4572,30 +4572,30 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>04:45 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>03:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>10h 45m</t>
+          <t>12h 45m</t>
         </is>
       </c>
       <c r="G91" s="7" t="n">
-        <v>10.75</v>
+        <v>12.75</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 04:45 AM / Logged out 03:30 PM)</t>
+          <t>✈️ Early dawn flight departure handling (12h 45m)</t>
         </is>
       </c>
     </row>
@@ -5067,30 +5067,30 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>03:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>03:35 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>12h 05m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G102" s="4" t="n">
-        <v>12.08</v>
+        <v>9</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
@@ -5545,47 +5545,47 @@
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G113" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -6052,35 +6052,35 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:20 AM</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>05:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>9h 05m</t>
+          <t>7h 40m</t>
         </is>
       </c>
       <c r="G124" s="4" t="n">
-        <v>9.08</v>
+        <v>7.67</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -6107,25 +6107,25 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:05 PM</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 05m</t>
         </is>
       </c>
       <c r="G125" s="7" t="n">
-        <v>8.5</v>
+        <v>9.08</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -6187,80 +6187,80 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G127" s="7" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G128" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -6287,25 +6287,25 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G129" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6322,26 +6322,26 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:05 AM</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>7h 55m</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
-        <v>8.5</v>
+        <v>7.92</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -6377,25 +6377,25 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G131" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -6412,52 +6412,52 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -6467,16 +6467,16 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>04:15 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G133" s="7" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
@@ -6492,45 +6492,45 @@
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -6557,16 +6557,16 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G135" s="7" t="n">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6637,52 +6637,52 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G137" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6692,16 +6692,16 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G138" s="4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6717,22 +6717,22 @@
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -6742,65 +6742,65 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G139" s="7" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -6862,92 +6862,92 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G142" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G143" s="7" t="n">
-        <v>5.5</v>
+        <v>8.08</v>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -6987,12 +6987,12 @@
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -7007,16 +7007,16 @@
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G145" s="7" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
@@ -7032,12 +7032,12 @@
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -7047,42 +7047,42 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -7092,97 +7092,97 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G147" s="7" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>08:10 AM</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>4h 50m</t>
         </is>
       </c>
       <c r="G148" s="4" t="n">
-        <v>11.5</v>
+        <v>4.83</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -7192,82 +7192,82 @@
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G149" s="7" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>03:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G150" s="4" t="n">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -7277,16 +7277,16 @@
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>03:30 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G151" s="7" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
@@ -7295,249 +7295,249 @@
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G152" s="4" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B153" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>Raboushee</t>
-        </is>
-      </c>
-      <c r="D153" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F153" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I153" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>10h 30m</t>
-        </is>
-      </c>
-      <c r="G154" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E155" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F155" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G155" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I155" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B156" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="inlineStr">
-        <is>
-          <t>Osama Alkabbani</t>
-        </is>
-      </c>
-      <c r="D156" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E156" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F156" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G156" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I156" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>03:00 AM</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -7547,16 +7547,16 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G157" s="7" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
@@ -7565,159 +7565,159 @@
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>5h 30m</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>Afternoon Duty</t>
-        </is>
-      </c>
-      <c r="I158" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>06:00 AM</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>13h 15m</t>
+          <t>11h 30m</t>
         </is>
       </c>
       <c r="G159" s="7" t="n">
-        <v>13.25</v>
+        <v>11.5</v>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
-        <is>
-          <t>Osama Alkabbani</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>06:00 AM</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>11h 30m</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
@@ -7727,106 +7727,106 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>10h 30m</t>
         </is>
       </c>
       <c r="G161" s="7" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
         </is>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>05:40 PM</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>10h 40m</t>
-        </is>
-      </c>
-      <c r="G162" s="4" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I162" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E162" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="G163" s="7" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
@@ -7835,64 +7835,64 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty</t>
+          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
         </is>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>06:00 AM</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>11h 30m</t>
-        </is>
-      </c>
-      <c r="G164" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+      <c r="D164" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F164" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
@@ -7925,50 +7925,500 @@
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>5h 30m</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Afternoon Duty</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>13h 15m</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>9h 20m</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>10h 40m</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C166" s="3" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>04:51 PM</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>9h 21m</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>10h 00m</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G176" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
       </c>
-      <c r="I166" s="3" t="inlineStr">
+      <c r="I176" s="3" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (07:00 AM – 05:00 PM / 10h 00m)</t>
         </is>
@@ -12110,20 +12560,20 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>72</v>
+        <v>74.75</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>174</v>
+        <v>173.6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>246</v>
+        <v>248.35</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -12132,17 +12582,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>69.33</v>
+        <v>72</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>169.67</v>
+        <v>174</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>27</v>
@@ -12154,20 +12604,20 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>66.67</v>
+        <v>69.33</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>107.09</v>
+        <v>169.67</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>173.76</v>
+        <v>239</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -12176,20 +12626,20 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>84.66</v>
+        <v>66.67</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>84.34999999999999</v>
+        <v>107.09</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>169.01</v>
+        <v>173.76</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -12198,17 +12648,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>74.75</v>
+        <v>84.66</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>82.16</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>156.91</v>
+        <v>169.01</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>17</v>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -675,12 +675,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Paid Mission</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -1135,47 +1135,47 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Paid Mission</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1657,20 +1657,20 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Mission</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2152,20 +2152,20 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G37" s="7" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Paid Shift</t>
+          <t>Paid Mission</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2647,11 +2647,11 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training / HQ SERAVIA (07:45 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3132,21 +3132,21 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:40 AM</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 20m</t>
         </is>
       </c>
       <c r="G59" s="7" t="n">
-        <v>8.08</v>
+        <v>8.33</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training / HQ SERAVIA (07:40 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3627,21 +3627,21 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:13 AM</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>8h 47m</t>
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>7.42</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:13 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4122,21 +4122,21 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:18 AM</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>8h 42m</t>
         </is>
       </c>
       <c r="G81" s="7" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:18 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4617,30 +4617,30 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:05 AM</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>05:13 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>9h 23m</t>
+          <t>8h 55m</t>
         </is>
       </c>
       <c r="G92" s="4" t="n">
-        <v>9.380000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:05 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -5112,21 +5112,21 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>07:47 AM</t>
+          <t>07:10 AM</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>03:35 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>7h 48m</t>
+          <t>8h 50m</t>
         </is>
       </c>
       <c r="G103" s="7" t="n">
-        <v>7.8</v>
+        <v>8.83</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:10 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -5590,47 +5590,47 @@
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G114" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Paid Mission</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>🏢 Official Airport Mission / Pass Delay (Company Paid)</t>
         </is>
       </c>
     </row>
@@ -6097,35 +6097,35 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>05:05 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>9h 05m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="G125" s="7" t="n">
-        <v>9.08</v>
+        <v>8.75</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -6152,25 +6152,25 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:05 PM</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 05m</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">
-        <v>8.5</v>
+        <v>9.08</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -6232,80 +6232,80 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G128" s="4" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G129" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>08:05 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6337,11 +6337,11 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>7h 55m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6367,35 +6367,35 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:05 AM</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>7h 55m</t>
         </is>
       </c>
       <c r="G131" s="7" t="n">
-        <v>8.5</v>
+        <v>7.92</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6412,26 +6412,26 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 20m</t>
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:05 PM)</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -6467,25 +6467,25 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G133" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -6502,52 +6502,52 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -6557,16 +6557,16 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>04:15 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G135" s="7" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
@@ -6582,45 +6582,45 @@
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G136" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -6647,25 +6647,25 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G137" s="7" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6692,16 +6692,16 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G138" s="4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6727,12 +6727,12 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -6742,11 +6742,11 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G139" s="7" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6772,52 +6772,52 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -6827,16 +6827,16 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G141" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
@@ -6852,17 +6852,17 @@
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6897,45 +6897,45 @@
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G143" s="7" t="n">
-        <v>8.08</v>
+        <v>6</v>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6962,16 +6962,16 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G144" s="4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -7042,116 +7042,116 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>6</v>
+        <v>8.08</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:55 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G147" s="7" t="n">
-        <v>5.5</v>
+        <v>8.08</v>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>08:10 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>4h 50m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G148" s="4" t="n">
-        <v>4.83</v>
+        <v>8.5</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -7167,17 +7167,17 @@
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -7187,16 +7187,16 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G149" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
@@ -7212,45 +7212,45 @@
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G150" s="4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7267,137 +7267,137 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G151" s="7" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:10 AM</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>4h 50m</t>
         </is>
       </c>
       <c r="G152" s="4" t="n">
-        <v>9</v>
+        <v>4.83</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>5h 45m</t>
         </is>
       </c>
       <c r="G153" s="7" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 01:30 PM)</t>
         </is>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -7407,42 +7407,42 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G154" s="4" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -7452,42 +7452,42 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G155" s="7" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -7497,42 +7497,42 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>03:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G156" s="4" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -7547,16 +7547,16 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>03:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G157" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
@@ -7570,263 +7570,263 @@
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B158" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D158" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E158" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F158" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G158" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I158" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>07:10 AM</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>8h 50m</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:10 AM – 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>06:00 AM</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>05:30 PM</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>11h 30m</t>
         </is>
       </c>
-      <c r="G159" s="7" t="n">
+      <c r="G160" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="H159" s="5" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
       </c>
-      <c r="I159" s="6" t="inlineStr">
+      <c r="I160" s="3" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C160" s="9" t="inlineStr">
-        <is>
-          <t>Raboushee</t>
-        </is>
-      </c>
-      <c r="D160" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E160" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F160" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G160" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I160" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>10h 30m</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H161" s="5" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C162" s="9" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D162" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E162" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F162" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G162" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I162" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>03:00 AM</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G163" s="7" t="n">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
@@ -7835,24 +7835,24 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
@@ -7880,74 +7880,74 @@
       </c>
       <c r="I164" s="9" t="inlineStr">
         <is>
-          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>Raboushee</t>
-        </is>
-      </c>
-      <c r="D165" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="G165" s="7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H165" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G165" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>06:00 AM</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -7957,191 +7957,191 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>11h 30m</t>
         </is>
       </c>
       <c r="G166" s="4" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Afternoon Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D167" s="5" t="inlineStr">
-        <is>
-          <t>03:15 AM</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>13h 15m</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="H167" s="5" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>10h 30m</t>
         </is>
       </c>
       <c r="G168" s="4" t="n">
-        <v>9.33</v>
+        <v>10.5</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
         </is>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>Osama Alkabbani</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
-        <is>
-          <t>06:00 AM</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>11h 30m</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H169" s="5" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I169" s="6" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G169" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="G170" s="4" t="n">
-        <v>9.67</v>
+        <v>8.75</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -8150,133 +8150,133 @@
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
         </is>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:07 AM</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>05:40 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>10h 40m</t>
+          <t>8h 53m</t>
         </is>
       </c>
       <c r="G171" s="7" t="n">
-        <v>10.67</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:07 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G172" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Ground Duty</t>
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F172" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G172" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>04:51 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>9h 21m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G173" s="7" t="n">
-        <v>9.35</v>
+        <v>9.5</v>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
@@ -8285,29 +8285,29 @@
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8317,108 +8317,558 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G174" s="4" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Afternoon Duty</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
         </is>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>13h 15m</t>
         </is>
       </c>
       <c r="G175" s="7" t="n">
-        <v>9.5</v>
+        <v>13.25</v>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
         </is>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>9h 20m</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I176" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>9h 20m</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 04:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>10h 40m</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B181" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>04:51 PM</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>9h 21m</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 05:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>10h 00m</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G186" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
       </c>
-      <c r="I176" s="3" t="inlineStr">
+      <c r="I186" s="3" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (07:00 AM – 05:00 PM / 10h 00m)</t>
         </is>
@@ -12604,20 +13054,20 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>69.33</v>
+        <v>71</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>169.67</v>
+        <v>172.68</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>239</v>
+        <v>243.68</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -12626,20 +13076,20 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>66.67</v>
+        <v>69.33</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>107.09</v>
+        <v>169.67</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>173.76</v>
+        <v>239</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -12648,20 +13098,20 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>84.66</v>
+        <v>66.67</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>84.34999999999999</v>
+        <v>107.09</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>169.01</v>
+        <v>173.76</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -12670,17 +13120,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Mohamed Adnan</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>71</v>
+        <v>84.66</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>73.42999999999999</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>144.43</v>
+        <v>169.01</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>17</v>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -488,12 +488,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I186"/>
+  <dimension ref="A1:I196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -697,7 +697,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1180,47 +1180,47 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Mohamed Adnan</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1702,20 +1702,20 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G27" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3182,16 +3182,16 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -3667,26 +3667,26 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>03:55 AM</t>
+          <t>08:40 AM</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>11h 25m</t>
+          <t>6h 50m</t>
         </is>
       </c>
       <c r="G71" s="7" t="n">
-        <v>11.42</v>
+        <v>6.83</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (08:40 AM – 03:30 PM)</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4172,25 +4172,25 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>10h 35m</t>
+          <t>10h 45m</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>10.58</v>
+        <v>10.75</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Early dawn flight departure handling (10h 45m)</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -4667,25 +4667,25 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>05:13 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>12h 28m</t>
+          <t>12h 15m</t>
         </is>
       </c>
       <c r="G93" s="7" t="n">
-        <v>12.47</v>
+        <v>12.25</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 04:45 AM / Logged out 05:13 PM)</t>
+          <t>✈️ Early dawn flight departure handling (12h 15m)</t>
         </is>
       </c>
     </row>
@@ -5152,26 +5152,26 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>07:47 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>03:35 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>7h 48m</t>
+          <t>7h 30m</t>
         </is>
       </c>
       <c r="G104" s="4" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+          <t>✈️ Live Daily Ground Duty (08:00 AM – 03:30 PM)</t>
         </is>
       </c>
     </row>
@@ -5635,47 +5635,47 @@
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B115" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>Mohamed Adnan</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F115" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G115" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -6152,25 +6152,25 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>05:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>9h 05m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">
-        <v>9.08</v>
+        <v>8</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -6197,25 +6197,25 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:05 PM</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 05m</t>
         </is>
       </c>
       <c r="G127" s="7" t="n">
-        <v>8.5</v>
+        <v>9.08</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -6277,80 +6277,80 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G129" s="7" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>08:05 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>7h 55m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G131" s="7" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
@@ -6412,26 +6412,26 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>08:05 AM</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>8h 20m</t>
+          <t>7h 55m</t>
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>8.33</v>
+        <v>7.92</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:05 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6457,35 +6457,35 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 20m</t>
         </is>
       </c>
       <c r="G133" s="7" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:05 PM)</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -6512,16 +6512,16 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -6557,25 +6557,25 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G135" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -6592,52 +6592,52 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G136" s="4" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -6647,16 +6647,16 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>04:15 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G137" s="7" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
@@ -6672,45 +6672,45 @@
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G138" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6727,17 +6727,17 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6817,26 +6817,26 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G141" s="7" t="n">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6907,52 +6907,52 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G143" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6962,16 +6962,16 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G144" s="4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6987,17 +6987,17 @@
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -7032,45 +7032,45 @@
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>8.08</v>
+        <v>6</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:55 AM – 04:00 PM)</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -7102,20 +7102,20 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G147" s="7" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -7142,16 +7142,16 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G148" s="4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -7177,12 +7177,12 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -7192,11 +7192,11 @@
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G149" s="7" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:55 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7222,116 +7222,116 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G150" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G151" s="7" t="n">
-        <v>5.5</v>
+        <v>8.08</v>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>08:10 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>4h 50m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G152" s="4" t="n">
-        <v>4.83</v>
+        <v>8.5</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -7347,36 +7347,36 @@
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>5h 45m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G153" s="7" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
@@ -7385,52 +7385,52 @@
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 01:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G154" s="4" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -7492,232 +7492,232 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:10 AM</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>4h 50m</t>
         </is>
       </c>
       <c r="G156" s="4" t="n">
-        <v>9.5</v>
+        <v>4.83</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>5h 45m</t>
         </is>
       </c>
       <c r="G157" s="7" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 01:30 PM)</t>
         </is>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>12:30 PM</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>4h 30m</t>
         </is>
       </c>
       <c r="G158" s="4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>07:10 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>8h 50m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G159" s="7" t="n">
-        <v>8.83</v>
+        <v>8.5</v>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:10 AM – 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G160" s="4" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
@@ -7762,12 +7762,12 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>03:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -7777,37 +7777,37 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G162" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
@@ -7817,16 +7817,16 @@
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>03:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G163" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
@@ -7835,109 +7835,109 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C164" s="9" t="inlineStr">
-        <is>
-          <t>Joudi Alghorani</t>
-        </is>
-      </c>
-      <c r="D164" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E164" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F164" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G164" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I164" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>07:10 AM</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>8h 50m</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:10 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B165" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C165" s="9" t="inlineStr">
-        <is>
-          <t>Khaled</t>
-        </is>
-      </c>
-      <c r="D165" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E165" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F165" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G165" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -7975,488 +7975,488 @@
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="inlineStr">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D167" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E167" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F167" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G167" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I167" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>03:00 AM</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>10h 30m</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>03:30 PM</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F170" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G170" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F171" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G171" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>07:10 PM</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>12h 10m</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
       </c>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D169" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E169" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F169" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G169" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I169" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>Joudi Alghorani</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>07:15 AM</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>8h 45m</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>Khaled</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
-        <is>
-          <t>07:07 AM</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>8h 53m</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:07 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>Osama Alkabbani</t>
-        </is>
-      </c>
-      <c r="D172" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E172" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G172" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I172" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 07:10 PM / 12h 10m)</t>
         </is>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D173" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="G173" s="7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H173" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>5h 30m</t>
-        </is>
-      </c>
-      <c r="G174" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>Afternoon Duty</t>
-        </is>
-      </c>
-      <c r="I174" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G174" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>10h 30m</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D175" s="5" t="inlineStr">
-        <is>
-          <t>03:15 AM</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>13h 15m</t>
-        </is>
-      </c>
-      <c r="G175" s="7" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="H175" s="5" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="I175" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>Joudi Alghorani</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>07:20 AM</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>04:40 PM</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>9h 20m</t>
-        </is>
-      </c>
-      <c r="G176" s="4" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="I176" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
+      <c r="D176" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F176" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G176" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="G177" s="7" t="n">
-        <v>9.33</v>
+        <v>8.75</v>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
@@ -8465,69 +8465,69 @@
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 04:40 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
         </is>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>07:07 AM</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>8h 53m</t>
         </is>
       </c>
       <c r="G178" s="4" t="n">
-        <v>11.5</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:07 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
@@ -8537,106 +8537,106 @@
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>11h 30m</t>
         </is>
       </c>
       <c r="G179" s="7" t="n">
-        <v>9.67</v>
+        <v>11.5</v>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>05:40 PM</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>10h 40m</t>
-        </is>
-      </c>
-      <c r="G180" s="4" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+      <c r="A180" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E180" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G180" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I180" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G181" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
@@ -8645,230 +8645,680 @@
       </c>
       <c r="I181" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>04:51 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>9h 21m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G182" s="4" t="n">
-        <v>9.35</v>
+        <v>5.5</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Afternoon Duty</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
         </is>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>13h 15m</t>
         </is>
       </c>
       <c r="G183" s="7" t="n">
-        <v>9.67</v>
+        <v>13.25</v>
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 05:00 PM)</t>
+          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
         </is>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="G184" s="4" t="n">
-        <v>11.5</v>
+        <v>9.33</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
         </is>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="5" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>9h 20m</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 04:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E186" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G186" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10h 40m</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>04:51 PM</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>9h 21m</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 05:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>10h 40m</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="D195" s="5" t="inlineStr">
         <is>
           <t>07:30 AM</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E195" s="5" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
+      <c r="F195" s="5" t="inlineStr">
         <is>
           <t>9h 30m</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n">
+      <c r="G195" s="7" t="n">
         <v>9.5</v>
       </c>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="H195" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I195" s="6" t="inlineStr">
         <is>
           <t>✈️ Live Daily Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C186" s="3" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>10h 00m</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G196" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
       </c>
-      <c r="I186" s="3" t="inlineStr">
+      <c r="I196" s="3" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (07:00 AM – 05:00 PM / 10h 00m)</t>
         </is>
@@ -8890,7 +9340,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -9094,35 +9544,35 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Standardized</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>Standard daytime shift (8h 30m)</t>
         </is>
       </c>
     </row>
@@ -9589,7 +10039,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -9617,7 +10067,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard daytime shift (8h 30m)</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10534,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -10112,7 +10562,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard daytime shift (8h 30m)</t>
         </is>
       </c>
     </row>
@@ -10579,7 +11029,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10607,7 +11057,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>✈️ Dawn flight check-in &amp; boarding ops (12.83 hrs)</t>
+          <t>✈️ Early dawn flight departure handling (12h 50m)</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11524,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -11084,16 +11534,16 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>12h 20m</t>
+          <t>12h 50m</t>
         </is>
       </c>
       <c r="G49" s="7" t="n">
-        <v>12.33</v>
+        <v>12.83</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
@@ -11102,7 +11552,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>✈️ Dawn flight check-in &amp; boarding ops (12.33 hrs)</t>
+          <t>✈️ Early dawn flight departure handling (12h 50m)</t>
         </is>
       </c>
     </row>
@@ -11569,7 +12019,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -11579,16 +12029,16 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>12h 00m</t>
+          <t>12h 30m</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11597,7 +12047,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early morning departure ops (12.0 hrs)</t>
+          <t>✈️ Early morning departure ops (12h 30m)</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12514,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -12074,16 +12524,16 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>12h 00m</t>
+          <t>12h 30m</t>
         </is>
       </c>
       <c r="G71" s="7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
@@ -12092,7 +12542,7 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>✈️ Early morning departure ops (12.0 hrs)</t>
+          <t>✈️ Early morning departure ops (12h 30m)</t>
         </is>
       </c>
     </row>
@@ -12559,7 +13009,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -12921,7 +13371,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -12988,20 +13438,20 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>75.08</v>
+        <v>85.16</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>177</v>
+        <v>178.17</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>252.08</v>
+        <v>263.3299999999999</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -13010,20 +13460,20 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>74.75</v>
+        <v>75.08</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>173.6</v>
+        <v>177</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>248.35</v>
+        <v>252.08</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -13032,20 +13482,20 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>72</v>
+        <v>74.75</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>174</v>
+        <v>173.6</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>246</v>
+        <v>248.35</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -13054,20 +13504,20 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>172.68</v>
+        <v>174</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>243.68</v>
+        <v>246</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -13076,20 +13526,20 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>69.33</v>
+        <v>71</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>169.67</v>
+        <v>172.68</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>239</v>
+        <v>243.68</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -13098,20 +13548,20 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>66.67</v>
+        <v>69.33</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>107.09</v>
+        <v>169.67</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>173.76</v>
+        <v>239</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -13120,20 +13570,20 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Adnan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>84.66</v>
+        <v>66.67</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>84.34999999999999</v>
+        <v>107.09</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>169.01</v>
+        <v>173.76</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I196"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>02:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6h 15m</t>
+          <t>7h 15m</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
+          <t>🎓 Training Session (07:45 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -1495,47 +1495,47 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2017,20 +2017,20 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2502,30 +2502,30 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>7h 00m</t>
         </is>
       </c>
       <c r="G45" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>🎓 Training Session (08:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:30 AM</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3007,20 +3007,20 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3492,30 +3492,30 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G67" s="7" t="n">
-        <v>8.08</v>
+        <v>9</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3987,21 +3987,21 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>04:00 AM</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>12h 00m</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>7.42</v>
+        <v>12</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Early dawn flight departure handling (12h 00m)</t>
         </is>
       </c>
     </row>
@@ -4482,30 +4482,30 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G89" s="7" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4977,21 +4977,21 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>03:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>7h 40m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G100" s="4" t="n">
-        <v>7.67</v>
+        <v>9</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -5472,21 +5472,21 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>07:47 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>03:35 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>7h 48m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G111" s="7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -5950,47 +5950,47 @@
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C122" s="9" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D122" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F122" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G122" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I122" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -6357,36 +6357,36 @@
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G131" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>08:05 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6427,11 +6427,11 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>7h 55m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6457,26 +6457,26 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>08:05 AM</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>8h 20m</t>
+          <t>7h 55m</t>
         </is>
       </c>
       <c r="G133" s="7" t="n">
-        <v>8.33</v>
+        <v>7.92</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:05 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6502,26 +6502,26 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 20m</t>
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:05 PM)</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -6557,25 +6557,25 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G135" s="7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6615,12 +6615,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -6647,16 +6647,16 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G137" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
@@ -6682,116 +6682,116 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G138" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>04:15 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G139" s="7" t="n">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6817,17 +6817,17 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -6922,20 +6922,20 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="G143" s="7" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6962,16 +6962,16 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G144" s="4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7042,52 +7042,52 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
@@ -7122,81 +7122,81 @@
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G148" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G149" s="7" t="n">
-        <v>8.08</v>
+        <v>6</v>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:55 AM – 04:00 PM)</t>
+          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -7282,20 +7282,20 @@
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G151" s="7" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -7312,26 +7312,26 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G152" s="4" t="n">
-        <v>8.5</v>
+        <v>8.08</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:55 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -7402,52 +7402,52 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>6h 00m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="G154" s="4" t="n">
-        <v>6</v>
+        <v>8.08</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -7457,16 +7457,16 @@
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G155" s="7" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
@@ -7482,36 +7482,36 @@
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>08:10 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>4h 50m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="G156" s="4" t="n">
-        <v>4.83</v>
+        <v>8</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -7527,81 +7527,81 @@
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>5h 45m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G157" s="7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 01:30 PM)</t>
+          <t>Daily Station Duty (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>12:30 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>4h 30m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="G158" s="4" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -7637,16 +7637,16 @@
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G159" s="7" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
@@ -7672,26 +7672,26 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:10 AM</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>4h 50m</t>
         </is>
       </c>
       <c r="G160" s="4" t="n">
-        <v>5.5</v>
+        <v>4.83</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7717,187 +7717,187 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:45 AM</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>5h 45m</t>
         </is>
       </c>
       <c r="G161" s="7" t="n">
-        <v>9.5</v>
+        <v>5.75</v>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>🎓 Etihad Altéa DCS Training / HQ SERAVIA (07:45 AM – 01:30 PM)</t>
         </is>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>12:30 PM</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>4h 30m</t>
         </is>
       </c>
       <c r="G162" s="4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G163" s="7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>07:10 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>8h 50m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G164" s="4" t="n">
-        <v>8.83</v>
+        <v>5.5</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:10 AM – 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
@@ -7907,16 +7907,16 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G165" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
@@ -7925,52 +7925,52 @@
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G166" s="4" t="n">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
@@ -7997,16 +7997,16 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G167" s="7" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>03:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8047,172 +8047,172 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G168" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
+          <t>07:10 AM</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>8h 50m</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:10 AM – 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>03:30 PM</t>
-        </is>
-      </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>8h 30m</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H169" s="5" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I169" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C170" s="9" t="inlineStr">
-        <is>
-          <t>Joudi Alghorani</t>
-        </is>
-      </c>
-      <c r="D170" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E170" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F170" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G170" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I170" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B171" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="inlineStr">
-        <is>
-          <t>Khaled</t>
-        </is>
-      </c>
-      <c r="D171" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E171" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F171" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G171" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H171" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -8222,115 +8222,115 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>07:10 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>12h 10m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G172" s="4" t="n">
-        <v>12.17</v>
+        <v>9.5</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 07:10 PM / 12h 10m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>03:00 AM</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="G173" s="7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
         </is>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C174" s="9" t="inlineStr">
-        <is>
-          <t>Raboushee</t>
-        </is>
-      </c>
-      <c r="D174" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E174" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F174" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G174" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I174" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
@@ -8357,42 +8357,42 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>03:30 PM</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>10h 30m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G175" s="7" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
@@ -8425,119 +8425,119 @@
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>Joudi Alghorani</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="inlineStr">
-        <is>
-          <t>07:15 AM</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>8h 45m</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="H177" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="I177" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G177" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>07:07 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>07:10 PM</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>8h 53m</t>
+          <t>12h 10m</t>
         </is>
       </c>
       <c r="G178" s="4" t="n">
-        <v>8.880000000000001</v>
+        <v>12.17</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:07 AM – 04:00 PM)</t>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 07:10 PM / 12h 10m)</t>
         </is>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>06:00 AM</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
@@ -8555,24 +8555,24 @@
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 06:30 PM / 11h 30m)</t>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
@@ -8600,24 +8600,24 @@
       </c>
       <c r="I180" s="9" t="inlineStr">
         <is>
-          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
@@ -8627,127 +8627,127 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>10h 30m</t>
         </is>
       </c>
       <c r="G181" s="7" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I181" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
         </is>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>5h 30m</t>
-        </is>
-      </c>
-      <c r="G182" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>Afternoon Duty</t>
-        </is>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="20" customHeight="1">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C183" s="6" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D183" s="5" t="inlineStr">
-        <is>
-          <t>03:15 AM</t>
-        </is>
-      </c>
-      <c r="E183" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>13h 15m</t>
-        </is>
-      </c>
-      <c r="G183" s="7" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="H183" s="5" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="I183" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+      <c r="D183" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E183" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I183" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -8757,21 +8757,21 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="G184" s="4" t="n">
-        <v>9.33</v>
+        <v>8.75</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8780,19 +8780,19 @@
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
         </is>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -8802,21 +8802,21 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:07 AM</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>8h 53m</t>
         </is>
       </c>
       <c r="G185" s="7" t="n">
-        <v>9.33</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
@@ -8825,109 +8825,109 @@
       </c>
       <c r="I185" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 04:40 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:07 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B186" s="8" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t>Mohammad Almohammad</t>
         </is>
       </c>
-      <c r="D186" s="8" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E186" s="8" t="inlineStr">
+      <c r="E187" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F186" s="8" t="inlineStr">
+      <c r="F187" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G186" s="10" t="n">
+      <c r="G187" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H186" s="8" t="inlineStr">
+      <c r="H187" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>Osama Alkabbani</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
-        <is>
-          <t>06:00 AM</t>
-        </is>
-      </c>
-      <c r="E187" s="5" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>11h 30m</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H187" s="5" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I187" s="6" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+      <c r="I187" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -8942,16 +8942,16 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G188" s="4" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8960,19 +8960,19 @@
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -8982,137 +8982,137 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>05:40 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>10h 40m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G189" s="7" t="n">
-        <v>10.67</v>
+        <v>5.5</v>
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Afternoon Duty</t>
         </is>
       </c>
       <c r="I189" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
         </is>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="G190" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="I190" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Ground Duty</t>
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E190" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F190" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G190" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I190" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>04:51 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>9h 21m</t>
+          <t>13h 15m</t>
         </is>
       </c>
       <c r="G191" s="7" t="n">
-        <v>9.35</v>
+        <v>13.25</v>
       </c>
       <c r="H191" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I191" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
         </is>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -9122,16 +9122,16 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="G192" s="4" t="n">
-        <v>9.67</v>
+        <v>9.33</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -9140,187 +9140,637 @@
       </c>
       <c r="I192" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 05:00 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
         </is>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>9h 20m</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 04:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C194" s="9" t="inlineStr">
+        <is>
           <t>Mohammad Almohammad</t>
         </is>
       </c>
-      <c r="D193" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>05:40 PM</t>
-        </is>
-      </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>10h 40m</t>
-        </is>
-      </c>
-      <c r="G193" s="7" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="H193" s="5" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="20" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="inlineStr">
-        <is>
-          <t>Osama Alkabbani</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>06:00 AM</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>11h 30m</t>
-        </is>
-      </c>
-      <c r="G194" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I194" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I194" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>06:00 AM</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>11h 30m</t>
         </is>
       </c>
       <c r="G195" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I195" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>10h 40m</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>04:00 AM</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>12h 30m</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (12h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B199" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C196" s="3" t="inlineStr">
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>04:51 PM</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>9h 21m</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 05:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>10h 40m</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D205" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E205" s="5" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F205" s="5" t="inlineStr">
         <is>
           <t>10h 00m</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H205" s="5" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
       </c>
-      <c r="I196" s="3" t="inlineStr">
+      <c r="I205" s="6" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (07:00 AM – 05:00 PM / 10h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (08:00 AM – 05:00 PM)</t>
         </is>
       </c>
     </row>
@@ -9864,7 +10314,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9874,20 +10324,20 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Standardized</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10809,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -10369,11 +10819,11 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -10382,7 +10832,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -10854,7 +11304,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -10864,11 +11314,11 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -10877,7 +11327,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -11332,47 +11782,47 @@
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled weekly day off</t>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -11867,7 +12317,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Morning flight shift</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12812,7 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Morning flight shift</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -12857,7 +13307,7 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Morning flight shift (4:00 PM return)</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -13504,20 +13954,20 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>72</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>174</v>
+        <v>175.25</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>246</v>
+        <v>247.25</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -13526,20 +13976,20 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>172.68</v>
+        <v>174</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>243.68</v>
+        <v>246</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -13548,20 +13998,20 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>69.33</v>
+        <v>71</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>169.67</v>
+        <v>172.68</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>239</v>
+        <v>243.68</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -13570,20 +14020,20 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>66.67</v>
+        <v>69.33</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>107.09</v>
+        <v>169.67</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>173.76</v>
+        <v>239</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -13592,20 +14042,20 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>61.5</v>
+        <v>66.67</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>69.72</v>
+        <v>107.09</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>131.22</v>
+        <v>173.76</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:I212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1747,20 +1747,20 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2242,20 +2242,20 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Paid Shift</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -6202,20 +6202,20 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>9h 05m</t>
+          <t>9h 10m</t>
         </is>
       </c>
       <c r="G127" s="7" t="n">
-        <v>9.08</v>
+        <v>9.17</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 05:05 PM)</t>
         </is>
       </c>
     </row>
@@ -6615,12 +6615,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 08:00 AM / Logged out 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -7020,12 +7020,12 @@
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 08:00 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7425,12 +7425,12 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -7807,26 +7807,26 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>12:30 PM</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>4h 35m</t>
         </is>
       </c>
       <c r="G163" s="7" t="n">
-        <v>8.5</v>
+        <v>4.58</v>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 12:30 PM)</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -7862,16 +7862,16 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="G164" s="4" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7897,35 +7897,35 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G165" s="7" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -7970,24 +7970,24 @@
       </c>
       <c r="I166" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
@@ -7997,16 +7997,16 @@
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G167" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -8032,7 +8032,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
@@ -8077,12 +8077,12 @@
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>07:10 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -8092,11 +8092,11 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>8h 50m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G169" s="7" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:10 AM – 04:00 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
@@ -8122,12 +8122,12 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:10 AM</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8137,11 +8137,11 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 50m</t>
         </is>
       </c>
       <c r="G170" s="4" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:10 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -8167,35 +8167,35 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G171" s="7" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
         </is>
       </c>
     </row>
@@ -8212,26 +8212,26 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>03:37 PM</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>7h 37m</t>
         </is>
       </c>
       <c r="G172" s="4" t="n">
-        <v>9.5</v>
+        <v>7.62</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>✈️ Live Daily Duty (Logged in 08:00 AM / Logged out 03:37 PM | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
         </is>
       </c>
     </row>
@@ -8257,35 +8257,35 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>03:00 AM</t>
+          <t>06:00 AM</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>11h 30m</t>
         </is>
       </c>
       <c r="G173" s="7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -8330,322 +8330,322 @@
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
         <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>03:00 AM</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I176" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="B177" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
+      <c r="C177" s="6" t="inlineStr">
         <is>
           <t>Hanan</t>
         </is>
       </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E175" s="5" t="inlineStr">
+      <c r="E177" s="5" t="inlineStr">
         <is>
           <t>03:30 PM</t>
         </is>
       </c>
-      <c r="F175" s="5" t="inlineStr">
+      <c r="F177" s="5" t="inlineStr">
         <is>
           <t>8h 30m</t>
         </is>
       </c>
-      <c r="G175" s="7" t="n">
+      <c r="G177" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="H175" s="5" t="inlineStr">
+      <c r="H177" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I175" s="6" t="inlineStr">
+      <c r="I177" s="6" t="inlineStr">
         <is>
           <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="8" t="inlineStr">
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C176" s="9" t="inlineStr">
+      <c r="C178" s="9" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="D176" s="8" t="inlineStr">
+      <c r="D178" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E176" s="8" t="inlineStr">
+      <c r="E178" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F176" s="8" t="inlineStr">
+      <c r="F178" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G176" s="10" t="n">
+      <c r="G178" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H176" s="8" t="inlineStr">
+      <c r="H178" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I176" s="9" t="inlineStr">
+      <c r="I178" s="9" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="8" t="inlineStr">
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="8" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
+      <c r="C179" s="9" t="inlineStr">
         <is>
           <t>Khaled</t>
         </is>
       </c>
-      <c r="D177" s="8" t="inlineStr">
+      <c r="D179" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E177" s="8" t="inlineStr">
+      <c r="E179" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F177" s="8" t="inlineStr">
+      <c r="F179" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G177" s="10" t="n">
+      <c r="G179" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H177" s="8" t="inlineStr">
+      <c r="H179" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I177" s="9" t="inlineStr">
+      <c r="I179" s="9" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="20" customHeight="1">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>Mohammad Almohammad</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>07:10 PM</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>12h 10m</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G180" s="4" t="n">
         <v>12.17</v>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>Extended Shift</t>
         </is>
       </c>
-      <c r="I178" s="3" t="inlineStr">
+      <c r="I180" s="3" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (07:00 AM – 07:10 PM / 12h 10m)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="5" t="inlineStr">
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="8" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
-        <is>
-          <t>Osama Alkabbani</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
-        <is>
-          <t>06:00 AM</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>11h 30m</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H179" s="5" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I179" s="6" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C180" s="9" t="inlineStr">
-        <is>
-          <t>Raboushee</t>
-        </is>
-      </c>
-      <c r="D180" s="8" t="inlineStr">
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E180" s="8" t="inlineStr">
+      <c r="E181" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F180" s="8" t="inlineStr">
+      <c r="F181" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G180" s="10" t="n">
+      <c r="G181" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H180" s="8" t="inlineStr">
+      <c r="H181" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I180" s="9" t="inlineStr">
+      <c r="I181" s="9" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="20" customHeight="1">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>Rasheed Akel</t>
-        </is>
-      </c>
-      <c r="D181" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E181" s="5" t="inlineStr">
-        <is>
-          <t>05:30 PM</t>
-        </is>
-      </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>10h 30m</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H181" s="5" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
         </is>
       </c>
     </row>
@@ -8662,52 +8662,52 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>03:30 AM</t>
+          <t>06:00 AM</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>11h 30m</t>
         </is>
       </c>
       <c r="G182" s="4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D183" s="8" t="inlineStr">
@@ -8742,180 +8742,180 @@
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>10h 30m</t>
         </is>
       </c>
       <c r="G184" s="4" t="n">
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
         </is>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="5" t="inlineStr">
         <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>Khaled</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
-        <is>
-          <t>07:07 AM</t>
-        </is>
-      </c>
-      <c r="E185" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>8h 53m</t>
-        </is>
-      </c>
-      <c r="G185" s="7" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E186" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G186" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>8h 45m</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:07 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C186" s="3" t="inlineStr">
-        <is>
-          <t>Mohammad Almohammad</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>11h 30m</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>Extended Shift</t>
-        </is>
-      </c>
-      <c r="I186" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 06:30 PM / 11h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B187" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C187" s="9" t="inlineStr">
-        <is>
-          <t>Osama Alkabbani</t>
-        </is>
-      </c>
-      <c r="D187" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E187" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F187" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G187" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I187" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
         </is>
       </c>
     </row>
@@ -8932,26 +8932,26 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:07 AM</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>8h 53m</t>
         </is>
       </c>
       <c r="G188" s="4" t="n">
-        <v>9.5</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:07 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -8977,161 +8977,161 @@
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>11h 30m</t>
         </is>
       </c>
       <c r="G189" s="7" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>Afternoon Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I189" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
-      <c r="A190" s="8" t="inlineStr">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C190" s="9" t="inlineStr">
-        <is>
-          <t>Yasmin</t>
-        </is>
-      </c>
-      <c r="D190" s="8" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C191" s="9" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E190" s="8" t="inlineStr">
+      <c r="E191" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F190" s="8" t="inlineStr">
+      <c r="F191" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="G190" s="10" t="n">
+      <c r="G191" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H190" s="8" t="inlineStr">
+      <c r="H191" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="I190" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="20" customHeight="1">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C191" s="6" t="inlineStr">
-        <is>
-          <t>Hanan</t>
-        </is>
-      </c>
-      <c r="D191" s="5" t="inlineStr">
-        <is>
-          <t>03:15 AM</t>
-        </is>
-      </c>
-      <c r="E191" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>13h 15m</t>
-        </is>
-      </c>
-      <c r="G191" s="7" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="H191" s="5" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="I191" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+      <c r="I191" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="G192" s="4" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -9140,69 +9140,69 @@
       </c>
       <c r="I192" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 30m)</t>
         </is>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="G193" s="7" t="n">
-        <v>9.33</v>
+        <v>5.5</v>
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Afternoon Duty</t>
         </is>
       </c>
       <c r="I193" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 04:40 PM)</t>
+          <t>✈️ Live Afternoon Station Duty (12:00 PM – 05:30 PM / 5h 30m)</t>
         </is>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C194" s="9" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
@@ -9247,35 +9247,35 @@
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>13h 15m</t>
         </is>
       </c>
       <c r="G195" s="7" t="n">
-        <v>11.5</v>
+        <v>13.25</v>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I195" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
         </is>
       </c>
     </row>
@@ -9292,12 +9292,12 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -9307,11 +9307,11 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="G196" s="4" t="n">
-        <v>9.67</v>
+        <v>9.33</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
         </is>
       </c>
     </row>
@@ -9337,116 +9337,116 @@
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>05:40 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>10h 40m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="G197" s="7" t="n">
-        <v>10.67</v>
+        <v>9.33</v>
       </c>
       <c r="H197" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I197" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 04:40 PM)</t>
         </is>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="A198" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C198" s="3" t="inlineStr">
-        <is>
-          <t>Yasmin</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>04:00 AM</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>12h 30m</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="I198" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (12h 30m)</t>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E198" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F198" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G198" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I198" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>Hanan</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:55 AM</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>06:24 PM</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>10h 29m</t>
         </is>
       </c>
       <c r="G199" s="7" t="n">
-        <v>9</v>
+        <v>10.48</v>
       </c>
       <c r="H199" s="5" t="inlineStr">
         <is>
@@ -9455,79 +9455,79 @@
       </c>
       <c r="I199" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty</t>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:55 AM / Logged out 06:24 PM)</t>
         </is>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>06:00 AM</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>04:51 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>9h 21m</t>
+          <t>11h 30m</t>
         </is>
       </c>
       <c r="G200" s="4" t="n">
-        <v>9.35</v>
+        <v>11.5</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
         </is>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
@@ -9545,24 +9545,24 @@
       </c>
       <c r="I201" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 05:00 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (9h 40m)</t>
         </is>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -9597,45 +9597,45 @@
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>06:00 AM</t>
+          <t>04:00 AM</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>11h 30m</t>
+          <t>12h 30m</t>
         </is>
       </c>
       <c r="G203" s="7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="H203" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="I203" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+          <t>✈️ Early dawn flight departure handling (12h 30m)</t>
         </is>
       </c>
     </row>
@@ -9652,12 +9652,12 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Hanan</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9667,11 +9667,11 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="G204" s="4" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+          <t>✈️ Live Daily Ground Duty</t>
         </is>
       </c>
     </row>
@@ -9697,35 +9697,35 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:30 AM</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>04:51 PM</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>10h 00m</t>
+          <t>9h 21m</t>
         </is>
       </c>
       <c r="G205" s="7" t="n">
-        <v>10</v>
+        <v>9.35</v>
       </c>
       <c r="H205" s="5" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="I205" s="6" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (07:00 AM – 05:00 PM / 10h 00m)</t>
+          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
         </is>
       </c>
     </row>
@@ -9742,33 +9742,303 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 05:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>10h 40m</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:40 PM / 10h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>04:20 PM</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 04:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>06:00 AM</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:00 AM – 05:30 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>10h 00m</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:00 PM / 10h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
           <t>Yasmin</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>05:00 PM</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G212" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="I206" s="3" t="inlineStr">
+      <c r="I212" s="3" t="inlineStr">
         <is>
           <t>✈️ Live Daily Ground Duty (08:00 AM – 05:00 PM)</t>
         </is>
@@ -14049,13 +14319,13 @@
         <v>66.67</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>107.09</v>
+        <v>147.45</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>173.76</v>
+        <v>214.12</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -39,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +62,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -121,6 +127,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -488,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I212"/>
+  <dimension ref="A1:I213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2727,21 +2742,21 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>8</v>
+        <v>9.33</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -3222,21 +3237,21 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:45 PM</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>9h 25m</t>
         </is>
       </c>
       <c r="G61" s="7" t="n">
-        <v>8.08</v>
+        <v>9.42</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
@@ -3717,21 +3732,21 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>7.42</v>
+        <v>8.75</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3740,7 +3755,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:15 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4212,21 +4227,21 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:10 AM</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>8h 50m</t>
         </is>
       </c>
       <c r="G83" s="7" t="n">
-        <v>7.5</v>
+        <v>8.83</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
@@ -4235,7 +4250,7 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4707,21 +4722,21 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:10 AM</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>05:13 PM</t>
+          <t>05:53 PM</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>9h 23m</t>
+          <t>10h 43m</t>
         </is>
       </c>
       <c r="G94" s="4" t="n">
-        <v>9.380000000000001</v>
+        <v>10.72</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4730,7 +4745,7 @@
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 05:53 PM)</t>
         </is>
       </c>
     </row>
@@ -5202,21 +5217,21 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>07:47 AM</t>
+          <t>07:07 AM</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>03:35 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>7h 48m</t>
+          <t>9h 08m</t>
         </is>
       </c>
       <c r="G105" s="7" t="n">
-        <v>7.8</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
@@ -5225,7 +5240,7 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:07 AM / Logged out 04:15 PM)</t>
         </is>
       </c>
     </row>
@@ -6192,21 +6207,21 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>05:05 PM</t>
+          <t>05:45 PM</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>9h 10m</t>
+          <t>10h 30m</t>
         </is>
       </c>
       <c r="G127" s="7" t="n">
-        <v>9.17</v>
+        <v>10.5</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
@@ -6215,7 +6230,7 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 05:05 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 05:45 PM)</t>
         </is>
       </c>
     </row>
@@ -6597,21 +6612,21 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:10 PM</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 50m</t>
         </is>
       </c>
       <c r="G136" s="4" t="n">
-        <v>8.5</v>
+        <v>9.83</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6620,7 +6635,7 @@
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 05:10 PM)</t>
         </is>
       </c>
     </row>
@@ -7002,21 +7017,21 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="G145" s="7" t="n">
-        <v>8</v>
+        <v>9.33</v>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
@@ -7025,7 +7040,7 @@
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 04:40 PM)</t>
         </is>
       </c>
     </row>
@@ -7407,21 +7422,21 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>9h 25m</t>
         </is>
       </c>
       <c r="G154" s="4" t="n">
-        <v>8.08</v>
+        <v>9.42</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -7430,7 +7445,7 @@
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 04:40 PM)</t>
         </is>
       </c>
     </row>
@@ -7812,21 +7827,21 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>12:30 PM</t>
+          <t>01:10 PM</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>4h 35m</t>
+          <t>5h 55m</t>
         </is>
       </c>
       <c r="G163" s="7" t="n">
-        <v>4.58</v>
+        <v>5.92</v>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
@@ -7835,7 +7850,7 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 12:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 01:10 PM)</t>
         </is>
       </c>
     </row>
@@ -8217,21 +8232,21 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>03:37 PM</t>
+          <t>04:17 PM</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>7h 37m</t>
+          <t>8h 57m</t>
         </is>
       </c>
       <c r="G172" s="4" t="n">
-        <v>7.62</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -8240,7 +8255,7 @@
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 08:00 AM / Logged out 03:37 PM | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:20 AM / Logged out 04:17 PM | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
         </is>
       </c>
     </row>
@@ -9027,21 +9042,21 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="G190" s="4" t="n">
-        <v>7.42</v>
+        <v>8.75</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -9050,7 +9065,7 @@
       </c>
       <c r="I190" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -9432,21 +9447,21 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>06:24 PM</t>
+          <t>07:04 PM</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>10h 29m</t>
+          <t>11h 49m</t>
         </is>
       </c>
       <c r="G199" s="7" t="n">
-        <v>10.48</v>
+        <v>11.82</v>
       </c>
       <c r="H199" s="5" t="inlineStr">
         <is>
@@ -9455,7 +9470,7 @@
       </c>
       <c r="I199" s="6" t="inlineStr">
         <is>
-          <t>⚡ Extended Shift / Overtime (Logged in 07:55 AM / Logged out 06:24 PM)</t>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 07:04 PM)</t>
         </is>
       </c>
     </row>
@@ -9837,21 +9852,21 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>04:20 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>8h 25m</t>
+          <t>9h 45m</t>
         </is>
       </c>
       <c r="G208" s="4" t="n">
-        <v>8.42</v>
+        <v>9.75</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9860,7 +9875,7 @@
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 04:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Logged out 05:00 PM)</t>
         </is>
       </c>
     </row>
@@ -10041,6 +10056,51 @@
       <c r="I212" s="3" t="inlineStr">
         <is>
           <t>✈️ Live Daily Ground Duty (08:00 AM – 05:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B213" s="11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C213" s="12" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D213" s="11" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G213" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="11" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I213" s="12" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Awaiting Checkout)</t>
         </is>
       </c>
     </row>
@@ -14319,10 +14379,10 @@
         <v>66.67</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>147.45</v>
+        <v>167.45</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>214.12</v>
+        <v>234.12</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>26</v>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -1240,47 +1240,47 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -14350,17 +14350,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Raboushee</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>69.33</v>
+        <v>66.67</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>169.67</v>
+        <v>176.45</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>239</v>
+        <v>243.12</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>27</v>
@@ -14372,20 +14372,20 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Raboushee</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>66.67</v>
+        <v>69.33</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>167.45</v>
+        <v>169.67</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>234.12</v>
+        <v>239</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -10082,16 +10082,16 @@
       </c>
       <c r="E213" s="11" t="inlineStr">
         <is>
-          <t>To Be Updated</t>
+          <t>06:40 PM</t>
         </is>
       </c>
       <c r="F213" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>11h 25m</t>
         </is>
       </c>
       <c r="G213" s="13" t="n">
-        <v>0</v>
+        <v>11.42</v>
       </c>
       <c r="H213" s="11" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="I213" s="12" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Awaiting Checkout)</t>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 06:40 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I213"/>
+  <dimension ref="A1:I214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10101,6 +10101,51 @@
       <c r="I213" s="12" t="inlineStr">
         <is>
           <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 06:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>07:30 PM</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>12h 10m</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:20 AM / Logged out 07:30 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I214"/>
+  <dimension ref="A1:I215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10146,6 +10146,51 @@
       <c r="I214" s="6" t="inlineStr">
         <is>
           <t>⚡ Extended Shift / Overtime (Logged in 07:20 AM / Logged out 07:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>07:24 AM</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>03:00 PM</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>7h 36m</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:00 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -10172,16 +10172,16 @@
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>03:40 PM</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>7h 36m</t>
+          <t>8h 16m</t>
         </is>
       </c>
       <c r="G215" s="7" t="n">
-        <v>7.6</v>
+        <v>8.27</v>
       </c>
       <c r="H215" s="5" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="I215" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:00 PM)</t>
+          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:40 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I215"/>
+  <dimension ref="A1:I218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10191,6 +10191,141 @@
       <c r="I215" s="6" t="inlineStr">
         <is>
           <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>11h 00m</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H216" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I216" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:00 PM / 11h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>11h 00m</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I217" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:00 PM / 11h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 05:40 PM / 9h 40m)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I218"/>
+  <dimension ref="A1:I227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10326,6 +10326,411 @@
       <c r="I218" s="6" t="inlineStr">
         <is>
           <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 05:40 PM / 9h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>10h 30m</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I221" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I222" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I223" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I224" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>06:30 AM</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I225" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:30 AM – 06:00 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H226" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (10:00 AM – 06:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>06:30 AM</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I227" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:30 AM – 06:00 PM / 11h 30m)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I227"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10731,6 +10731,141 @@
       <c r="I227" s="6" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (06:30 AM – 06:00 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H228" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I228" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>10h 30m</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I229" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:30 AM – 06:00 PM / 10h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H230" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I230" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:45 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I230"/>
+  <dimension ref="A1:I233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10866,6 +10866,141 @@
       <c r="I230" s="6" t="inlineStr">
         <is>
           <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I231" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>10h 30m</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H232" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I232" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:30 AM – 06:00 PM / 10h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I233" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -10307,25 +10307,25 @@
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>05:40 PM</t>
+          <t>06:20 PM</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>10h 20m</t>
         </is>
       </c>
       <c r="G218" s="7" t="n">
-        <v>9.67</v>
+        <v>10.33</v>
       </c>
       <c r="H218" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="I218" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 05:40 PM / 9h 40m)</t>
+          <t>⚡ Live Extended Station Duty (08:00 AM – 06:20 PM / 10h 20m)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I233"/>
+  <dimension ref="A1:I236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11001,6 +11001,141 @@
       <c r="I233" s="6" t="inlineStr">
         <is>
           <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I234" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>8h 10m</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I235" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>12h 15m</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="H236" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I236" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (03:30 AM – 03:45 PM / 12h 15m)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I236"/>
+  <dimension ref="A1:I240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11136,6 +11136,186 @@
       <c r="I236" s="6" t="inlineStr">
         <is>
           <t>✈️ Early dawn flight departure handling (03:30 AM – 03:45 PM / 12h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H237" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I237" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (07:00 AM – 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>11h 00m</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H238" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I238" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:00 PM / 11h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I240" s="6" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I218"/>
+  <dimension ref="A1:I219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10326,6 +10326,51 @@
       <c r="I218" s="6" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>08:00 PM</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>03:10 AM</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>7h 10m</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>Night Shift</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Logged out 03:10 AM next day)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I219"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10371,6 +10371,51 @@
       <c r="I219" s="6" t="inlineStr">
         <is>
           <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Logged out 03:10 AM next day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>07:20 PM</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr">
+        <is>
+          <t>12h 20m</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 07:20 PM / 12h 20m)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I220"/>
+  <dimension ref="A1:I221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10414,6 +10414,51 @@
         </is>
       </c>
       <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 07:20 PM / 12h 20m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>07:20 PM</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>12h 20m</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I221" s="6" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (07:00 AM – 07:20 PM / 12h 20m)</t>
         </is>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I221"/>
+  <dimension ref="A1:I222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10461,6 +10461,51 @@
       <c r="I221" s="6" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (07:00 AM – 07:20 PM / 12h 20m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Almohammad</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>07:06 PM</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>12h 06m</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I222" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 07:06 PM / 12h 06m)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I222"/>
+  <dimension ref="A1:I223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10506,6 +10506,51 @@
       <c r="I222" s="6" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (07:00 AM – 07:06 PM / 12h 06m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>05:30 AM</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>13h 30m</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="I223" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (05:30 AM – 07:00 PM / 13h 30m)</t>
         </is>
       </c>
     </row>

--- a/attendance_master_2026.xlsx
+++ b/attendance_master_2026.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I223"/>
+  <dimension ref="A1:I226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10551,6 +10551,141 @@
       <c r="I223" s="6" t="inlineStr">
         <is>
           <t>⚡ Live Extended Station Duty (05:30 AM – 07:00 PM / 13h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I224" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Company Paid Standby (Flight Cancelled - Station Standby)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I225" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Company Paid Standby (Flight Cancelled - Station Standby)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H226" s="5" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t>🏢 Company Paid Standby (Flight Cancelled - Station Standby)</t>
         </is>
       </c>
     </row>
